--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -860,16 +860,16 @@
         <v>2.62</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I2" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
         <v>4.4</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
         <v>1.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
         <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="H4" t="n">
         <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O5" t="n">
         <v>1.15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G9" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="H9" t="n">
         <v>6.2</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J9" t="n">
         <v>4.6</v>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
         <v>1.59</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3666,7 +3666,7 @@
         <v>1.11</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>2.18</v>
       </c>
       <c r="G15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
         <v>3.05</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
         <v>4.2</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="G16" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="G22" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H22" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="I22" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="K22" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G28" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="H28" t="n">
         <v>2.92</v>
       </c>
       <c r="I28" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -7494,7 +7494,7 @@
         <v>1.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G31" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H31" t="n">
         <v>5.1</v>
       </c>
       <c r="I31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J31" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G32" t="n">
         <v>1.99</v>
@@ -8492,7 +8492,7 @@
         <v>3.15</v>
       </c>
       <c r="K32" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.24</v>
+        <v>1.02</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
@@ -1144,7 +1144,7 @@
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.8</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I4" t="n">
         <v>3.05</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.33</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
         <v>1.15</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.48</v>
       </c>
       <c r="G9" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="H9" t="n">
         <v>6.2</v>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
         <v>1.59</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G11" t="n">
         <v>4.1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I11" t="n">
         <v>3.2</v>
@@ -3158,7 +3158,7 @@
         <v>2.66</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
@@ -3660,13 +3660,13 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3699,7 +3699,7 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -4168,10 +4168,10 @@
         <v>3.05</v>
       </c>
       <c r="I15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.75</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.65</v>
       </c>
       <c r="K15" t="n">
         <v>4.2</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -4416,16 +4416,16 @@
         <v>2.38</v>
       </c>
       <c r="G16" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="H16" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="I16" t="n">
         <v>3.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="K16" t="n">
         <v>3.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G22" t="n">
         <v>4.4</v>
@@ -5946,7 +5946,7 @@
         <v>2.22</v>
       </c>
       <c r="I22" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J22" t="n">
         <v>2.9</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="G31" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="H31" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G32" t="n">
         <v>1.99</v>
       </c>
       <c r="H32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I32" t="n">
         <v>7.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8510,7 +8510,7 @@
         <v>1.66</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
         <v>1.99</v>
       </c>
       <c r="G33" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H33" t="n">
         <v>4</v>
@@ -8743,7 +8743,7 @@
         <v>5.2</v>
       </c>
       <c r="J33" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K33" t="n">
         <v>3.45</v>
@@ -8764,7 +8764,7 @@
         <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -863,7 +863,7 @@
         <v>2.86</v>
       </c>
       <c r="H2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
         <v>2.72</v>
@@ -875,16 +875,16 @@
         <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
         <v>2.36</v>
@@ -893,194 +893,194 @@
         <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I4" t="n">
         <v>3.05</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
         <v>1.15</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -1891,212 +1891,212 @@
         <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.01</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.48</v>
       </c>
       <c r="G9" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="H9" t="n">
         <v>6.2</v>
@@ -2668,7 +2668,7 @@
         <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G10" t="n">
         <v>2.08</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="J11" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
         <v>2.36</v>
@@ -4168,7 +4168,7 @@
         <v>3.05</v>
       </c>
       <c r="I15" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
         <v>3.75</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>2.64</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
         <v>2.7</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="G22" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H22" t="n">
         <v>2.22</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="J22" t="n">
         <v>2.9</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -7491,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="G31" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="H31" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K31" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8256,7 +8256,7 @@
         <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G32" t="n">
         <v>1.99</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>5.2</v>
       </c>
       <c r="J33" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K33" t="n">
         <v>3.45</v>
@@ -8764,7 +8764,7 @@
         <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB33"/>
+  <dimension ref="A1:CB39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G2" t="n">
         <v>2.86</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I2" t="n">
         <v>2.72</v>
@@ -875,16 +875,16 @@
         <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
         <v>4.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
         <v>2.36</v>
@@ -896,7 +896,7 @@
         <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
         <v>1.56</v>
@@ -908,7 +908,7 @@
         <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X2" t="n">
         <v>25</v>
@@ -923,7 +923,7 @@
         <v>44</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
@@ -944,7 +944,7 @@
         <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ2" t="n">
         <v>50</v>
@@ -962,7 +962,7 @@
         <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
         <v>19.5</v>
@@ -986,7 +986,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
         <v>17.5</v>
@@ -998,7 +998,7 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>30</v>
@@ -1013,7 +1013,7 @@
         <v>42</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
         <v>11.5</v>
@@ -1028,59 +1028,59 @@
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="BN2" t="n">
         <v>6.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP2" t="n">
         <v>19.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
         <v>18.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="BX2" t="n">
         <v>27</v>
       </c>
       <c r="BY2" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>18</v>
       </c>
       <c r="CA2" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="G3" t="n">
         <v>3.15</v>
@@ -1123,218 +1123,218 @@
         <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
@@ -1383,16 +1383,16 @@
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
         <v>2.26</v>
@@ -1401,194 +1401,194 @@
         <v>1.67</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
         <v>1.15</v>
@@ -1670,7 +1670,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -1885,16 +1885,16 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
         <v>1.02</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
       </c>
       <c r="N6" t="n">
         <v>1.25</v>
@@ -1906,7 +1906,7 @@
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -2139,218 +2139,218 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.02</v>
       </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G8" t="n">
         <v>1.74</v>
@@ -2393,218 +2393,218 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
         <v>2.34</v>
       </c>
-      <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -2635,220 +2635,220 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G9" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="H9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I9" t="n">
         <v>7.4</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
         <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -2889,220 +2889,220 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="H10" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
         <v>1.71</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1.99</v>
       </c>
       <c r="G11" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>2.82</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>1.15</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,246 +3388,246 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,16 +3642,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
@@ -3660,10 +3660,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3675,31 +3675,31 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
@@ -3816,65 +3816,65 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -3905,237 +3905,237 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.87</v>
+        <v>3.95</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="I14" t="n">
         <v>2.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
         <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,229 +4150,229 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>1.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="H16" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.61</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.28</v>
+        <v>1.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,17 +4907,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Independiente Chivilcoy</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CA Douglas Haig</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4933,208 +4933,208 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Circulo Deportivo Otamendi</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olimpo</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
       </c>
       <c r="J19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.02</v>
       </c>
-      <c r="K19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,48 +5415,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Villa Mitre</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
@@ -5465,184 +5465,184 @@
         <v>1.01</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Club Atletico el Linqueno</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sportivo Belgrano</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P22" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.34</v>
+        <v>1.12</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,244 +6177,244 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Escobar FC</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gimnasia Conc del Uruguay</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -6431,17 +6431,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9 de Julio Rafaela</t>
+          <t>Independiente Chivilcoy</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gimnasia y Chivilcoy</t>
+          <t>CA Douglas Haig</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,36 +6685,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Circulo Deportivo Otamendi</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Olimpo</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
         <v>1.01</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,36 +6939,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Villa Mitre</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
         <v>1.01</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,36 +7193,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Club Atletico el Linqueno</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sportivo Belgrano</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7237,7 +7237,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -7447,234 +7447,234 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.42</v>
+        <v>3.25</v>
       </c>
       <c r="G28" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="H28" t="n">
-        <v>2.92</v>
+        <v>2.12</v>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="K28" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P28" t="n">
         <v>1.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,36 +7701,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Escobar FC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Gimnasia Conc del Uruguay</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
@@ -7955,251 +7955,251 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P30" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8209,36 +8209,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>9 de Julio Rafaela</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Gimnasia y Chivilcoy</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>1.53</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="K31" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8463,498 +8463,2022 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1.8</v>
       </c>
       <c r="G32" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="H32" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="I32" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K32" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.66</v>
       </c>
-      <c r="Q32" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 08:16:17</t>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Atletico GO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:43:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Club Oriental de La Paz</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Colon FC</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:43:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:43:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:43:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>FC Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:43:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Maranhao</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB38" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:43:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Ypiranga RS</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Confianca</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F39" t="n">
         <v>1.99</v>
       </c>
-      <c r="G33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="H33" t="n">
-        <v>4</v>
-      </c>
-      <c r="I33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="G39" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="n">
         <v>3.45</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB33" t="inlineStr">
-        <is>
-          <t>2026-06-26 08:16:17</t>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB39" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:43:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -1111,187 +1111,187 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="G3" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="W3" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG3" t="n">
         <v>23</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
         <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AM3" t="n">
         <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BO3" t="n">
         <v>4.5</v>
@@ -1300,41 +1300,41 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.68</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -1425,7 +1425,7 @@
         <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
         <v>55</v>
@@ -1434,7 +1434,7 @@
         <v>17.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
         <v>15.5</v>
@@ -1455,13 +1455,13 @@
         <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
         <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
         <v>70</v>
@@ -1473,7 +1473,7 @@
         <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AQ4" t="n">
         <v>12.5</v>
@@ -1482,7 +1482,7 @@
         <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1503,7 +1503,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BA4" t="n">
         <v>24</v>
@@ -1515,10 +1515,10 @@
         <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF4" t="n">
         <v>12</v>
@@ -1536,13 +1536,13 @@
         <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN4" t="n">
         <v>6</v>
@@ -1554,16 +1554,16 @@
         <v>18.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU4" t="n">
         <v>4.7</v>
@@ -1572,23 +1572,23 @@
         <v>21</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>970</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
         <v>1.25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.31</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.3</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="G8" t="n">
         <v>1.74</v>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>2.36</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2429,7 +2429,7 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
         <v>2.34</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.47</v>
       </c>
       <c r="G9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H9" t="n">
         <v>6.4</v>
@@ -2665,7 +2665,7 @@
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q9" t="n">
         <v>1.53</v>
@@ -2686,7 +2686,7 @@
         <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="X9" t="n">
         <v>29</v>
@@ -2806,7 +2806,7 @@
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,13 +2818,13 @@
         <v>4.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BP9" t="n">
         <v>9.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2836,7 +2836,7 @@
         <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H10" t="n">
         <v>4.1</v>
@@ -2937,10 +2937,10 @@
         <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X10" t="n">
         <v>23</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3191,7 +3191,7 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>2.92</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H12" t="n">
         <v>2.48</v>
@@ -3418,7 +3418,7 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
         <v>2.94</v>
@@ -3430,16 +3430,16 @@
         <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U12" t="n">
         <v>1.9</v>
@@ -3448,109 +3448,109 @@
         <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="Z12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" t="n">
         <v>22</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AG12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV12" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
         <v>1.23</v>
       </c>
       <c r="R13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S13" t="n">
         <v>1.22</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>2.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
         <v>3.45</v>
@@ -3932,7 +3932,7 @@
         <v>1.77</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P14" t="n">
         <v>1.76</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -4180,10 +4180,10 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="O15" t="n">
         <v>1.33</v>
@@ -4192,13 +4192,13 @@
         <v>1.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
         <v>1.59</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -4945,13 +4945,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q18" t="n">
         <v>1.23</v>
@@ -4960,7 +4960,7 @@
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.23</v>
+        <v>2.56</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="n">
         <v>4.5</v>
@@ -5199,13 +5199,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
         <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q19" t="n">
         <v>1.16</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O22" t="n">
         <v>1.12</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -6457,22 +6457,22 @@
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P24" t="n">
         <v>1.24</v>
@@ -6481,184 +6481,184 @@
         <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -6711,22 +6711,22 @@
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K25" t="n">
         <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
         <v>1.24</v>
@@ -6735,184 +6735,184 @@
         <v>1.01</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -6965,208 +6965,208 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P26" t="n">
         <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -7225,16 +7225,16 @@
         <v>1000</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P27" t="n">
         <v>1.24</v>
@@ -7243,184 +7243,184 @@
         <v>1.01</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
         <v>2.74</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -7494,7 +7494,7 @@
         <v>1.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
         <v>1.18</v>
@@ -7569,58 +7569,58 @@
         <v>38</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH28" t="n">
         <v>3.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -7727,22 +7727,22 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P29" t="n">
         <v>1.24</v>
@@ -7751,184 +7751,184 @@
         <v>1.01</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -7978,13 +7978,13 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
         <v>3.15</v>
       </c>
       <c r="K30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -8017,10 +8017,10 @@
         <v>1.83</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X30" t="n">
         <v>970</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -8235,208 +8235,208 @@
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K31" t="n">
         <v>1000</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
         <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -8477,166 +8477,166 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="H32" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="I32" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
         <v>3.3</v>
       </c>
       <c r="K32" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.68</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="V32" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X32" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE32" t="n">
         <v>1.8</v>
       </c>
-      <c r="X32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -8731,166 +8731,166 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="G33" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="I33" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="J33" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K33" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="L33" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P33" t="n">
         <v>1.83</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R33" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U33" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="V33" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W33" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="X33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>540</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>450</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC33" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y33" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG33" t="n">
+      <c r="BD33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE33" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BF33" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>3.15</v>
+        <v>12.5</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -8985,220 +8985,220 @@
         </is>
       </c>
       <c r="F34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G34" t="n">
         <v>2.42</v>
       </c>
-      <c r="G34" t="n">
-        <v>2.8</v>
-      </c>
       <c r="H34" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="I34" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P34" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q34" t="n">
         <v>2.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI34" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -9239,230 +9239,230 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -9493,230 +9493,230 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P36" t="n">
         <v>1.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="G39" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H39" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-26 16:43:11</t>
+          <t>2026-06-26 19:00:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB39"/>
+  <dimension ref="A1:CB43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
         <v>4.4</v>
@@ -881,34 +881,34 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
         <v>25</v>
@@ -926,7 +926,7 @@
         <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
@@ -938,7 +938,7 @@
         <v>22</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>16.5</v>
@@ -968,7 +968,7 @@
         <v>19.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
         <v>17</v>
@@ -977,10 +977,10 @@
         <v>28</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
@@ -992,10 +992,10 @@
         <v>17.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
         <v>23</v>
@@ -1013,10 +1013,10 @@
         <v>42</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="n">
         <v>4.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>3.5</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -1135,7 +1135,7 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="O3" t="n">
         <v>1.48</v>
@@ -1144,25 +1144,25 @@
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
         <v>9.800000000000001</v>
@@ -1177,13 +1177,13 @@
         <v>50</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
         <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>44</v>
@@ -1204,10 +1204,10 @@
         <v>95</v>
       </c>
       <c r="AK3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM3" t="n">
         <v>190</v>
@@ -1219,58 +1219,58 @@
         <v>38</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="AR3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT3" t="n">
         <v>5.1</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AU3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY3" t="n">
         <v>6</v>
       </c>
-      <c r="AT3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
         <v>2.86</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>2.48</v>
       </c>
       <c r="G4" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
         <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>4.1</v>
@@ -1395,25 +1395,25 @@
         <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
         <v>2.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
         <v>2.46</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
         <v>1.58</v>
@@ -1422,43 +1422,43 @@
         <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z4" t="n">
         <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ4" t="n">
         <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
         <v>34</v>
@@ -1470,10 +1470,10 @@
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>12.5</v>
@@ -1482,7 +1482,7 @@
         <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1503,7 +1503,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BA4" t="n">
         <v>24</v>
@@ -1515,10 +1515,10 @@
         <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
         <v>12</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tobol Kostanay</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Altay</t>
+          <t>Trygg/Lade</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.74</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="P8" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -2626,229 +2626,229 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norrby IF</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="G9" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>4.8</v>
       </c>
-      <c r="K9" t="n">
+      <c r="AR9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG9" t="n">
         <v>5.4</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X9" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="BH9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV9" t="n">
         <v>32</v>
       </c>
-      <c r="Z9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="BW9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY9" t="n">
         <v>11</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>8.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -2880,229 +2880,229 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="G10" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="I10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X10" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT10" t="n">
         <v>4.5</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="AU10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN10" t="n">
         <v>4.5</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X10" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="BO10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT10" t="n">
         <v>11</v>
       </c>
-      <c r="AH10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="BU10" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>6</v>
-      </c>
       <c r="BV10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,21 +3129,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Follo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
@@ -3155,10 +3155,10 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,28 +3167,28 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
         <v>1.15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
         <v>1.15</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
@@ -3308,72 +3308,72 @@
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,174 +3383,174 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Stjordals-Blink</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Junkeren</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.09</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.42</v>
-      </c>
       <c r="P12" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>1.09</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2</v>
+        <v>1.09</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
         <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
         <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3559,75 +3559,75 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,33 +3637,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Tobol Kostanay</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.74</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3699,10 +3699,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3867,21 +3867,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,174 +3891,174 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.95</v>
+        <v>2.98</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="H14" t="n">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>1.77</v>
+        <v>2.72</v>
       </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR14" t="n">
         <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
         <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4067,75 +4067,75 @@
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,17 +4145,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4180,25 +4180,25 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="S15" t="n">
-        <v>2.84</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
         <v>1.04</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X16" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BJ16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,31 +4658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.38</v>
+        <v>3.9</v>
       </c>
       <c r="G17" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>2.88</v>
+        <v>1.42</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,22 +4691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>1.58</v>
       </c>
       <c r="R17" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4715,10 +4715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="W17" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4829,68 +4829,68 @@
         <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -4907,17 +4907,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4942,25 +4942,25 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,21 +5161,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Sotra SK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Jerv</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
@@ -5187,10 +5187,10 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,22 +5199,22 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O19" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -5223,10 +5223,10 @@
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,126 +5669,126 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="O21" t="n">
-        <v>1.08</v>
+        <v>1.45</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.08</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>1.08</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP21" t="n">
         <v>1.03</v>
@@ -5839,81 +5839,81 @@
         <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IBV</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22" t="n">
         <v>0</v>
       </c>
-      <c r="G22" t="n">
+      <c r="CA22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,36 +6177,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6239,10 +6239,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,36 +6431,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Independiente Chivilcoy</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CA Douglas Haig</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,23 +6469,23 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P24" t="n">
         <v>1.25</v>
       </c>
-      <c r="O24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
         <v>1.12</v>
       </c>
-      <c r="S24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="T24" t="n">
         <v>1.01</v>
       </c>
@@ -6661,21 +6661,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,36 +6685,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Circulo Deportivo Otamendi</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olimpo</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,22 +6723,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="O25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="R25" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6915,21 +6915,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,36 +6939,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Villa Mitre</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,22 +6977,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="O26" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="R26" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -7169,21 +7169,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,36 +7193,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Club Atletico el Linqueno</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sportivo Belgrano</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7231,10 +7231,10 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P27" t="n">
         <v>1.24</v>
@@ -7243,7 +7243,7 @@
         <v>1.01</v>
       </c>
       <c r="R27" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="S27" t="n">
         <v>1.01</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7452,229 +7452,229 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Independiente Chivilcoy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>CA Douglas Haig</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>2.74</v>
+        <v>1.03</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="P28" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1.58</v>
       </c>
       <c r="T28" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR28" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BN28" t="n">
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -7701,36 +7701,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Escobar FC</t>
+          <t>Circulo Deportivo Otamendi</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gimnasia Conc del Uruguay</t>
+          <t>Olimpo</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
         <v>1.04</v>
       </c>
-      <c r="G29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1.03</v>
-      </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,22 +7739,22 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O29" t="n">
         <v>1.01</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R29" t="n">
         <v>1.12</v>
       </c>
       <c r="S29" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,180 +7955,180 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Villa Mitre</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K30" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>1.26</v>
       </c>
       <c r="O30" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="P30" t="n">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>1.02</v>
       </c>
       <c r="R30" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="S30" t="n">
-        <v>4.8</v>
+        <v>1.72</v>
       </c>
       <c r="T30" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR30" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV30" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW30" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX30" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="BB30" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC30" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD30" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BE30" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8185,14 +8185,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -8209,17 +8209,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9 de Julio Rafaela</t>
+          <t>Club Atletico el Linqueno</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gimnasia y Chivilcoy</t>
+          <t>Sportivo Belgrano</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -8253,7 +8253,7 @@
         <v>1.01</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q31" t="n">
         <v>1.02</v>
@@ -8262,7 +8262,7 @@
         <v>1.12</v>
       </c>
       <c r="S31" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8463,36 +8463,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="G32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H32" t="n">
         <v>2.12</v>
       </c>
-      <c r="H32" t="n">
-        <v>4.3</v>
-      </c>
       <c r="I32" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="K32" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -8501,213 +8501,213 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.48</v>
       </c>
       <c r="O32" t="n">
         <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX32" t="n">
         <v>4.4</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X32" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT32" t="n">
+      <c r="AY32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG32" t="n">
         <v>4.6</v>
       </c>
-      <c r="AU32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BH32" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ32" t="n">
         <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BN32" t="n">
         <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BP32" t="n">
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BT32" t="n">
         <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,180 +8717,180 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Escobar FC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Gimnasia Conc del Uruguay</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="G33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S33" t="n">
         <v>1.5</v>
       </c>
-      <c r="H33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I33" t="n">
-        <v>11</v>
-      </c>
-      <c r="J33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T33" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR33" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS33" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU33" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW33" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX33" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA33" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB33" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC33" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD33" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE33" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF33" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8947,21 +8947,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,36 +8971,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>9 de Julio Rafaela</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Gimnasia y Chivilcoy</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="K34" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -9009,22 +9009,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="P34" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="R34" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="S34" t="n">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9033,10 +9033,10 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -9147,10 +9147,10 @@
         <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -9225,180 +9225,180 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="G35" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="H35" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="J35" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="K35" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.88</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="P35" t="n">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V35" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="W35" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="X35" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y35" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z35" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB35" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AE35" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AF35" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG35" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH35" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI35" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ35" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AK35" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL35" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP35" t="n">
-        <v>2.78</v>
+        <v>8.6</v>
       </c>
       <c r="AQ35" t="n">
         <v>10.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.48</v>
+        <v>6.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.52</v>
+        <v>6.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>2.66</v>
+        <v>6.2</v>
       </c>
       <c r="AY35" t="n">
-        <v>2.64</v>
+        <v>9.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.96</v>
+        <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BB35" t="n">
-        <v>2.96</v>
+        <v>8.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.96</v>
+        <v>8.6</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="BE35" t="n">
-        <v>3.35</v>
+        <v>11.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.35</v>
+        <v>19</v>
       </c>
       <c r="BG35" t="n">
-        <v>3.35</v>
+        <v>11</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
@@ -9479,180 +9479,180 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H36" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I36" t="n">
-        <v>210</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O36" t="n">
         <v>1.44</v>
       </c>
-      <c r="M36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.37</v>
-      </c>
       <c r="P36" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q36" t="n">
         <v>2.14</v>
       </c>
       <c r="R36" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S36" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V36" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP36" t="n">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="AQ36" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR36" t="n">
-        <v>25</v>
+        <v>1.82</v>
       </c>
       <c r="AS36" t="n">
-        <v>75</v>
+        <v>2.28</v>
       </c>
       <c r="AT36" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AV36" t="n">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="AW36" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="AX36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY36" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ36" t="n">
-        <v>17</v>
+        <v>4.4</v>
       </c>
       <c r="BA36" t="n">
-        <v>46</v>
+        <v>2.26</v>
       </c>
       <c r="BB36" t="n">
-        <v>18</v>
+        <v>2.32</v>
       </c>
       <c r="BC36" t="n">
-        <v>17.5</v>
+        <v>2.14</v>
       </c>
       <c r="BD36" t="n">
-        <v>32</v>
+        <v>2.22</v>
       </c>
       <c r="BE36" t="n">
-        <v>80</v>
+        <v>1.8</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BH36" t="n">
         <v>1000</v>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9733,251 +9733,251 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="G37" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="H37" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J37" t="n">
         <v>4.3</v>
       </c>
       <c r="K37" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P37" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="Q37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U37" t="n">
         <v>1.69</v>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9987,234 +9987,234 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="G38" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="H38" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P38" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BL38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BN38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BP38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BR38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BT38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BV38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BX38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BZ38" t="n">
         <v>0</v>
@@ -10224,261 +10224,1277 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00:30</t>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB39" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:18:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB40" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:18:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>FC Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X41" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>340</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB41" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:18:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Maranhao</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X42" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB42" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:18:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Ypiranga RS</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Confianca</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="F43" t="n">
         <v>1.95</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G43" t="n">
         <v>2.16</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H43" t="n">
         <v>4.5</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I43" t="n">
         <v>5.3</v>
       </c>
-      <c r="J39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="J43" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ43" t="n">
         <v>0</v>
       </c>
-      <c r="M39" t="n">
+      <c r="CA43" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB39" t="inlineStr">
-        <is>
-          <t>2026-06-26 19:00:30</t>
+      <c r="CB43" t="inlineStr">
+        <is>
+          <t>2026-06-26 21:18:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -863,7 +863,7 @@
         <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
         <v>2.7</v>
@@ -890,7 +890,7 @@
         <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
         <v>1.56</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.78</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
@@ -2408,130 +2408,130 @@
         <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
         <v>1.03</v>
@@ -2543,7 +2543,7 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI8" t="n">
         <v>1.01</v>
@@ -2561,7 +2561,7 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.34</v>
@@ -2659,16 +2659,16 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.48</v>
@@ -2677,10 +2677,10 @@
         <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
         <v>1.29</v>
@@ -2689,112 +2689,112 @@
         <v>2.02</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="n">
         <v>36</v>
       </c>
       <c r="AA9" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
         <v>48</v>
       </c>
       <c r="AF9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
         <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
         <v>42</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.8</v>
+        <v>16.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.8</v>
+        <v>36</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.5</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
         <v>11.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.6</v>
+        <v>27</v>
       </c>
       <c r="BB9" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="BC9" t="n">
         <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.7</v>
+        <v>32</v>
       </c>
       <c r="BF9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.4</v>
+        <v>24</v>
       </c>
       <c r="BH9" t="n">
         <v>3.95</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>1.47</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I10" t="n">
         <v>7.4</v>
@@ -2910,10 +2910,10 @@
         <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -2922,10 +2922,10 @@
         <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
         <v>2.48</v>
@@ -2940,7 +2940,7 @@
         <v>1.15</v>
       </c>
       <c r="W10" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="X10" t="n">
         <v>29</v>
@@ -3054,7 +3054,7 @@
         <v>4.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -3143,157 +3143,157 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>1.89</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>1.15</v>
+        <v>2.16</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
         <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
         <v>1.03</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
         <v>1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3445,10 +3445,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G13" t="n">
         <v>1.74</v>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>2.36</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
         <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
@@ -4067,68 +4067,68 @@
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.4</v>
+        <v>7.4</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -4165,10 +4165,10 @@
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="J15" t="n">
         <v>1.03</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -4945,13 +4945,13 @@
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O18" t="n">
         <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q18" t="n">
         <v>1.87</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -5175,46 +5175,46 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>1.24</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.23</v>
+        <v>1.74</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>1.23</v>
+        <v>2.82</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -5223,109 +5223,109 @@
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
         <v>1.03</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
         <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M20" t="n">
         <v>1.04</v>
@@ -5591,68 +5591,68 @@
         <v>16.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.91</v>
+        <v>3.25</v>
       </c>
       <c r="BJ20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
         <v>12.5</v>
       </c>
-      <c r="BK20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BN20" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.76</v>
+        <v>7.6</v>
       </c>
       <c r="BR20" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.81</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BV20" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.81</v>
+        <v>9</v>
       </c>
       <c r="BX20" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.84</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.79</v>
+        <v>8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="G21" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="H21" t="n">
         <v>2.88</v>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
         <v>2.76</v>
@@ -5701,82 +5701,82 @@
         <v>3.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M21" t="n">
         <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O21" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R21" t="n">
         <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="X21" t="n">
         <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AG21" t="n">
         <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL21" t="n">
         <v>65</v>
@@ -5785,128 +5785,128 @@
         <v>170</v>
       </c>
       <c r="AN21" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.43</v>
+        <v>5.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.43</v>
+        <v>3.65</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.43</v>
+        <v>2.24</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.43</v>
+        <v>3.95</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.43</v>
+        <v>2.24</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -5961,13 +5961,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O22" t="n">
         <v>1.23</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q22" t="n">
         <v>1.23</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -7993,13 +7993,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O30" t="n">
         <v>1.01</v>
       </c>
       <c r="P30" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q30" t="n">
         <v>1.02</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
         <v>2.48</v>
       </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P32" t="n">
         <v>1.59</v>
@@ -8516,7 +8516,7 @@
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="T32" t="n">
         <v>1.93</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
         <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
         <v>2.28</v>
       </c>
       <c r="U37" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V37" t="n">
         <v>1.1</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -10109,58 +10109,58 @@
         <v>95</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH38" t="n">
         <v>3.35</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G39" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H39" t="n">
         <v>4.6</v>
@@ -10294,7 +10294,7 @@
         <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T39" t="n">
         <v>1.91</v>
@@ -10306,7 +10306,7 @@
         <v>1.22</v>
       </c>
       <c r="W39" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X39" t="n">
         <v>14</v>
@@ -10324,7 +10324,7 @@
         <v>8.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD39" t="n">
         <v>21</v>
@@ -10372,7 +10372,7 @@
         <v>24</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT39" t="n">
         <v>7.2</v>
@@ -10384,7 +10384,7 @@
         <v>16.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX39" t="n">
         <v>9</v>
@@ -10396,7 +10396,7 @@
         <v>17.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB39" t="n">
         <v>17</v>
@@ -10408,13 +10408,13 @@
         <v>29</v>
       </c>
       <c r="BE39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF39" t="n">
         <v>11</v>
       </c>
       <c r="BG39" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10423,10 +10423,10 @@
         <v>1.01</v>
       </c>
       <c r="BJ39" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
@@ -10435,28 +10435,28 @@
         <v>1.01</v>
       </c>
       <c r="BN39" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO39" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP39" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ39" t="n">
         <v>1.01</v>
       </c>
       <c r="BR39" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS39" t="n">
         <v>1.01</v>
       </c>
       <c r="BT39" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
@@ -10471,14 +10471,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA39" t="n">
         <v>1.01</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
         <v>4.2</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.8</v>
+        <v>2.98</v>
       </c>
       <c r="AU40" t="n">
         <v>7</v>
@@ -10677,7 +10677,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ40" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK40" t="n">
         <v>1.01</v>
@@ -10686,16 +10686,16 @@
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BN40" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO40" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP40" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ40" t="n">
         <v>1.01</v>
@@ -10707,10 +10707,10 @@
         <v>1.01</v>
       </c>
       <c r="BT40" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
         <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K41" t="n">
         <v>5.4</v>
@@ -10784,10 +10784,10 @@
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N41" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>1.25</v>
@@ -10805,10 +10805,10 @@
         <v>2.74</v>
       </c>
       <c r="T41" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U41" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V41" t="n">
         <v>1.11</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -11017,34 +11017,34 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="G42" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="H42" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I42" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K42" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="O42" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P42" t="n">
         <v>1.61</v>
@@ -11068,13 +11068,13 @@
         <v>1.19</v>
       </c>
       <c r="W42" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X42" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Y42" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z42" t="n">
         <v>50</v>
@@ -11083,10 +11083,10 @@
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD42" t="n">
         <v>26</v>
@@ -11095,10 +11095,10 @@
         <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG42" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH42" t="n">
         <v>30</v>
@@ -11107,7 +11107,7 @@
         <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK42" t="n">
         <v>28</v>
@@ -11119,61 +11119,61 @@
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR42" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS42" t="n">
         <v>1.01</v>
       </c>
       <c r="AT42" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU42" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV42" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW42" t="n">
         <v>1.01</v>
       </c>
       <c r="AX42" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY42" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA42" t="n">
         <v>1.01</v>
       </c>
       <c r="BB42" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC42" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD42" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF42" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG42" t="n">
         <v>1.01</v>
@@ -11188,49 +11188,49 @@
         <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BN42" t="n">
         <v>1000</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BP42" t="n">
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BT42" t="n">
         <v>1000</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BZ42" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>
@@ -11292,10 +11292,10 @@
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N43" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="O43" t="n">
         <v>1.52</v>
@@ -11313,10 +11313,10 @@
         <v>4.7</v>
       </c>
       <c r="T43" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="U43" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V43" t="n">
         <v>1.23</v>
@@ -11352,31 +11352,31 @@
         <v>13.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH43" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM43" t="n">
         <v>260</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP43" t="n">
         <v>6.4</v>
@@ -11385,10 +11385,10 @@
         <v>9</v>
       </c>
       <c r="AR43" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AS43" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
         <v>5</v>
@@ -11400,7 +11400,7 @@
         <v>15</v>
       </c>
       <c r="AW43" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
         <v>8.199999999999999</v>
@@ -11412,7 +11412,7 @@
         <v>18.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
         <v>18.5</v>
@@ -11421,16 +11421,16 @@
         <v>20</v>
       </c>
       <c r="BD43" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>150</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
         <v>19</v>
       </c>
       <c r="BG43" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="n">
         <v>3.2</v>
@@ -11442,49 +11442,49 @@
         <v>1000</v>
       </c>
       <c r="BK43" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BN43" t="n">
         <v>1000</v>
       </c>
       <c r="BO43" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BP43" t="n">
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BT43" t="n">
         <v>1000</v>
       </c>
       <c r="BU43" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BZ43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-26 21:18:23</t>
+          <t>2026-06-26 23:36:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB49"/>
+  <dimension ref="A1:CB57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>3.5</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="I3" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -1135,7 +1135,7 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
         <v>1.48</v>
@@ -1159,10 +1159,10 @@
         <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
         <v>9.800000000000001</v>
@@ -1171,7 +1171,7 @@
         <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AA3" t="n">
         <v>50</v>
@@ -1219,58 +1219,58 @@
         <v>38</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG3" t="n">
         <v>8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7.2</v>
       </c>
       <c r="BH3" t="n">
         <v>2.86</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -1377,10 +1377,10 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -2393,34 +2393,34 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O8" t="n">
         <v>1.02</v>
       </c>
-      <c r="K8" t="n">
-        <v>950</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -2647,10 +2647,10 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2662,7 +2662,7 @@
         <v>1.08</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9" t="n">
         <v>1.07</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -2901,10 +2901,10 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O10" t="n">
         <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q10" t="n">
         <v>1.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -3155,10 +3155,10 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q11" t="n">
         <v>1.02</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norwegian 2nd Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,239 +3388,239 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trygg/Lade</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.71</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
-        <v>1.82</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>1.06</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="R12" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="T12" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
         <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3690,7 +3690,7 @@
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FK Kaisar</t>
+          <t>Trygg/Lade</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>1.82</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
-        <v>1.06</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S14" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tobol Kostanay</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FK Altay</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.1</v>
+        <v>1.92</v>
       </c>
       <c r="G15" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="H15" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.13</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>1.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Norwegian 2nd Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Stjordals-Blink</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Junkeren</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G16" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="H16" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="I16" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="K16" t="n">
-        <v>46</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>1.82</v>
+        <v>2.48</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2</v>
+        <v>2.84</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Norwegian 2nd Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,175 +4658,175 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Follo</t>
+          <t>Tobol Kostanay</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.9</v>
+        <v>1.11</v>
       </c>
       <c r="G17" t="n">
-        <v>5.6</v>
+        <v>1.74</v>
       </c>
       <c r="H17" t="n">
-        <v>1.71</v>
+        <v>2.68</v>
       </c>
       <c r="I17" t="n">
-        <v>1.87</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>1.09</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>1.13</v>
       </c>
       <c r="O17" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>1.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="S17" t="n">
-        <v>2.16</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="X17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.64</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.66</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.86</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.54</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.54</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.98</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>2.78</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.74</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Stjordals-Blink</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Norrby IF</t>
+          <t>Junkeren</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="G18" t="n">
-        <v>1.54</v>
+        <v>2.14</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.62</v>
+        <v>1.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
-        <v>2.48</v>
+        <v>1.82</v>
       </c>
       <c r="T18" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="W18" t="n">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="X18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,239 +5166,239 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Follo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.92</v>
+        <v>4.5</v>
       </c>
       <c r="G19" t="n">
-        <v>1.98</v>
+        <v>5.3</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>1.68</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>1.79</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="P19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.24</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X19" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AX19" t="n">
         <v>2.34</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X19" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AY19" t="n">
-        <v>9.4</v>
+        <v>2.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>2.18</v>
       </c>
       <c r="BA19" t="n">
-        <v>27</v>
+        <v>2.28</v>
       </c>
       <c r="BB19" t="n">
-        <v>15.5</v>
+        <v>2.42</v>
       </c>
       <c r="BC19" t="n">
-        <v>16.5</v>
+        <v>2.36</v>
       </c>
       <c r="BD19" t="n">
-        <v>20</v>
+        <v>2.36</v>
       </c>
       <c r="BE19" t="n">
-        <v>32</v>
+        <v>2.38</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.4</v>
+        <v>2.34</v>
       </c>
       <c r="BG19" t="n">
-        <v>24</v>
+        <v>3.4</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -5689,10 +5689,10 @@
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="J21" t="n">
         <v>1.03</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
         <v>1.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R23" t="n">
         <v>1.23</v>
@@ -6233,10 +6233,10 @@
         <v>4.4</v>
       </c>
       <c r="T23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.89</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.87</v>
       </c>
       <c r="V23" t="n">
         <v>1.42</v>
@@ -6251,7 +6251,7 @@
         <v>12</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA23" t="n">
         <v>70</v>
@@ -6263,7 +6263,7 @@
         <v>8.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>55</v>
@@ -6299,19 +6299,19 @@
         <v>60</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AR23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AU23" t="n">
         <v>3.05</v>
@@ -6320,37 +6320,37 @@
         <v>3.7</v>
       </c>
       <c r="AW23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA23" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BB23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD23" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.5</v>
       </c>
       <c r="BE23" t="n">
         <v>4.6</v>
       </c>
       <c r="BF23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG23" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>4.4</v>
       </c>
       <c r="BH23" t="n">
         <v>3.05</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,246 +6436,246 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I24" t="n">
         <v>2.2</v>
       </c>
-      <c r="G24" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.4</v>
-      </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>1.77</v>
       </c>
       <c r="O24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.21</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.53</v>
-      </c>
       <c r="S24" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="T24" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="W24" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Norwegian 2nd Division</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,55 +6690,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sotra SK</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jerv</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>1.32</v>
       </c>
       <c r="O25" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>1.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6747,109 +6747,109 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
         <v>1.03</v>
@@ -6915,21 +6915,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6944,55 +6944,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Sotra SK</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Jerv</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="O26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.32</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -7001,109 +7001,109 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
         <v>1.03</v>
@@ -7169,21 +7169,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7198,239 +7198,239 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="H27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.42</v>
       </c>
-      <c r="I27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.83</v>
-      </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL27" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,251 +8971,251 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>2.74</v>
+        <v>1.02</v>
       </c>
       <c r="K34" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="P34" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.32</v>
+        <v>1.29</v>
       </c>
       <c r="R34" t="n">
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="T34" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB34" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD34" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF34" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34" t="n">
         <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BN34" t="n">
         <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BT34" t="n">
         <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9225,17 +9225,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Villa Mitre</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -9251,7 +9251,7 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K35" t="n">
         <v>1000</v>
@@ -9263,22 +9263,22 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P35" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -9455,21 +9455,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9479,17 +9479,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Club Atletico el Linqueno</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sportivo Belgrano</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -9505,7 +9505,7 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
@@ -9517,22 +9517,22 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O36" t="n">
         <v>1.01</v>
       </c>
       <c r="P36" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R36" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -9601,52 +9601,52 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
         <v>1.01</v>
@@ -9709,21 +9709,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9733,17 +9733,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Independiente Chivilcoy</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CA Douglas Haig</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -9759,7 +9759,7 @@
         <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K37" t="n">
         <v>1000</v>
@@ -9780,13 +9780,13 @@
         <v>1.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="R37" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -9963,21 +9963,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9987,36 +9987,36 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Circulo Deportivo Otamendi</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olimpo</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="G38" t="n">
         <v>1000</v>
       </c>
       <c r="H38" t="n">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="I38" t="n">
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -10025,7 +10025,7 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O38" t="n">
         <v>1.01</v>
@@ -10034,13 +10034,13 @@
         <v>1.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="R38" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -10217,21 +10217,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Escobar FC</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gimnasia Conc del Uruguay</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -10267,7 +10267,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10279,7 +10279,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O39" t="n">
         <v>1.01</v>
@@ -10288,13 +10288,13 @@
         <v>1.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="R39" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -10471,21 +10471,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10495,17 +10495,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9 de Julio Rafaela</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gimnasia y Chivilcoy</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -10521,7 +10521,7 @@
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10542,13 +10542,13 @@
         <v>1.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="R40" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S40" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -10725,21 +10725,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10749,180 +10749,180 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G41" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I41" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K41" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="O41" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="P41" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="R41" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>4.8</v>
+        <v>1.43</v>
       </c>
       <c r="T41" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U41" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="X41" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z41" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA41" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC41" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD41" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE41" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG41" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH41" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI41" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL41" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM41" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ41" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR41" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU41" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV41" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW41" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX41" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ41" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA41" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="BB41" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC41" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD41" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BE41" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF41" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG41" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH41" t="n">
         <v>1000</v>
@@ -10986,14 +10986,14 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11003,36 +11003,36 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="G42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H42" t="n">
         <v>2.12</v>
       </c>
-      <c r="H42" t="n">
-        <v>4.3</v>
-      </c>
       <c r="I42" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="K42" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -11041,213 +11041,213 @@
         <v>1.1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.98</v>
+        <v>2.48</v>
       </c>
       <c r="O42" t="n">
         <v>1.44</v>
       </c>
       <c r="P42" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="R42" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX42" t="n">
         <v>4.4</v>
       </c>
-      <c r="T42" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X42" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT42" t="n">
+      <c r="AY42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG42" t="n">
         <v>4.6</v>
       </c>
-      <c r="AU42" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BH42" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BN42" t="n">
         <v>1000</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BP42" t="n">
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BT42" t="n">
         <v>1000</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BZ42" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11257,180 +11257,180 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Club Atletico el Linqueno</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sportivo Belgrano</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="G43" t="n">
-        <v>1.5</v>
+        <v>110</v>
       </c>
       <c r="H43" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="J43" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="K43" t="n">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="O43" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="P43" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.04</v>
+        <v>1.02</v>
       </c>
       <c r="R43" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="S43" t="n">
-        <v>3.75</v>
+        <v>1.56</v>
       </c>
       <c r="T43" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ43" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR43" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AS43" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AT43" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU43" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AV43" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW43" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AX43" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY43" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ43" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA43" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB43" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC43" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD43" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE43" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BF43" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11487,21 +11487,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ43" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11511,234 +11511,234 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>Circulo Deportivo Otamendi</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Olimpo</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.12</v>
+        <v>1.52</v>
       </c>
       <c r="G44" t="n">
-        <v>2.42</v>
+        <v>110</v>
       </c>
       <c r="H44" t="n">
-        <v>3.5</v>
+        <v>1.52</v>
       </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>110</v>
       </c>
       <c r="J44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K44" t="n">
         <v>3</v>
       </c>
-      <c r="K44" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L44" t="n">
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="O44" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="P44" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.28</v>
+        <v>1.02</v>
       </c>
       <c r="R44" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="S44" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="T44" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U44" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AR44" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AU44" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV44" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AW44" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX44" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AY44" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ44" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB44" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC44" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE44" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI44" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ44" t="n">
         <v>1000</v>
       </c>
       <c r="BK44" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BN44" t="n">
         <v>1000</v>
       </c>
       <c r="BO44" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BP44" t="n">
         <v>1000</v>
       </c>
       <c r="BQ44" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BR44" t="n">
         <v>1000</v>
       </c>
       <c r="BS44" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BT44" t="n">
         <v>1000</v>
       </c>
       <c r="BU44" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BV44" t="n">
         <v>1000</v>
       </c>
       <c r="BW44" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BX44" t="n">
         <v>1000</v>
       </c>
       <c r="BY44" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BZ44" t="n">
         <v>0</v>
@@ -11748,14 +11748,14 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11765,251 +11765,251 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Independiente Chivilcoy</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>CA Douglas Haig</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="G45" t="n">
-        <v>1.91</v>
+        <v>110</v>
       </c>
       <c r="H45" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>5.3</v>
+        <v>110</v>
       </c>
       <c r="J45" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="K45" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="O45" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="P45" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.06</v>
+        <v>1.02</v>
       </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="S45" t="n">
-        <v>3.8</v>
+        <v>1.58</v>
       </c>
       <c r="T45" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U45" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y45" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z45" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA45" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD45" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE45" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF45" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG45" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH45" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI45" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL45" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM45" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO45" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ45" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR45" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT45" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU45" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV45" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW45" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AX45" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY45" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ45" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA45" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BB45" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC45" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD45" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF45" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG45" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
       </c>
       <c r="BI45" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BJ45" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK45" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BN45" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP45" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BR45" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="BT45" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU45" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BZ45" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CA45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12019,251 +12019,251 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Villa Mitre</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="G46" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="H46" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J46" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K46" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>3.15</v>
+        <v>1.27</v>
       </c>
       <c r="O46" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="P46" t="n">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.16</v>
+        <v>1.02</v>
       </c>
       <c r="R46" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>1.72</v>
       </c>
       <c r="T46" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="U46" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="X46" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y46" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z46" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA46" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC46" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD46" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE46" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH46" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI46" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK46" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL46" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM46" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO46" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR46" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.98</v>
+        <v>1.03</v>
       </c>
       <c r="AU46" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV46" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AW46" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX46" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AY46" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AZ46" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB46" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BC46" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BD46" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE46" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF46" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG46" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
       </c>
       <c r="BI46" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="BJ46" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="BN46" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO46" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP46" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="BT46" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV46" t="n">
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BZ46" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12273,126 +12273,126 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Escobar FC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Gimnasia Conc del Uruguay</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="G47" t="n">
-        <v>1.55</v>
+        <v>1000</v>
       </c>
       <c r="H47" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="K47" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N47" t="n">
-        <v>3.7</v>
+        <v>1.25</v>
       </c>
       <c r="O47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P47" t="n">
         <v>1.25</v>
       </c>
-      <c r="P47" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q47" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="R47" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="S47" t="n">
-        <v>2.74</v>
+        <v>1.51</v>
       </c>
       <c r="T47" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U47" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="X47" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y47" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z47" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA47" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC47" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD47" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE47" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF47" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG47" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH47" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI47" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ47" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK47" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL47" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM47" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO47" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP47" t="n">
         <v>1.03</v>
@@ -12443,7 +12443,7 @@
         <v>1.03</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG47" t="n">
         <v>1.01</v>
@@ -12510,14 +12510,14 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12527,171 +12527,171 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>9 de Julio Rafaela</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Gimnasia y Chivilcoy</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="G48" t="n">
-        <v>1.9</v>
+        <v>110</v>
       </c>
       <c r="H48" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>6.8</v>
+        <v>110</v>
       </c>
       <c r="J48" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="K48" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2.58</v>
+        <v>1.25</v>
       </c>
       <c r="O48" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="P48" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R48" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="S48" t="n">
-        <v>4.3</v>
+        <v>1.49</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U48" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="X48" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y48" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z48" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA48" t="n">
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC48" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD48" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE48" t="n">
         <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG48" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH48" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI48" t="n">
         <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK48" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL48" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
         <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT48" t="n">
         <v>1.03</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE48" t="n">
         <v>1.03</v>
@@ -12703,58 +12703,58 @@
         <v>1.01</v>
       </c>
       <c r="BH48" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ48" t="n">
         <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BN48" t="n">
         <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BP48" t="n">
         <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BT48" t="n">
         <v>1000</v>
       </c>
       <c r="BU48" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BV48" t="n">
         <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BZ48" t="n">
         <v>0</v>
@@ -12764,14 +12764,14 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12781,244 +12781,2276 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="G49" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="H49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" t="n">
         <v>4.5</v>
       </c>
-      <c r="I49" t="n">
-        <v>5.4</v>
-      </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K49" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N49" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="O49" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="P49" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="R49" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S49" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T49" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="U49" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="V49" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W49" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="X49" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ49" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y49" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP49" t="n">
+      <c r="AR49" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU49" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ49" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AV49" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AX49" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AY49" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ49" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BB49" t="n">
-        <v>18.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC49" t="n">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BF49" t="n">
         <v>19</v>
       </c>
       <c r="BG49" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB49" t="inlineStr">
+        <is>
+          <t>2026-06-27 04:13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H50" t="n">
         <v>4.3</v>
       </c>
-      <c r="BH49" t="n">
+      <c r="I50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X50" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB50" t="inlineStr">
+        <is>
+          <t>2026-06-27 04:13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Atletico GO</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>11</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>530</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>440</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB51" t="inlineStr">
+        <is>
+          <t>2026-06-27 04:13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Club Oriental de La Paz</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Colon FC</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X52" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU52" t="n">
         <v>3.2</v>
       </c>
-      <c r="BI49" t="n">
+      <c r="AV52" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB52" t="inlineStr">
+        <is>
+          <t>2026-06-27 04:13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X53" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>36</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CB53" t="inlineStr">
+        <is>
+          <t>2026-06-27 04:13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S54" t="n">
+        <v>4</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X54" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CB54" t="inlineStr">
+        <is>
+          <t>2026-06-27 04:13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>FC Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H55" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X55" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>340</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB55" t="inlineStr">
+        <is>
+          <t>2026-06-27 04:13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Maranhao</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X56" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB56" t="inlineStr">
+        <is>
+          <t>2026-06-27 04:13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ypiranga RS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Confianca</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S57" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X57" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI57" t="n">
         <v>2.2</v>
       </c>
-      <c r="BJ49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK49" t="n">
+      <c r="BJ57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK57" t="n">
         <v>1.47</v>
       </c>
-      <c r="BL49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM49" t="n">
+      <c r="BL57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM57" t="n">
         <v>1.47</v>
       </c>
-      <c r="BN49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO49" t="n">
+      <c r="BN57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO57" t="n">
         <v>1.47</v>
       </c>
-      <c r="BP49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ49" t="n">
+      <c r="BP57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ57" t="n">
         <v>1.47</v>
       </c>
-      <c r="BR49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS49" t="n">
+      <c r="BR57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS57" t="n">
         <v>1.47</v>
       </c>
-      <c r="BT49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU49" t="n">
+      <c r="BT57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU57" t="n">
         <v>1.47</v>
       </c>
-      <c r="BV49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW49" t="n">
+      <c r="BV57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW57" t="n">
         <v>1.47</v>
       </c>
-      <c r="BX49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY49" t="n">
+      <c r="BX57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY57" t="n">
         <v>1.47</v>
       </c>
-      <c r="BZ49" t="n">
+      <c r="BZ57" t="n">
         <v>0</v>
       </c>
-      <c r="CA49" t="n">
+      <c r="CA57" t="n">
         <v>0</v>
       </c>
-      <c r="CB49" t="inlineStr">
-        <is>
-          <t>2026-06-27 01:54:37</t>
+      <c r="CB57" t="inlineStr">
+        <is>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -863,7 +863,7 @@
         <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I2" t="n">
         <v>2.7</v>
@@ -872,7 +872,7 @@
         <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
@@ -881,7 +881,7 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.21</v>
@@ -893,7 +893,7 @@
         <v>1.64</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
         <v>2.52</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>3.5</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
         <v>2.5</v>
@@ -1126,7 +1126,7 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -1135,7 +1135,7 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O3" t="n">
         <v>1.48</v>
@@ -1150,7 +1150,7 @@
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
         <v>2.94</v>
@@ -1924,7 +1924,7 @@
         <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X6" t="n">
         <v>25</v>
@@ -2014,10 +2014,10 @@
         <v>5.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>26</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
         <v>18.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
         <v>1.02</v>
@@ -2414,7 +2414,7 @@
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
         <v>1.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q11" t="n">
         <v>1.02</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
         <v>5.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>1.21</v>
@@ -3935,19 +3935,19 @@
         <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R14" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S14" t="n">
         <v>2.12</v>
       </c>
       <c r="T14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U14" t="n">
         <v>2.44</v>
@@ -3995,7 +3995,7 @@
         <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
         <v>970</v>
@@ -4007,67 +4007,67 @@
         <v>75</v>
       </c>
       <c r="AN14" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
         <v>42</v>
       </c>
       <c r="AP14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV14" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AW14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB14" t="n">
         <v>4</v>
       </c>
-      <c r="AR14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS14" t="n">
+      <c r="BC14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG14" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BH14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI14" t="n">
         <v>3.3</v>
@@ -4082,25 +4082,25 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.24</v>
+        <v>2.74</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.12</v>
+        <v>6.4</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.44</v>
+        <v>2.64</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.44</v>
+        <v>2.64</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
         <v>4.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -4210,7 +4210,7 @@
         <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
@@ -4240,7 +4240,7 @@
         <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>18.5</v>
@@ -4267,7 +4267,7 @@
         <v>42</v>
       </c>
       <c r="AP15" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>16.5</v>
@@ -4279,7 +4279,7 @@
         <v>36</v>
       </c>
       <c r="AT15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU15" t="n">
         <v>8</v>
@@ -4294,7 +4294,7 @@
         <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
         <v>14</v>
@@ -4324,55 +4324,55 @@
         <v>3.95</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BV15" t="n">
         <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BX15" t="n">
         <v>38</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -4431,10 +4431,10 @@
         <v>5.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
         <v>5.2</v>
@@ -4452,7 +4452,7 @@
         <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T16" t="n">
         <v>1.72</v>
@@ -4464,7 +4464,7 @@
         <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="X16" t="n">
         <v>29</v>
@@ -4548,7 +4548,7 @@
         <v>8.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
         <v>5.7</v>
@@ -4575,7 +4575,7 @@
         <v>6.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI16" t="n">
         <v>3.6</v>
@@ -4584,13 +4584,13 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN16" t="n">
         <v>4.5</v>
@@ -4599,34 +4599,34 @@
         <v>3.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT16" t="n">
         <v>11</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
         <v>1.74</v>
@@ -4694,19 +4694,19 @@
         <v>1.13</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
         <v>1.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R17" t="n">
         <v>1.08</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4715,7 +4715,7 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
         <v>2.34</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -4924,19 +4924,19 @@
         <v>1.82</v>
       </c>
       <c r="G18" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -5181,16 +5181,16 @@
         <v>5.3</v>
       </c>
       <c r="H19" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="I19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.24</v>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.17</v>
@@ -5223,7 +5223,7 @@
         <v>2.36</v>
       </c>
       <c r="V19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="W19" t="n">
         <v>1.23</v>
@@ -5283,58 +5283,58 @@
         <v>970</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.12</v>
+        <v>2.94</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.46</v>
+        <v>3.65</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.26</v>
+        <v>3.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.06</v>
+        <v>3.35</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.06</v>
+        <v>3.35</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.46</v>
+        <v>3.65</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.18</v>
+        <v>3.05</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.42</v>
+        <v>3.55</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.36</v>
+        <v>3.45</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.34</v>
+        <v>3.35</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>2.98</v>
       </c>
       <c r="G20" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="H20" t="n">
         <v>2.5</v>
@@ -5468,7 +5468,7 @@
         <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T20" t="n">
         <v>1.96</v>
@@ -5480,7 +5480,7 @@
         <v>1.53</v>
       </c>
       <c r="W20" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="X20" t="n">
         <v>11</v>
@@ -5537,19 +5537,19 @@
         <v>40</v>
       </c>
       <c r="AP20" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU20" t="n">
         <v>6.2</v>
@@ -5558,37 +5558,37 @@
         <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ20" t="n">
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH20" t="n">
         <v>3.05</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -5689,10 +5689,10 @@
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I21" t="n">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
         <v>1.03</v>
@@ -5710,19 +5710,19 @@
         <v>1.09</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P21" t="n">
         <v>1.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S21" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,31 +5928,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.99</v>
+        <v>3.9</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5961,31 +5961,31 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="O22" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="W22" t="n">
         <v>1.01</v>
@@ -6102,72 +6102,72 @@
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,251 +6177,251 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.56</v>
+        <v>1.99</v>
       </c>
       <c r="G23" t="n">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>2.86</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.56</v>
+        <v>1.37</v>
       </c>
       <c r="O23" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.12</v>
+        <v>1.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>4.4</v>
+        <v>1.15</v>
       </c>
       <c r="T23" t="n">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,239 +6436,239 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Astana</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.9</v>
+        <v>2.56</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="H24" t="n">
-        <v>1.42</v>
+        <v>2.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="J24" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
         <v>3.45</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>1.77</v>
+        <v>2.56</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="P24" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.58</v>
+        <v>2.28</v>
       </c>
       <c r="R24" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -6720,25 +6720,25 @@
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="O25" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P25" t="n">
         <v>1.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.87</v>
+        <v>1.35</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>1.35</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -6977,10 +6977,10 @@
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P26" t="n">
         <v>1.98</v>
@@ -6992,13 +6992,13 @@
         <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V26" t="n">
         <v>1.43</v>
@@ -7061,58 +7061,58 @@
         <v>30</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
         <v>4.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P27" t="n">
         <v>2.34</v>
@@ -7243,10 +7243,10 @@
         <v>1.64</v>
       </c>
       <c r="R27" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T27" t="n">
         <v>1.59</v>
@@ -7354,7 +7354,7 @@
         <v>21</v>
       </c>
       <c r="BC27" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD27" t="n">
         <v>21</v>
@@ -7363,49 +7363,49 @@
         <v>3.95</v>
       </c>
       <c r="BF27" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG27" t="n">
         <v>16.5</v>
       </c>
       <c r="BH27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI27" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK27" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BL27" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO27" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP27" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS27" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU27" t="n">
         <v>5.1</v>
@@ -7414,23 +7414,23 @@
         <v>23</v>
       </c>
       <c r="BW27" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BX27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY27" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -7485,13 +7485,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
         <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q28" t="n">
         <v>1.23</v>
@@ -7500,7 +7500,7 @@
         <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>2.56</v>
+        <v>1.23</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G34" t="n">
         <v>1000</v>
@@ -8997,7 +8997,7 @@
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
@@ -9009,13 +9009,13 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O34" t="n">
         <v>1.29</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q34" t="n">
         <v>1.29</v>
@@ -9024,7 +9024,7 @@
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9033,7 +9033,7 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K35" t="n">
         <v>1000</v>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O35" t="n">
         <v>1.3</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q35" t="n">
         <v>1.3</v>
@@ -9278,7 +9278,7 @@
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.3</v>
+        <v>2.42</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -9287,10 +9287,10 @@
         <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -9505,34 +9505,34 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O36" t="n">
         <v>1.02</v>
       </c>
-      <c r="K36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P36" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R36" t="n">
         <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -9541,10 +9541,10 @@
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -9601,52 +9601,52 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
         <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K37" t="n">
         <v>1000</v>
@@ -9774,7 +9774,7 @@
         <v>1.25</v>
       </c>
       <c r="O37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P37" t="n">
         <v>1.25</v>
@@ -9786,7 +9786,7 @@
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -9795,7 +9795,7 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
         <v>1.01</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10028,19 +10028,19 @@
         <v>1.25</v>
       </c>
       <c r="O38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P38" t="n">
         <v>1.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R38" t="n">
         <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -10049,10 +10049,10 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10282,7 +10282,7 @@
         <v>1.25</v>
       </c>
       <c r="O39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P39" t="n">
         <v>1.25</v>
@@ -10303,7 +10303,7 @@
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10536,7 +10536,7 @@
         <v>1.25</v>
       </c>
       <c r="O40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P40" t="n">
         <v>1.25</v>
@@ -10557,7 +10557,7 @@
         <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G41" t="n">
         <v>1000</v>
@@ -10775,7 +10775,7 @@
         <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -10790,7 +10790,7 @@
         <v>1.25</v>
       </c>
       <c r="O41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P41" t="n">
         <v>1.25</v>
@@ -10802,7 +10802,7 @@
         <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -10811,7 +10811,7 @@
         <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -11274,19 +11274,19 @@
         <v>1.04</v>
       </c>
       <c r="G43" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H43" t="n">
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J43" t="n">
         <v>1.03</v>
       </c>
       <c r="K43" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -11295,16 +11295,16 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P43" t="n">
         <v>1.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="R43" t="n">
         <v>1.12</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -11528,16 +11528,16 @@
         <v>1.52</v>
       </c>
       <c r="G44" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H44" t="n">
         <v>1.52</v>
       </c>
       <c r="I44" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K44" t="n">
         <v>3</v>
@@ -11549,7 +11549,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O44" t="n">
         <v>1.01</v>
@@ -11558,7 +11558,7 @@
         <v>1.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="R44" t="n">
         <v>1.12</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -11782,19 +11782,19 @@
         <v>1.04</v>
       </c>
       <c r="G45" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H45" t="n">
         <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J45" t="n">
         <v>1.03</v>
       </c>
       <c r="K45" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -12311,13 +12311,13 @@
         <v>1.08</v>
       </c>
       <c r="N47" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O47" t="n">
         <v>1.35</v>
       </c>
       <c r="P47" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q47" t="n">
         <v>1.53</v>
@@ -12326,7 +12326,7 @@
         <v>1.12</v>
       </c>
       <c r="S47" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -12544,19 +12544,19 @@
         <v>1.04</v>
       </c>
       <c r="G48" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H48" t="n">
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J48" t="n">
         <v>1.03</v>
       </c>
       <c r="K48" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -12795,19 +12795,19 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G49" t="n">
         <v>2.24</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I49" t="n">
         <v>4.5</v>
       </c>
       <c r="J49" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K49" t="n">
         <v>3.45</v>
@@ -12816,19 +12816,19 @@
         <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N49" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O49" t="n">
         <v>1.47</v>
       </c>
       <c r="P49" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R49" t="n">
         <v>1.22</v>
@@ -12849,13 +12849,13 @@
         <v>1.81</v>
       </c>
       <c r="X49" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y49" t="n">
         <v>970</v>
       </c>
       <c r="Z49" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA49" t="n">
         <v>120</v>
@@ -12912,7 +12912,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS49" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="AT49" t="n">
         <v>6.4</v>
@@ -12924,10 +12924,10 @@
         <v>7.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX49" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY49" t="n">
         <v>9.6</v>
@@ -12936,19 +12936,19 @@
         <v>19</v>
       </c>
       <c r="BA49" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="BB49" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="BC49" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD49" t="n">
         <v>10</v>
       </c>
       <c r="BE49" t="n">
-        <v>11.5</v>
+        <v>2.92</v>
       </c>
       <c r="BF49" t="n">
         <v>19</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -13049,16 +13049,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H50" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J50" t="n">
         <v>3.3</v>
@@ -13082,7 +13082,7 @@
         <v>1.67</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R50" t="n">
         <v>1.24</v>
@@ -13091,16 +13091,16 @@
         <v>4.4</v>
       </c>
       <c r="T50" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U50" t="n">
         <v>1.86</v>
       </c>
       <c r="V50" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W50" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X50" t="n">
         <v>970</v>
@@ -13109,10 +13109,10 @@
         <v>970</v>
       </c>
       <c r="Z50" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA50" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB50" t="n">
         <v>10</v>
@@ -13124,7 +13124,7 @@
         <v>970</v>
       </c>
       <c r="AE50" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF50" t="n">
         <v>970</v>
@@ -13139,7 +13139,7 @@
         <v>100</v>
       </c>
       <c r="AJ50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK50" t="n">
         <v>26</v>
@@ -13154,61 +13154,61 @@
         <v>24</v>
       </c>
       <c r="AO50" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP50" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ50" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX50" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR50" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>6</v>
-      </c>
       <c r="AY50" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AZ50" t="n">
-        <v>4.4</v>
+        <v>2.92</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="BB50" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="BD50" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BF50" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="BH50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -13306,43 +13306,43 @@
         <v>1.44</v>
       </c>
       <c r="G51" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H51" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I51" t="n">
         <v>11</v>
       </c>
       <c r="J51" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K51" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N51" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O51" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P51" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R51" t="n">
         <v>1.32</v>
       </c>
       <c r="S51" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T51" t="n">
         <v>2.28</v>
@@ -13357,10 +13357,10 @@
         <v>3</v>
       </c>
       <c r="X51" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z51" t="n">
         <v>110</v>
@@ -13369,7 +13369,7 @@
         <v>530</v>
       </c>
       <c r="AB51" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC51" t="n">
         <v>10.5</v>
@@ -13378,7 +13378,7 @@
         <v>38</v>
       </c>
       <c r="AE51" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF51" t="n">
         <v>7.8</v>
@@ -13390,7 +13390,7 @@
         <v>32</v>
       </c>
       <c r="AI51" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ51" t="n">
         <v>12.5</v>
@@ -13402,25 +13402,25 @@
         <v>50</v>
       </c>
       <c r="AM51" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AN51" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AO51" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AP51" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AR51" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS51" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AT51" t="n">
         <v>6</v>
@@ -13429,10 +13429,10 @@
         <v>9</v>
       </c>
       <c r="AV51" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AW51" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AX51" t="n">
         <v>6.8</v>
@@ -13441,10 +13441,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ51" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BA51" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BB51" t="n">
         <v>10.5</v>
@@ -13453,16 +13453,16 @@
         <v>15.5</v>
       </c>
       <c r="BD51" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE51" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>13</v>
       </c>
       <c r="BF51" t="n">
         <v>6.6</v>
       </c>
       <c r="BG51" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BH51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G52" t="n">
         <v>2.42</v>
@@ -13578,28 +13578,28 @@
         <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N52" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="O52" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P52" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="R52" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S52" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T52" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U52" t="n">
         <v>1.83</v>
@@ -13611,10 +13611,10 @@
         <v>1.7</v>
       </c>
       <c r="X52" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y52" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z52" t="n">
         <v>32</v>
@@ -13623,10 +13623,10 @@
         <v>110</v>
       </c>
       <c r="AB52" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC52" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD52" t="n">
         <v>19.5</v>
@@ -13635,7 +13635,7 @@
         <v>70</v>
       </c>
       <c r="AF52" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG52" t="n">
         <v>13.5</v>
@@ -13665,58 +13665,58 @@
         <v>95</v>
       </c>
       <c r="AP52" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AR52" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT52" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX52" t="n">
         <v>4</v>
       </c>
-      <c r="AW52" t="n">
+      <c r="AY52" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC52" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX52" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD52" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF52" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE52" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG52" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH52" t="n">
         <v>3.35</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
         <v>1.82</v>
       </c>
       <c r="G53" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H53" t="n">
         <v>4.8</v>
@@ -13838,7 +13838,7 @@
         <v>3.4</v>
       </c>
       <c r="O53" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P53" t="n">
         <v>1.81</v>
@@ -13862,7 +13862,7 @@
         <v>1.23</v>
       </c>
       <c r="W53" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X53" t="n">
         <v>14</v>
@@ -13871,10 +13871,10 @@
         <v>16.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA53" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB53" t="n">
         <v>8.4</v>
@@ -13886,7 +13886,7 @@
         <v>21</v>
       </c>
       <c r="AE53" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF53" t="n">
         <v>11.5</v>
@@ -13907,7 +13907,7 @@
         <v>22</v>
       </c>
       <c r="AL53" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM53" t="n">
         <v>150</v>
@@ -13916,7 +13916,7 @@
         <v>15</v>
       </c>
       <c r="AO53" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP53" t="n">
         <v>11</v>
@@ -13928,7 +13928,7 @@
         <v>24</v>
       </c>
       <c r="AS53" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT53" t="n">
         <v>7.2</v>
@@ -13940,7 +13940,7 @@
         <v>16.5</v>
       </c>
       <c r="AW53" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX53" t="n">
         <v>9</v>
@@ -13952,7 +13952,7 @@
         <v>17.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB53" t="n">
         <v>17</v>
@@ -13964,49 +13964,49 @@
         <v>29</v>
       </c>
       <c r="BE53" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF53" t="n">
         <v>11</v>
       </c>
       <c r="BG53" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH53" t="n">
         <v>1000</v>
       </c>
       <c r="BI53" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BJ53" t="n">
         <v>13.5</v>
       </c>
       <c r="BK53" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BN53" t="n">
         <v>5.7</v>
       </c>
       <c r="BO53" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP53" t="n">
         <v>18</v>
       </c>
       <c r="BQ53" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BR53" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS53" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BT53" t="n">
         <v>10.5</v>
@@ -14024,17 +14024,17 @@
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BZ53" t="n">
         <v>36</v>
       </c>
       <c r="CA53" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -14068,10 +14068,10 @@
         <v>1.92</v>
       </c>
       <c r="G54" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H54" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I54" t="n">
         <v>5.1</v>
@@ -14083,10 +14083,10 @@
         <v>3.75</v>
       </c>
       <c r="L54" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M54" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N54" t="n">
         <v>3.15</v>
@@ -14116,13 +14116,13 @@
         <v>1.25</v>
       </c>
       <c r="W54" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="X54" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y54" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z54" t="n">
         <v>42</v>
@@ -14179,58 +14179,58 @@
         <v>3.5</v>
       </c>
       <c r="AR54" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AU54" t="n">
         <v>7</v>
       </c>
       <c r="AV54" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AW54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD54" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX54" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>4</v>
-      </c>
       <c r="BE54" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF54" t="n">
         <v>12.5</v>
       </c>
       <c r="BG54" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BJ54" t="n">
         <v>15</v>
@@ -14242,7 +14242,7 @@
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BN54" t="n">
         <v>6</v>
@@ -14272,13 +14272,13 @@
         <v>1000</v>
       </c>
       <c r="BW54" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BZ54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G57" t="n">
         <v>2.16</v>
@@ -14842,7 +14842,7 @@
         <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L57" t="n">
         <v>1.01</v>
@@ -14869,16 +14869,16 @@
         <v>4.7</v>
       </c>
       <c r="T57" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U57" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V57" t="n">
         <v>1.22</v>
       </c>
       <c r="W57" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X57" t="n">
         <v>10.5</v>
@@ -14896,7 +14896,7 @@
         <v>7.8</v>
       </c>
       <c r="AC57" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD57" t="n">
         <v>26</v>
@@ -14914,7 +14914,7 @@
         <v>32</v>
       </c>
       <c r="AI57" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ57" t="n">
         <v>32</v>
@@ -14923,22 +14923,22 @@
         <v>36</v>
       </c>
       <c r="AL57" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM57" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN57" t="n">
         <v>32</v>
       </c>
       <c r="AO57" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP57" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="AQ57" t="n">
-        <v>9.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="AR57" t="n">
         <v>4</v>
@@ -14959,19 +14959,19 @@
         <v>4.2</v>
       </c>
       <c r="AX57" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY57" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ57" t="n">
-        <v>18.5</v>
+        <v>3.85</v>
       </c>
       <c r="BA57" t="n">
         <v>4.2</v>
       </c>
       <c r="BB57" t="n">
-        <v>18.5</v>
+        <v>3.85</v>
       </c>
       <c r="BC57" t="n">
         <v>20</v>
@@ -14983,7 +14983,7 @@
         <v>4.3</v>
       </c>
       <c r="BF57" t="n">
-        <v>19</v>
+        <v>3.85</v>
       </c>
       <c r="BG57" t="n">
         <v>4.3</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G2" t="n">
         <v>2.8</v>
@@ -869,7 +869,7 @@
         <v>2.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -887,7 +887,7 @@
         <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" t="n">
         <v>1.64</v>
@@ -896,7 +896,7 @@
         <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T2" t="n">
         <v>1.57</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G3" t="n">
         <v>3.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -1138,40 +1138,40 @@
         <v>2.76</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W3" t="n">
         <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
         <v>50</v>
@@ -1198,16 +1198,16 @@
         <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
         <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="n">
         <v>190</v>
@@ -1219,64 +1219,64 @@
         <v>38</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG3" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>8</v>
       </c>
       <c r="BH3" t="n">
         <v>2.86</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
@@ -1288,53 +1288,53 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV3" t="n">
         <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -1392,19 +1392,19 @@
         <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
         <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.41</v>
+        <v>2.92</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
         <v>2.68</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>1.4</v>
@@ -1900,25 +1900,25 @@
         <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T6" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="U6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V6" t="n">
         <v>1.52</v>
@@ -1942,7 +1942,7 @@
         <v>15</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
@@ -1951,10 +1951,10 @@
         <v>29</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>16</v>
@@ -1975,31 +1975,31 @@
         <v>70</v>
       </c>
       <c r="AN6" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
         <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
@@ -2011,28 +2011,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
         <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BH6" t="n">
         <v>4.2</v>
@@ -2044,13 +2044,13 @@
         <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN6" t="n">
         <v>6</v>
@@ -2062,16 +2062,16 @@
         <v>18.5</v>
       </c>
       <c r="BQ6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT6" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.6</v>
       </c>
       <c r="BU6" t="n">
         <v>4.7</v>
@@ -2080,23 +2080,23 @@
         <v>21</v>
       </c>
       <c r="BW6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA6" t="n">
         <v>6.8</v>
       </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>970</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="H7" t="n">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>1.15</v>
+        <v>2.36</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>2.56</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
         <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FK Ulytau Zhezkazgan</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>Trygg/Lade</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="n">
-        <v>1.29</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.74</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>2.02</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norwegian 2nd Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trygg/Lade</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="R14" t="n">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="U14" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z14" t="n">
         <v>36</v>
       </c>
-      <c r="Y14" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>55</v>
-      </c>
       <c r="AA14" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AK14" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AO14" t="n">
         <v>42</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.75</v>
+        <v>11.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH14" t="n">
         <v>3.95</v>
       </c>
-      <c r="BA14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC14" t="n">
+      <c r="BI14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO14" t="n">
         <v>3.9</v>
       </c>
-      <c r="BD14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.64</v>
+        <v>10.5</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.64</v>
+        <v>11</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -4150,229 +4150,229 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.93</v>
+        <v>1.46</v>
       </c>
       <c r="G15" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="I15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X15" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN15" t="n">
         <v>4.5</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="BO15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP15" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="BQ15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT15" t="n">
         <v>11</v>
       </c>
-      <c r="AO15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>24</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BU15" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,239 +4404,239 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Follo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Norrby IF</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.46</v>
+        <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.53</v>
+        <v>5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6</v>
+        <v>1.66</v>
       </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>1.77</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="T16" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>2.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.86</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y16" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>70</v>
+        <v>970</v>
       </c>
       <c r="AA16" t="n">
-        <v>200</v>
+        <v>970</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AC16" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="AF16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH16" t="n">
         <v>970</v>
       </c>
-      <c r="AG16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>24</v>
-      </c>
       <c r="AI16" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO16" t="n">
         <v>970</v>
       </c>
-      <c r="AK16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>95</v>
-      </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>3.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>21</v>
+        <v>4.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.6</v>
+        <v>2.94</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.2</v>
+        <v>3.65</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV16" t="n">
-        <v>19</v>
+        <v>3.35</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.6</v>
+        <v>3.1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.7</v>
+        <v>3.05</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="BC16" t="n">
-        <v>11.5</v>
+        <v>3.45</v>
       </c>
       <c r="BD16" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -4658,28 +4658,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tobol Kostanay</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Altay</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G17" t="n">
-        <v>1.74</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>2.68</v>
+        <v>1.09</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,19 +4691,19 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="O17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
         <v>1.29</v>
@@ -4715,10 +4715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>2.34</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Norwegian 2nd Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,31 +4912,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Stjordals-Blink</t>
+          <t>Tobol Kostanay</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Junkeren</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4945,22 +4945,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>1.13</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="P18" t="n">
-        <v>2.62</v>
+        <v>1.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="S18" t="n">
-        <v>1.82</v>
+        <v>1.31</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.88</v>
+        <v>2.34</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -5166,175 +5166,175 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Follo</t>
+          <t>Stjordals-Blink</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Junkeren</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I19" t="n">
         <v>4.5</v>
       </c>
-      <c r="G19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.77</v>
-      </c>
       <c r="J19" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="R19" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="S19" t="n">
-        <v>2.24</v>
+        <v>1.88</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>2.28</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1.23</v>
+        <v>1.95</v>
       </c>
       <c r="X19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
         <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.94</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>2.98</v>
       </c>
       <c r="G20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H20" t="n">
         <v>2.5</v>
@@ -5486,31 +5486,31 @@
         <v>11</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
         <v>970</v>
       </c>
       <c r="AA20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
         <v>14.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
         <v>22</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH20" t="n">
         <v>24</v>
@@ -5537,16 +5537,16 @@
         <v>40</v>
       </c>
       <c r="AP20" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT20" t="n">
         <v>8.199999999999999</v>
@@ -5558,37 +5558,37 @@
         <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
         <v>16</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AZ20" t="n">
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH20" t="n">
         <v>3.05</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="G24" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="H24" t="n">
         <v>2.8</v>
       </c>
       <c r="I24" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.42</v>
@@ -6469,7 +6469,7 @@
         <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="O24" t="n">
         <v>1.44</v>
@@ -6484,46 +6484,46 @@
         <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.89</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.87</v>
-      </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W24" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X24" t="n">
         <v>12.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AB24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC24" t="n">
         <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG24" t="n">
         <v>15.5</v>
@@ -6532,13 +6532,13 @@
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ24" t="n">
         <v>55</v>
       </c>
       <c r="AK24" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL24" t="n">
         <v>70</v>
@@ -6547,64 +6547,64 @@
         <v>170</v>
       </c>
       <c r="AN24" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AO24" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BH24" t="n">
         <v>3.05</v>
@@ -6625,16 +6625,16 @@
         <v>2.34</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BP24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BQ24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BR24" t="n">
         <v>44</v>
@@ -6643,22 +6643,22 @@
         <v>2.24</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BW24" t="n">
         <v>2.18</v>
       </c>
       <c r="BX24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY24" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BZ24" t="n">
         <v>42</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -6699,160 +6699,160 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="O25" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>1.35</v>
+        <v>3.85</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
         <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
         <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -6959,10 +6959,10 @@
         <v>2.66</v>
       </c>
       <c r="H26" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J26" t="n">
         <v>3.55</v>
@@ -6971,43 +6971,43 @@
         <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
         <v>1.26</v>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U26" t="n">
         <v>2.26</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W26" t="n">
         <v>1.6</v>
       </c>
       <c r="X26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="n">
         <v>16</v>
@@ -7019,7 +7019,7 @@
         <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC26" t="n">
         <v>9.800000000000001</v>
@@ -7031,7 +7031,7 @@
         <v>38</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="n">
         <v>14</v>
@@ -7049,134 +7049,134 @@
         <v>30</v>
       </c>
       <c r="AL26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM26" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="n">
         <v>21</v>
       </c>
       <c r="AO26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP26" t="n">
         <v>4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AR26" t="n">
         <v>4.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV26" t="n">
         <v>3.75</v>
       </c>
-      <c r="AU26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AW26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX26" t="n">
         <v>4</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AZ26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF26" t="n">
         <v>4</v>
       </c>
-      <c r="BA26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX26" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>3.4</v>
       </c>
       <c r="J27" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K27" t="n">
         <v>4.2</v>
@@ -7246,7 +7246,7 @@
         <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
         <v>1.59</v>
@@ -7315,10 +7315,10 @@
         <v>28</v>
       </c>
       <c r="AP27" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR27" t="n">
         <v>18</v>
@@ -7342,7 +7342,7 @@
         <v>12</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
         <v>11</v>
@@ -7351,13 +7351,13 @@
         <v>3.85</v>
       </c>
       <c r="BB27" t="n">
-        <v>21</v>
+        <v>3.75</v>
       </c>
       <c r="BC27" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BD27" t="n">
-        <v>21</v>
+        <v>3.75</v>
       </c>
       <c r="BE27" t="n">
         <v>3.95</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -7461,157 +7461,157 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.23</v>
+        <v>1.79</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>1.23</v>
+        <v>2.96</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
         <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
         <v>1.03</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7763,7 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
         <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
         <v>1.05</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -9009,22 +9009,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.27</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
         <v>1.29</v>
       </c>
       <c r="P34" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="R34" t="n">
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -9260,25 +9260,25 @@
         <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N35" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O35" t="n">
         <v>1.3</v>
       </c>
       <c r="P35" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="R35" t="n">
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
         <v>1.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R36" t="n">
         <v>1.18</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -9798,7 +9798,7 @@
         <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
         <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10560,7 @@
         <v>1.02</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -10775,34 +10775,34 @@
         <v>1000</v>
       </c>
       <c r="J41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
         <v>1.09</v>
       </c>
-      <c r="K41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N41" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O41" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P41" t="n">
         <v>1.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="R41" t="n">
         <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>1.45</v>
+        <v>3.35</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11035,7 @@
         <v>3.65</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
         <v>1.1</v>
@@ -11179,58 +11179,58 @@
         <v>4.6</v>
       </c>
       <c r="BH42" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO42" t="n">
         <v>3.5</v>
       </c>
-      <c r="BI42" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BJ42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK42" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM42" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BN42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO42" t="n">
-        <v>1.41</v>
-      </c>
       <c r="BP42" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.41</v>
+        <v>5.5</v>
       </c>
       <c r="BR42" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.41</v>
+        <v>5.8</v>
       </c>
       <c r="BT42" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.41</v>
+        <v>2.94</v>
       </c>
       <c r="BV42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.41</v>
+        <v>5</v>
       </c>
       <c r="BX42" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.41</v>
+        <v>5.6</v>
       </c>
       <c r="BZ42" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -11558,13 +11558,13 @@
         <v>1.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="R44" t="n">
         <v>1.12</v>
       </c>
       <c r="S44" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -12308,19 +12308,19 @@
         <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="N47" t="n">
         <v>1.28</v>
       </c>
       <c r="O47" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="P47" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="R47" t="n">
         <v>1.12</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
         <v>4.1</v>
       </c>
       <c r="I49" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>3.1</v>
@@ -12939,7 +12939,7 @@
         <v>5.5</v>
       </c>
       <c r="BB49" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC49" t="n">
         <v>8.4</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>2.04</v>
       </c>
       <c r="G50" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H50" t="n">
         <v>4.1</v>
@@ -13061,13 +13061,13 @@
         <v>4.7</v>
       </c>
       <c r="J50" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K50" t="n">
         <v>3.55</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M50" t="n">
         <v>1.1</v>
@@ -13082,7 +13082,7 @@
         <v>1.67</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R50" t="n">
         <v>1.24</v>
@@ -13100,7 +13100,7 @@
         <v>1.27</v>
       </c>
       <c r="W50" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X50" t="n">
         <v>970</v>
@@ -13115,7 +13115,7 @@
         <v>130</v>
       </c>
       <c r="AB50" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AC50" t="n">
         <v>970</v>
@@ -13163,7 +13163,7 @@
         <v>6.4</v>
       </c>
       <c r="AR50" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AS50" t="n">
         <v>2.26</v>
@@ -13178,7 +13178,7 @@
         <v>7.4</v>
       </c>
       <c r="AW50" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AX50" t="n">
         <v>6.2</v>
@@ -13202,77 +13202,77 @@
         <v>2.2</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BF50" t="n">
         <v>16</v>
       </c>
       <c r="BG50" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="BH50" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI50" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ50" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BN50" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO50" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP50" t="n">
         <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR50" t="n">
         <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BT50" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU50" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV50" t="n">
         <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BZ50" t="n">
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13342,7 @@
         <v>1.32</v>
       </c>
       <c r="S51" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T51" t="n">
         <v>2.28</v>
@@ -13354,7 +13354,7 @@
         <v>1.1</v>
       </c>
       <c r="W51" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X51" t="n">
         <v>16.5</v>
@@ -13384,7 +13384,7 @@
         <v>7.8</v>
       </c>
       <c r="AG51" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH51" t="n">
         <v>32</v>
@@ -13414,13 +13414,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR51" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS51" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT51" t="n">
         <v>6</v>
@@ -13429,10 +13429,10 @@
         <v>9</v>
       </c>
       <c r="AV51" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW51" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX51" t="n">
         <v>6.8</v>
@@ -13441,10 +13441,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ51" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BA51" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB51" t="n">
         <v>10.5</v>
@@ -13453,16 +13453,16 @@
         <v>15.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BE51" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF51" t="n">
         <v>6.6</v>
       </c>
       <c r="BG51" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         <v>2.42</v>
       </c>
       <c r="H52" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I52" t="n">
         <v>4.4</v>
@@ -13572,7 +13572,7 @@
         <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13581,28 +13581,28 @@
         <v>1.11</v>
       </c>
       <c r="N52" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O52" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P52" t="n">
         <v>1.54</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R52" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S52" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T52" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U52" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V52" t="n">
         <v>1.29</v>
@@ -13611,7 +13611,7 @@
         <v>1.7</v>
       </c>
       <c r="X52" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y52" t="n">
         <v>13</v>
@@ -13623,7 +13623,7 @@
         <v>110</v>
       </c>
       <c r="AB52" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC52" t="n">
         <v>8.4</v>
@@ -13665,58 +13665,58 @@
         <v>95</v>
       </c>
       <c r="AP52" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AR52" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS52" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD52" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT52" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB52" t="n">
+      <c r="BE52" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF52" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC52" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG52" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH52" t="n">
         <v>3.35</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
         <v>1.82</v>
       </c>
       <c r="G53" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H53" t="n">
         <v>4.8</v>
@@ -13829,7 +13829,7 @@
         <v>3.95</v>
       </c>
       <c r="L53" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M53" t="n">
         <v>1.07</v>
@@ -13862,7 +13862,7 @@
         <v>1.23</v>
       </c>
       <c r="W53" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X53" t="n">
         <v>14</v>
@@ -13973,68 +13973,68 @@
         <v>8.4</v>
       </c>
       <c r="BH53" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI53" t="n">
-        <v>1.95</v>
+        <v>2.68</v>
       </c>
       <c r="BJ53" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BK53" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>1.95</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN53" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO53" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BP53" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BQ53" t="n">
-        <v>1.76</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR53" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BS53" t="n">
-        <v>1.86</v>
+        <v>7.8</v>
       </c>
       <c r="BT53" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BU53" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BV53" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW53" t="n">
-        <v>1.88</v>
+        <v>8.6</v>
       </c>
       <c r="BX53" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY53" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="BZ53" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="CA53" t="n">
-        <v>1.85</v>
+        <v>7.6</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
         <v>2.06</v>
       </c>
       <c r="H54" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I54" t="n">
         <v>5.1</v>
@@ -14083,7 +14083,7 @@
         <v>3.75</v>
       </c>
       <c r="L54" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M54" t="n">
         <v>1.08</v>
@@ -14185,7 +14185,7 @@
         <v>4.3</v>
       </c>
       <c r="AT54" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="AU54" t="n">
         <v>7</v>
@@ -14230,7 +14230,7 @@
         <v>1000</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BJ54" t="n">
         <v>15</v>
@@ -14242,13 +14242,13 @@
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BN54" t="n">
         <v>6</v>
       </c>
       <c r="BO54" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BP54" t="n">
         <v>20</v>
@@ -14272,13 +14272,13 @@
         <v>1000</v>
       </c>
       <c r="BW54" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY54" t="n">
         <v>1.79</v>
-      </c>
-      <c r="BX54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY54" t="n">
-        <v>1.8</v>
       </c>
       <c r="BZ54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -14319,85 +14319,85 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="G55" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="H55" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J55" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K55" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M55" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N55" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O55" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P55" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R55" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S55" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T55" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U55" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V55" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W55" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="X55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y55" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z55" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AA55" t="n">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="AB55" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF55" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>11</v>
       </c>
       <c r="AG55" t="n">
         <v>12.5</v>
@@ -14406,25 +14406,25 @@
         <v>32</v>
       </c>
       <c r="AI55" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ55" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK55" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL55" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM55" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN55" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO55" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AP55" t="n">
         <v>1.03</v>
@@ -14475,22 +14475,22 @@
         <v>1.03</v>
       </c>
       <c r="BF55" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG55" t="n">
         <v>1.01</v>
       </c>
       <c r="BH55" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI55" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ55" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK55" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
@@ -14499,28 +14499,28 @@
         <v>1.01</v>
       </c>
       <c r="BN55" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO55" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP55" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ55" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR55" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS55" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT55" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU55" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -14576,7 +14576,7 @@
         <v>1.75</v>
       </c>
       <c r="G56" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H56" t="n">
         <v>5.1</v>
@@ -14585,7 +14585,7 @@
         <v>6.8</v>
       </c>
       <c r="J56" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K56" t="n">
         <v>3.75</v>
@@ -14597,19 +14597,19 @@
         <v>1.1</v>
       </c>
       <c r="N56" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
         <v>1.46</v>
       </c>
       <c r="P56" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q56" t="n">
         <v>2.22</v>
       </c>
       <c r="R56" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S56" t="n">
         <v>4.3</v>
@@ -14624,7 +14624,7 @@
         <v>1.19</v>
       </c>
       <c r="W56" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X56" t="n">
         <v>970</v>
@@ -14666,16 +14666,16 @@
         <v>23</v>
       </c>
       <c r="AK56" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL56" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM56" t="n">
         <v>1000</v>
       </c>
       <c r="AN56" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO56" t="n">
         <v>1000</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14839,7 @@
         <v>5.4</v>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K57" t="n">
         <v>3.55</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -872,7 +872,7 @@
         <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
@@ -893,7 +893,7 @@
         <v>1.64</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
         <v>2.54</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>3.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
         <v>2.48</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
         <v>3.35</v>
@@ -1201,13 +1201,13 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK3" t="n">
         <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
         <v>190</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>4.4</v>
       </c>
       <c r="G5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H5" t="n">
         <v>1.55</v>
@@ -1646,7 +1646,7 @@
         <v>2.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
         <v>1.5</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.92</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -1876,25 +1876,25 @@
         <v>2.52</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
         <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J6" t="n">
         <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
         <v>4.7</v>
@@ -1924,7 +1924,7 @@
         <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
         <v>25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -2145,13 +2145,13 @@
         <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
@@ -2163,7 +2163,7 @@
         <v>1.54</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S7" t="n">
         <v>2.36</v>
@@ -2193,25 +2193,25 @@
         <v>50</v>
       </c>
       <c r="AB7" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
         <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
         <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
         <v>38</v>
@@ -2226,13 +2226,13 @@
         <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AO7" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AP7" t="n">
         <v>1.01</v>
@@ -2250,7 +2250,7 @@
         <v>11.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
         <v>9.800000000000001</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -2381,100 +2381,100 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>1.29</v>
+        <v>2.52</v>
       </c>
       <c r="O8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.36</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2483,52 +2483,52 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
         <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
         <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
         <v>1.03</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -2635,154 +2635,154 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>1.08</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.49</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
         <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
         <v>1.03</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -2889,220 +2889,220 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.92</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.3</v>
+        <v>1.86</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
         <v>2.4</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -3143,112 +3143,112 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.02</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP11" t="n">
         <v>1.03</v>
@@ -3299,7 +3299,7 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -3397,157 +3397,157 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="H12" t="n">
-        <v>1.09</v>
+        <v>2.94</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>1.35</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
         <v>1.03</v>
@@ -3562,7 +3562,7 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -3651,46 +3651,46 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H13" t="n">
         <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q13" t="n">
         <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S13" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T13" t="n">
         <v>1.57</v>
@@ -3699,10 +3699,10 @@
         <v>2.44</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="X13" t="n">
         <v>36</v>
@@ -3714,7 +3714,7 @@
         <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
@@ -3726,7 +3726,7 @@
         <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF13" t="n">
         <v>970</v>
@@ -3741,7 +3741,7 @@
         <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="n">
         <v>970</v>
@@ -3753,10 +3753,10 @@
         <v>75</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AP13" t="n">
         <v>4.5</v>
@@ -3771,7 +3771,7 @@
         <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AU13" t="n">
         <v>3.8</v>
@@ -3786,7 +3786,7 @@
         <v>3.9</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="AZ13" t="n">
         <v>4.1</v>
@@ -3807,74 +3807,74 @@
         <v>4.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH13" t="n">
         <v>5.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="BN13" t="n">
         <v>5</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G14" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
         <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
@@ -3941,7 +3941,7 @@
         <v>1.72</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S14" t="n">
         <v>2.8</v>
@@ -3956,7 +3956,7 @@
         <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X14" t="n">
         <v>23</v>
@@ -3971,10 +3971,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>18.5</v>
@@ -3998,7 +3998,7 @@
         <v>26</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
@@ -4013,16 +4013,16 @@
         <v>42</v>
       </c>
       <c r="AP14" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
         <v>9.800000000000001</v>
@@ -4076,7 +4076,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         <v>4.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP14" t="n">
         <v>13</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         <v>5.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
@@ -4192,7 +4192,7 @@
         <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
         <v>1.58</v>
@@ -4285,7 +4285,7 @@
         <v>9.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="AW15" t="n">
         <v>7</v>
@@ -4315,13 +4315,13 @@
         <v>7</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG15" t="n">
         <v>6.8</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI15" t="n">
         <v>3.6</v>
@@ -4330,13 +4330,13 @@
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN15" t="n">
         <v>4.5</v>
@@ -4348,31 +4348,31 @@
         <v>9.4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BT15" t="n">
         <v>11</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -4416,58 +4416,58 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
         <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -4479,7 +4479,7 @@
         <v>970</v>
       </c>
       <c r="AB16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC16" t="n">
         <v>970</v>
@@ -4491,7 +4491,7 @@
         <v>970</v>
       </c>
       <c r="AF16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AG16" t="n">
         <v>20</v>
@@ -4515,64 +4515,64 @@
         <v>75</v>
       </c>
       <c r="AN16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO16" t="n">
         <v>970</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BD16" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE16" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -4667,103 +4667,103 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.09</v>
+        <v>4.8</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="H17" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="J17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.29</v>
       </c>
-      <c r="K17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -4772,43 +4772,43 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
         <v>1.03</v>
@@ -4829,10 +4829,10 @@
         <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
@@ -4865,7 +4865,7 @@
         <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -4921,118 +4921,118 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="G18" t="n">
         <v>1.74</v>
       </c>
       <c r="H18" t="n">
-        <v>2.68</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>1.13</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P18" t="n">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>1.31</v>
+        <v>2.76</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
         <v>2.34</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
         <v>1.03</v>
@@ -5041,37 +5041,37 @@
         <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
         <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
         <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
         <v>1.03</v>
@@ -5086,7 +5086,7 @@
         <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="H19" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="I19" t="n">
         <v>4.5</v>
@@ -5190,7 +5190,7 @@
         <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,190 +5199,190 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P19" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>1.37</v>
       </c>
       <c r="R19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S19" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AV19" t="n">
         <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
         <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
         <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
         <v>3.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
         <v>1.11</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="I22" t="n">
         <v>2.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>1.89</v>
       </c>
       <c r="K22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="O22" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="P22" t="n">
         <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G24" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="H24" t="n">
         <v>2.8</v>
@@ -6457,7 +6457,7 @@
         <v>2.88</v>
       </c>
       <c r="J24" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
         <v>3.5</v>
@@ -6484,7 +6484,7 @@
         <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
         <v>1.9</v>
@@ -6610,7 +6610,7 @@
         <v>3.05</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ24" t="n">
         <v>11</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G25" t="n">
         <v>2.16</v>
@@ -6717,7 +6717,7 @@
         <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
@@ -6741,10 +6741,10 @@
         <v>3.85</v>
       </c>
       <c r="T25" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="U25" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="V25" t="n">
         <v>1.27</v>
@@ -6753,10 +6753,10 @@
         <v>1.86</v>
       </c>
       <c r="X25" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y25" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z25" t="n">
         <v>34</v>
@@ -6768,22 +6768,22 @@
         <v>8.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE25" t="n">
         <v>70</v>
       </c>
       <c r="AF25" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>80</v>
@@ -6801,7 +6801,7 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AO25" t="n">
         <v>85</v>
@@ -6819,7 +6819,7 @@
         <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU25" t="n">
         <v>6.2</v>
@@ -6861,58 +6861,58 @@
         <v>1.01</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -6977,28 +6977,28 @@
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
         <v>1.26</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
         <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="T26" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V26" t="n">
         <v>1.44</v>
@@ -7118,7 +7118,7 @@
         <v>3.85</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="BJ26" t="n">
         <v>9.4</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
         <v>4.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P27" t="n">
         <v>2.34</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="H28" t="n">
         <v>2.1</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J28" t="n">
         <v>3.5</v>
@@ -7479,13 +7479,13 @@
         <v>4.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
         <v>1.26</v>
@@ -7509,10 +7509,10 @@
         <v>2.24</v>
       </c>
       <c r="V28" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X28" t="n">
         <v>20</v>
@@ -7569,58 +7569,58 @@
         <v>970</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K29" t="n">
         <v>4.5</v>
@@ -7739,19 +7739,19 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="O29" t="n">
         <v>1.16</v>
       </c>
       <c r="P29" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
         <v>1.16</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
         <v>1.16</v>
@@ -7763,7 +7763,7 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -8259,10 +8259,10 @@
         <v>1.08</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="S31" t="n">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -8507,16 +8507,16 @@
         <v>1.08</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q32" t="n">
         <v>1.08</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="S32" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -8991,13 +8991,13 @@
         <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I34" t="n">
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
@@ -9009,22 +9009,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>1.32</v>
       </c>
       <c r="O34" t="n">
         <v>1.29</v>
       </c>
       <c r="P34" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="R34" t="n">
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>2.66</v>
+        <v>1.29</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9036,7 +9036,7 @@
         <v>1.09</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -9263,22 +9263,22 @@
         <v>1.05</v>
       </c>
       <c r="N35" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
         <v>1.3</v>
       </c>
       <c r="P35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q35" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.8</v>
       </c>
       <c r="R35" t="n">
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>2.72</v>
+        <v>1.3</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -9798,7 +9798,7 @@
         <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
         <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="G41" t="n">
         <v>1000</v>
@@ -10775,7 +10775,7 @@
         <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -10784,25 +10784,25 @@
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N41" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O41" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="P41" t="n">
         <v>1.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="R41" t="n">
         <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>3.35</v>
+        <v>1.44</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -10811,10 +10811,10 @@
         <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -11041,13 +11041,13 @@
         <v>1.1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O42" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P42" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="Q42" t="n">
         <v>2.32</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -11779,13 +11779,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G45" t="n">
         <v>1000</v>
       </c>
       <c r="H45" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
         <v>1000</v>
       </c>
       <c r="J46" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K46" t="n">
         <v>1000</v>
@@ -12057,16 +12057,16 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="O46" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P46" t="n">
         <v>1.27</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="R46" t="n">
         <v>1.12</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -12287,13 +12287,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G47" t="n">
         <v>1000</v>
       </c>
       <c r="H47" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I47" t="n">
         <v>1000</v>
@@ -12308,13 +12308,13 @@
         <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="O47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P47" t="n">
         <v>1.25</v>
@@ -12326,7 +12326,7 @@
         <v>1.12</v>
       </c>
       <c r="S47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G49" t="n">
         <v>2.24</v>
@@ -12804,13 +12804,13 @@
         <v>4.1</v>
       </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J49" t="n">
         <v>3.1</v>
       </c>
       <c r="K49" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
         <v>1.67</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R50" t="n">
         <v>1.24</v>
@@ -13169,7 +13169,7 @@
         <v>2.26</v>
       </c>
       <c r="AT50" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU50" t="n">
         <v>4.8</v>
@@ -13181,7 +13181,7 @@
         <v>2.3</v>
       </c>
       <c r="AX50" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AY50" t="n">
         <v>5.9</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         <v>2.42</v>
       </c>
       <c r="H52" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I52" t="n">
         <v>4.4</v>
@@ -13572,7 +13572,7 @@
         <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -13814,16 +13814,16 @@
         <v>1.82</v>
       </c>
       <c r="G53" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H53" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I53" t="n">
         <v>5.3</v>
       </c>
       <c r="J53" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K53" t="n">
         <v>3.95</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -14083,10 +14083,10 @@
         <v>3.75</v>
       </c>
       <c r="L54" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M54" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N54" t="n">
         <v>3.15</v>
@@ -14227,68 +14227,68 @@
         <v>4.3</v>
       </c>
       <c r="BH54" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.83</v>
+        <v>2.62</v>
       </c>
       <c r="BJ54" t="n">
         <v>15</v>
       </c>
       <c r="BK54" t="n">
-        <v>1.64</v>
+        <v>6.8</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="BN54" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BO54" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="BP54" t="n">
         <v>20</v>
       </c>
       <c r="BQ54" t="n">
-        <v>1.68</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR54" t="n">
         <v>1000</v>
       </c>
       <c r="BS54" t="n">
-        <v>1.76</v>
+        <v>7.8</v>
       </c>
       <c r="BT54" t="n">
         <v>10.5</v>
       </c>
       <c r="BU54" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY54" t="n">
         <v>5.2</v>
       </c>
-      <c r="BV54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW54" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BX54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY54" t="n">
-        <v>1.79</v>
-      </c>
       <c r="BZ54" t="n">
         <v>1000</v>
       </c>
       <c r="CA54" t="n">
-        <v>1.76</v>
+        <v>10.5</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -14573,22 +14573,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G56" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H56" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I56" t="n">
         <v>6.8</v>
       </c>
       <c r="J56" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K56" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -14597,7 +14597,7 @@
         <v>1.1</v>
       </c>
       <c r="N56" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="O56" t="n">
         <v>1.46</v>
@@ -14606,7 +14606,7 @@
         <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R56" t="n">
         <v>1.23</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -14827,43 +14827,43 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="G57" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H57" t="n">
         <v>4.5</v>
       </c>
       <c r="I57" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J57" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K57" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L57" t="n">
         <v>1.01</v>
       </c>
       <c r="M57" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N57" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="P57" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="R57" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S57" t="n">
         <v>4.7</v>
@@ -14875,10 +14875,10 @@
         <v>1.71</v>
       </c>
       <c r="V57" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W57" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X57" t="n">
         <v>10.5</v>
@@ -14905,10 +14905,10 @@
         <v>110</v>
       </c>
       <c r="AF57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG57" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>14</v>
       </c>
       <c r="AH57" t="n">
         <v>32</v>
@@ -14917,10 +14917,10 @@
         <v>130</v>
       </c>
       <c r="AJ57" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK57" t="n">
         <v>32</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>36</v>
       </c>
       <c r="AL57" t="n">
         <v>70</v>
@@ -14929,34 +14929,34 @@
         <v>250</v>
       </c>
       <c r="AN57" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO57" t="n">
         <v>180</v>
       </c>
       <c r="AP57" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="AQ57" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="AR57" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AS57" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT57" t="n">
         <v>5</v>
       </c>
       <c r="AU57" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AV57" t="n">
         <v>15</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX57" t="n">
         <v>8</v>
@@ -14965,28 +14965,28 @@
         <v>8.4</v>
       </c>
       <c r="AZ57" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BA57" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB57" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BC57" t="n">
         <v>20</v>
       </c>
       <c r="BD57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF57" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE57" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BG57" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH57" t="n">
         <v>3.2</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G2" t="n">
         <v>2.8</v>
@@ -869,10 +869,10 @@
         <v>2.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>1.31</v>
@@ -881,22 +881,22 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
         <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T2" t="n">
         <v>1.6</v>
@@ -908,7 +908,7 @@
         <v>1.59</v>
       </c>
       <c r="W2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -917,25 +917,25 @@
         <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
         <v>46</v>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>30</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
@@ -947,7 +947,7 @@
         <v>38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AK2" t="n">
         <v>29</v>
@@ -956,16 +956,16 @@
         <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>12.5</v>
@@ -989,10 +989,10 @@
         <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>13.5</v>
@@ -1013,13 +1013,13 @@
         <v>42</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG2" t="n">
         <v>12.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI2" t="n">
         <v>3.35</v>
@@ -1028,16 +1028,16 @@
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO2" t="n">
         <v>5.3</v>
@@ -1046,13 +1046,13 @@
         <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
         <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1064,23 +1064,23 @@
         <v>18</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
         <v>26</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>18.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G3" t="n">
         <v>3.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -1135,13 +1135,13 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O3" t="n">
         <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
         <v>2.44</v>
@@ -1159,10 +1159,10 @@
         <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X3" t="n">
         <v>9.6</v>
@@ -1174,7 +1174,7 @@
         <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AB3" t="n">
         <v>13</v>
@@ -1192,49 +1192,49 @@
         <v>36</v>
       </c>
       <c r="AG3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH3" t="n">
         <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
         <v>95</v>
       </c>
       <c r="AK3" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM3" t="n">
         <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO3" t="n">
         <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
         <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY3" t="n">
         <v>11.5</v>
@@ -1255,16 +1255,16 @@
         <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
         <v>6.8</v>
@@ -1288,13 +1288,13 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1306,19 +1306,19 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV3" t="n">
         <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1407,10 +1407,10 @@
         <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -1622,88 +1622,88 @@
         <v>4.8</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="I5" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="J5" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q5" t="n">
         <v>2.26</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
         <v>1.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
       </c>
       <c r="AE5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG5" t="n">
         <v>32</v>
       </c>
-      <c r="AF5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>28</v>
-      </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
         <v>70</v>
@@ -1712,10 +1712,10 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AL5" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1724,40 +1724,40 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AU5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AV5" t="n">
         <v>3.3</v>
       </c>
       <c r="AW5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY5" t="n">
         <v>3.85</v>
       </c>
-      <c r="AX5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BA5" t="n">
         <v>4.1</v>
@@ -1778,61 +1778,61 @@
         <v>4.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>1.15</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.29</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I6" t="n">
         <v>2.82</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
         <v>3.9</v>
@@ -1903,16 +1903,16 @@
         <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
         <v>1.67</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
         <v>1.59</v>
@@ -1924,22 +1924,22 @@
         <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
         <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC6" t="n">
         <v>9.199999999999999</v>
@@ -1951,28 +1951,28 @@
         <v>40</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="n">
         <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="AN6" t="n">
         <v>17</v>
@@ -2008,13 +2008,13 @@
         <v>17.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BB6" t="n">
         <v>26</v>
@@ -2023,7 +2023,7 @@
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE6" t="n">
         <v>30</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
         <v>4.5</v>
@@ -2148,7 +2148,7 @@
         <v>1.24</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
         <v>5.2</v>
@@ -2256,10 +2256,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX7" t="n">
         <v>4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.95</v>
       </c>
       <c r="AY7" t="n">
         <v>9.199999999999999</v>
@@ -2274,16 +2274,16 @@
         <v>3.95</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
         <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.54</v>
@@ -2489,7 +2489,7 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AQ8" t="n">
         <v>3.95</v>
@@ -2498,22 +2498,22 @@
         <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="AT8" t="n">
         <v>3.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AW8" t="n">
         <v>5.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY8" t="n">
         <v>4.1</v>
@@ -2522,7 +2522,7 @@
         <v>4.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="BB8" t="n">
         <v>4.9</v>
@@ -2531,16 +2531,16 @@
         <v>4.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="BF8" t="n">
         <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
         <v>1.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V9" t="n">
         <v>1.28</v>
@@ -2704,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
         <v>970</v>
@@ -2743,16 +2743,16 @@
         <v>90</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
         <v>3.45</v>
@@ -2761,40 +2761,40 @@
         <v>3.2</v>
       </c>
       <c r="AV9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX9" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AY9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC9" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -2892,16 +2892,16 @@
         <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="H10" t="n">
         <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
@@ -2919,16 +2919,16 @@
         <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
         <v>1.98</v>
@@ -2940,7 +2940,7 @@
         <v>1.15</v>
       </c>
       <c r="W10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="X10" t="n">
         <v>15</v>
@@ -3006,46 +3006,46 @@
         <v>4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="AU10" t="n">
         <v>3.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW10" t="n">
         <v>4.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AY10" t="n">
         <v>3.25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BA10" t="n">
         <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BD10" t="n">
         <v>4</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BG10" t="n">
         <v>4.2</v>
@@ -3054,7 +3054,7 @@
         <v>3.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BJ10" t="n">
         <v>11.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.45</v>
@@ -3167,7 +3167,7 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
         <v>1.49</v>
@@ -3185,13 +3185,13 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
         <v>1.83</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -3397,40 +3397,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="H12" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.05</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.98</v>
       </c>
       <c r="K12" t="n">
         <v>3.45</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
         <v>1.23</v>
@@ -3439,16 +3439,16 @@
         <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="X12" t="n">
         <v>12.5</v>
@@ -3460,10 +3460,10 @@
         <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
         <v>8.6</v>
@@ -3472,13 +3472,13 @@
         <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -3487,10 +3487,10 @@
         <v>70</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AK12" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
         <v>75</v>
@@ -3499,128 +3499,128 @@
         <v>170</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AO12" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR12" t="n">
         <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AU12" t="n">
         <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.1</v>
+        <v>26</v>
       </c>
       <c r="AX12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BC12" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="BH12" t="n">
         <v>2.98</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.36</v>
+        <v>10.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.18</v>
+        <v>7.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.26</v>
+        <v>9</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ12" t="n">
         <v>42</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.26</v>
+        <v>9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H13" t="n">
         <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
         <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.41</v>
@@ -3675,7 +3675,7 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.33</v>
@@ -3684,7 +3684,7 @@
         <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
         <v>1.3</v>
@@ -3693,13 +3693,13 @@
         <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
         <v>1.66</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -3905,85 +3905,85 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G14" t="n">
         <v>1.55</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.67</v>
-      </c>
       <c r="H14" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P14" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="R14" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="S14" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="T14" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V14" t="n">
         <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="X14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Z14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA14" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AB14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC14" t="n">
         <v>15</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AE14" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG14" t="n">
         <v>970</v>
@@ -3992,13 +3992,13 @@
         <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AL14" t="n">
         <v>30</v>
@@ -4007,128 +4007,128 @@
         <v>80</v>
       </c>
       <c r="AN14" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AQ14" t="n">
         <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AV14" t="n">
         <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BD14" t="n">
         <v>18</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="BG14" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN14" t="n">
         <v>4.8</v>
       </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BO14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS14" t="n">
         <v>6.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G15" t="n">
         <v>1.98</v>
@@ -4189,7 +4189,7 @@
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
         <v>1.72</v>
@@ -4201,7 +4201,7 @@
         <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U15" t="n">
         <v>2.4</v>
@@ -4261,10 +4261,10 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP15" t="n">
         <v>17</v>
@@ -4336,13 +4336,13 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN15" t="n">
         <v>4.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP15" t="n">
         <v>13</v>
@@ -4354,10 +4354,10 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU15" t="n">
         <v>6</v>
@@ -4366,13 +4366,13 @@
         <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX15" t="n">
         <v>38</v>
       </c>
       <c r="BY15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G16" t="n">
         <v>1.53</v>
@@ -4428,16 +4428,16 @@
         <v>4.8</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.24</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
@@ -4446,13 +4446,13 @@
         <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R16" t="n">
         <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
         <v>1.71</v>
@@ -4491,7 +4491,7 @@
         <v>100</v>
       </c>
       <c r="AF16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
         <v>10.5</v>
@@ -4515,7 +4515,7 @@
         <v>110</v>
       </c>
       <c r="AN16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO16" t="n">
         <v>90</v>
@@ -4524,13 +4524,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
         <v>9.199999999999999</v>
@@ -4539,10 +4539,10 @@
         <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX16" t="n">
         <v>8.199999999999999</v>
@@ -4554,7 +4554,7 @@
         <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB16" t="n">
         <v>11</v>
@@ -4566,19 +4566,19 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF16" t="n">
         <v>5.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH16" t="n">
         <v>4.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4596,13 +4596,13 @@
         <v>4.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BP16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4626,7 +4626,7 @@
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4688,7 @@
         <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
         <v>5.3</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G18" t="n">
         <v>6.2</v>
@@ -4930,7 +4930,7 @@
         <v>1.72</v>
       </c>
       <c r="I18" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J18" t="n">
         <v>3.55</v>
@@ -4951,7 +4951,7 @@
         <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
         <v>2.04</v>
@@ -4969,7 +4969,7 @@
         <v>1.89</v>
       </c>
       <c r="V18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W18" t="n">
         <v>1.19</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>1.74</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I19" t="n">
         <v>7.4</v>
@@ -5190,10 +5190,10 @@
         <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -5253,7 +5253,7 @@
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
         <v>970</v>
@@ -5277,22 +5277,22 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AR19" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.18</v>
+        <v>3.5</v>
       </c>
       <c r="AT19" t="n">
         <v>6.6</v>
@@ -5301,40 +5301,40 @@
         <v>7.4</v>
       </c>
       <c r="AV19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD19" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE19" t="n">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
         <v>1.18</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
         <v>7.2</v>
@@ -5519,7 +5519,7 @@
         <v>50</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK20" t="n">
         <v>970</v>
@@ -5537,28 +5537,28 @@
         <v>34</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.2</v>
+        <v>2.96</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.94</v>
+        <v>2.48</v>
       </c>
       <c r="AX20" t="n">
         <v>10.5</v>
@@ -5570,7 +5570,7 @@
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BB20" t="n">
         <v>12</v>
@@ -5582,19 +5582,19 @@
         <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
         <v>4.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
         <v>1.59</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R21" t="n">
         <v>1.22</v>
@@ -5725,7 +5725,7 @@
         <v>4.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
         <v>1.83</v>
@@ -5812,7 +5812,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX21" t="n">
         <v>16</v>
@@ -5827,13 +5827,13 @@
         <v>4.9</v>
       </c>
       <c r="BB21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC21" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC21" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE21" t="n">
         <v>5.1</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H22" t="n">
         <v>3.45</v>
@@ -5955,34 +5955,34 @@
         <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="U22" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V22" t="n">
         <v>1.33</v>
@@ -6000,7 +6000,7 @@
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB22" t="n">
         <v>11.5</v>
@@ -6012,7 +6012,7 @@
         <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF22" t="n">
         <v>970</v>
@@ -6024,13 +6024,13 @@
         <v>970</v>
       </c>
       <c r="AI22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
         <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
         <v>40</v>
@@ -6042,85 +6042,85 @@
         <v>970</v>
       </c>
       <c r="AO22" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP22" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX22" t="n">
-        <v>10.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.81</v>
+        <v>1.41</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
@@ -6132,7 +6132,7 @@
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BT22" t="n">
         <v>7.4</v>
@@ -6144,13 +6144,13 @@
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H23" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I23" t="n">
         <v>2.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
         <v>3.8</v>
@@ -6224,7 +6224,7 @@
         <v>1.77</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R23" t="n">
         <v>1.29</v>
@@ -6251,10 +6251,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB23" t="n">
         <v>15</v>
@@ -6278,7 +6278,7 @@
         <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ23" t="n">
         <v>120</v>
@@ -6287,7 +6287,7 @@
         <v>70</v>
       </c>
       <c r="AL23" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM23" t="n">
         <v>150</v>
@@ -6299,7 +6299,7 @@
         <v>23</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ23" t="n">
         <v>7</v>
@@ -6311,7 +6311,7 @@
         <v>6.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU23" t="n">
         <v>4.1</v>
@@ -6320,34 +6320,34 @@
         <v>4.7</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF23" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>7.6</v>
       </c>
       <c r="BG23" t="n">
         <v>13.5</v>
@@ -6356,7 +6356,7 @@
         <v>3.25</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6368,7 +6368,7 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="BN23" t="n">
         <v>7.6</v>
@@ -6380,7 +6380,7 @@
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
@@ -6410,11 +6410,11 @@
         <v>32</v>
       </c>
       <c r="CA23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I24" t="n">
         <v>4.1</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G25" t="n">
         <v>2.22</v>
@@ -6771,7 +6771,7 @@
         <v>9</v>
       </c>
       <c r="AD25" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
         <v>70</v>
@@ -6795,7 +6795,7 @@
         <v>28</v>
       </c>
       <c r="AL25" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -6813,10 +6813,10 @@
         <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT25" t="n">
         <v>7</v>
@@ -6828,10 +6828,10 @@
         <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY25" t="n">
         <v>8.199999999999999</v>
@@ -6840,25 +6840,25 @@
         <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB25" t="n">
         <v>19</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF25" t="n">
         <v>14</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH25" t="n">
         <v>3.25</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         <v>3.9</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
         <v>4.2</v>
@@ -6983,7 +6983,7 @@
         <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
         <v>1.74</v>
@@ -7004,7 +7004,7 @@
         <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X26" t="n">
         <v>21</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
         <v>2.36</v>
       </c>
       <c r="H27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I27" t="n">
         <v>3.4</v>
@@ -7240,10 +7240,10 @@
         <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S27" t="n">
         <v>2.6</v>
@@ -7258,7 +7258,7 @@
         <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X27" t="n">
         <v>27</v>
@@ -7300,7 +7300,7 @@
         <v>36</v>
       </c>
       <c r="AK27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
         <v>36</v>
@@ -7309,7 +7309,7 @@
         <v>75</v>
       </c>
       <c r="AN27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO27" t="n">
         <v>28</v>
@@ -7324,7 +7324,7 @@
         <v>18</v>
       </c>
       <c r="AS27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT27" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -7348,19 +7348,19 @@
         <v>11</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BC27" t="n">
         <v>19</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF27" t="n">
         <v>9.4</v>
@@ -7372,19 +7372,19 @@
         <v>4.2</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ27" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN27" t="n">
         <v>5.5</v>
@@ -7393,7 +7393,7 @@
         <v>4.2</v>
       </c>
       <c r="BP27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ27" t="n">
         <v>7.6</v>
@@ -7402,7 +7402,7 @@
         <v>24</v>
       </c>
       <c r="BS27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT27" t="n">
         <v>6.8</v>
@@ -7414,23 +7414,23 @@
         <v>23</v>
       </c>
       <c r="BW27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX27" t="n">
         <v>29</v>
       </c>
       <c r="BY27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ27" t="n">
         <v>17.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
         <v>2.88</v>
       </c>
       <c r="O28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
@@ -7572,55 +7572,55 @@
         <v>7.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA28" t="n">
         <v>4.1</v>
       </c>
       <c r="BB28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC28" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BD28" t="n">
         <v>4.1</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH28" t="n">
         <v>3.05</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -7724,10 +7724,10 @@
         <v>2.16</v>
       </c>
       <c r="I29" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
@@ -7745,7 +7745,7 @@
         <v>1.27</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
         <v>1.81</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>3.7</v>
       </c>
       <c r="H30" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I30" t="n">
         <v>3.1</v>
@@ -7984,34 +7984,34 @@
         <v>2.62</v>
       </c>
       <c r="K30" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="M30" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N30" t="n">
         <v>2.12</v>
       </c>
       <c r="O30" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="P30" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
         <v>1.12</v>
       </c>
       <c r="S30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
         <v>1.6</v>
@@ -8020,13 +8020,13 @@
         <v>1.48</v>
       </c>
       <c r="W30" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y30" t="n">
         <v>7.4</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>8.4</v>
       </c>
       <c r="Z30" t="n">
         <v>970</v>
@@ -8083,10 +8083,10 @@
         <v>5.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT30" t="n">
         <v>6.2</v>
@@ -8095,46 +8095,46 @@
         <v>5.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB30" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG30" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BH30" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
         <v>4.6</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>4.4</v>
@@ -8268,7 +8268,7 @@
         <v>1.67</v>
       </c>
       <c r="U31" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V31" t="n">
         <v>1.25</v>
@@ -8292,7 +8292,7 @@
         <v>11.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD31" t="n">
         <v>23</v>
@@ -8334,25 +8334,25 @@
         <v>18</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AR31" t="n">
         <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT31" t="n">
         <v>9</v>
       </c>
       <c r="AU31" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV31" t="n">
         <v>13.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX31" t="n">
         <v>8.199999999999999</v>
@@ -8361,7 +8361,7 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BA31" t="n">
         <v>26</v>
@@ -8376,13 +8376,13 @@
         <v>17.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF31" t="n">
         <v>7.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH31" t="n">
         <v>4.3</v>
@@ -8394,7 +8394,7 @@
         <v>9.6</v>
       </c>
       <c r="BK31" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
@@ -8406,25 +8406,25 @@
         <v>4.8</v>
       </c>
       <c r="BO31" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BP31" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="BT31" t="n">
         <v>9</v>
       </c>
       <c r="BU31" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G32" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H32" t="n">
         <v>3.25</v>
@@ -8495,19 +8495,19 @@
         <v>3.35</v>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="M32" t="n">
         <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O32" t="n">
         <v>1.52</v>
       </c>
       <c r="P32" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q32" t="n">
         <v>2.54</v>
@@ -8528,7 +8528,7 @@
         <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X32" t="n">
         <v>10.5</v>
@@ -8591,22 +8591,22 @@
         <v>8.4</v>
       </c>
       <c r="AR32" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT32" t="n">
         <v>6.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX32" t="n">
         <v>12.5</v>
@@ -8621,22 +8621,22 @@
         <v>5.9</v>
       </c>
       <c r="BB32" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC32" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE32" t="n">
         <v>6.2</v>
       </c>
       <c r="BF32" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH32" t="n">
         <v>2.8</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -8731,64 +8731,64 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G33" t="n">
         <v>2.04</v>
       </c>
       <c r="H33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J33" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="M33" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N33" t="n">
         <v>2.28</v>
       </c>
       <c r="O33" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="P33" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
         <v>1.14</v>
       </c>
       <c r="S33" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="U33" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V33" t="n">
         <v>1.17</v>
       </c>
       <c r="W33" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X33" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z33" t="n">
         <v>55</v>
@@ -8797,7 +8797,7 @@
         <v>260</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AC33" t="n">
         <v>10.5</v>
@@ -8809,22 +8809,22 @@
         <v>170</v>
       </c>
       <c r="AF33" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH33" t="n">
         <v>42</v>
       </c>
       <c r="AI33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ33" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AK33" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AL33" t="n">
         <v>95</v>
@@ -8833,22 +8833,22 @@
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT33" t="n">
         <v>4.7</v>
@@ -8857,10 +8857,10 @@
         <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AX33" t="n">
         <v>7.4</v>
@@ -8869,46 +8869,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB33" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="BC33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF33" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BG33" t="n">
-        <v>230</v>
+        <v>8</v>
       </c>
       <c r="BH33" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ33" t="n">
         <v>14.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BN33" t="n">
         <v>4.4</v>
@@ -8917,44 +8917,44 @@
         <v>3.4</v>
       </c>
       <c r="BP33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BQ33" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="BT33" t="n">
         <v>9.6</v>
       </c>
       <c r="BU33" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>40</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
         <v>2.12</v>
       </c>
       <c r="G34" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H34" t="n">
         <v>2.64</v>
@@ -9015,7 +9015,7 @@
         <v>1.12</v>
       </c>
       <c r="P34" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="Q34" t="n">
         <v>1.36</v>
@@ -9033,7 +9033,7 @@
         <v>2.52</v>
       </c>
       <c r="V34" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W34" t="n">
         <v>1.64</v>
@@ -9048,7 +9048,7 @@
         <v>36</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB34" t="n">
         <v>25</v>
@@ -9084,16 +9084,16 @@
         <v>34</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="AQ34" t="n">
         <v>14</v>
@@ -9102,7 +9102,7 @@
         <v>17.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AT34" t="n">
         <v>12.5</v>
@@ -9138,13 +9138,13 @@
         <v>16.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BH34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G35" t="n">
         <v>4.5</v>
@@ -9248,49 +9248,49 @@
         <v>1.76</v>
       </c>
       <c r="I35" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="J35" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P35" t="n">
         <v>3.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R35" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S35" t="n">
         <v>1.89</v>
       </c>
       <c r="T35" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="V35" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X35" t="n">
         <v>48</v>
@@ -9320,7 +9320,7 @@
         <v>50</v>
       </c>
       <c r="AG35" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH35" t="n">
         <v>17.5</v>
@@ -9344,10 +9344,10 @@
         <v>24</v>
       </c>
       <c r="AO35" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AQ35" t="n">
         <v>14.5</v>
@@ -9359,19 +9359,19 @@
         <v>17</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU35" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW35" t="n">
         <v>12.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY35" t="n">
         <v>14.5</v>
@@ -9383,86 +9383,86 @@
         <v>16</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF35" t="n">
         <v>16</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN35" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP35" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR35" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT35" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV35" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX35" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -9493,19 +9493,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G36" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H36" t="n">
         <v>2.78</v>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J36" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K36" t="n">
         <v>5</v>
@@ -9532,7 +9532,7 @@
         <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="T36" t="n">
         <v>1.36</v>
@@ -9541,10 +9541,10 @@
         <v>3.25</v>
       </c>
       <c r="V36" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W36" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X36" t="n">
         <v>55</v>
@@ -9553,25 +9553,25 @@
         <v>32</v>
       </c>
       <c r="Z36" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA36" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB36" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AC36" t="n">
         <v>15</v>
       </c>
       <c r="AD36" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE36" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF36" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG36" t="n">
         <v>14</v>
@@ -9586,7 +9586,7 @@
         <v>34</v>
       </c>
       <c r="AK36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL36" t="n">
         <v>24</v>
@@ -9595,19 +9595,19 @@
         <v>42</v>
       </c>
       <c r="AN36" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO36" t="n">
         <v>13.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ36" t="n">
         <v>21</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS36" t="n">
         <v>36</v>
@@ -9616,28 +9616,28 @@
         <v>18</v>
       </c>
       <c r="AU36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV36" t="n">
         <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="AX36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ36" t="n">
         <v>10.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BC36" t="n">
         <v>15</v>
@@ -9646,19 +9646,19 @@
         <v>17</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH36" t="n">
         <v>6.2</v>
       </c>
       <c r="BI36" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BJ36" t="n">
         <v>8.4</v>
@@ -9670,7 +9670,7 @@
         <v>50</v>
       </c>
       <c r="BM36" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BN36" t="n">
         <v>6.6</v>
@@ -9679,7 +9679,7 @@
         <v>4.9</v>
       </c>
       <c r="BP36" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ36" t="n">
         <v>5.7</v>
@@ -9706,17 +9706,17 @@
         <v>22</v>
       </c>
       <c r="BY36" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ36" t="n">
         <v>10.5</v>
       </c>
       <c r="CA36" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -9753,16 +9753,16 @@
         <v>4.4</v>
       </c>
       <c r="H37" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I37" t="n">
         <v>1.81</v>
       </c>
       <c r="J37" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K37" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L37" t="n">
         <v>1.14</v>
@@ -9786,7 +9786,7 @@
         <v>2.32</v>
       </c>
       <c r="S37" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T37" t="n">
         <v>1.37</v>
@@ -9798,7 +9798,7 @@
         <v>2.08</v>
       </c>
       <c r="W37" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X37" t="n">
         <v>70</v>
@@ -9852,55 +9852,55 @@
         <v>970</v>
       </c>
       <c r="AO37" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR37" t="n">
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV37" t="n">
         <v>10</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF37" t="n">
         <v>11.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -10001,19 +10001,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="G38" t="n">
         <v>1000</v>
       </c>
       <c r="H38" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I38" t="n">
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10022,16 +10022,16 @@
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>3.7</v>
+        <v>1.32</v>
       </c>
       <c r="O38" t="n">
         <v>1.29</v>
       </c>
       <c r="P38" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q38" t="n">
         <v>1.29</v>
@@ -10040,7 +10040,7 @@
         <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -10049,11 +10049,11 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W38" t="n">
         <v>1.02</v>
       </c>
-      <c r="W38" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X38" t="n">
         <v>1000</v>
       </c>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -10255,19 +10255,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G39" t="n">
         <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I39" t="n">
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10279,28 +10279,28 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P39" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R39" t="n">
         <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -10509,58 +10509,58 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="G40" t="n">
         <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
         <v>1000</v>
       </c>
       <c r="J40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K40" t="n">
+        <v>500</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V40" t="n">
         <v>1.02</v>
       </c>
-      <c r="K40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -10763,19 +10763,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.09</v>
+        <v>2.5</v>
       </c>
       <c r="G41" t="n">
         <v>1000</v>
       </c>
       <c r="H41" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
-        <v>1.09</v>
+        <v>2.5</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -10787,31 +10787,31 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O41" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="P41" t="n">
         <v>1.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.28</v>
+        <v>1.03</v>
       </c>
       <c r="R41" t="n">
         <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="T41" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U41" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W41" t="n">
         <v>1.01</v>
@@ -10904,22 +10904,22 @@
         <v>1.01</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BG41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -11017,19 +11017,19 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G42" t="n">
         <v>1000</v>
       </c>
       <c r="H42" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="I42" t="n">
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11038,25 +11038,25 @@
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="O42" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="P42" t="n">
         <v>1.29</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="R42" t="n">
         <v>1.18</v>
       </c>
       <c r="S42" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -11065,10 +11065,10 @@
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -11271,13 +11271,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="G43" t="n">
         <v>1000</v>
       </c>
       <c r="H43" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I43" t="n">
         <v>1000</v>
@@ -11292,19 +11292,19 @@
         <v>1.23</v>
       </c>
       <c r="M43" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="O43" t="n">
         <v>1.06</v>
       </c>
       <c r="P43" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
@@ -11319,10 +11319,10 @@
         <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -11525,19 +11525,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G44" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H44" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
@@ -11549,22 +11549,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>2.74</v>
+        <v>1.25</v>
       </c>
       <c r="O44" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="P44" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="R44" t="n">
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11573,10 +11573,10 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -11779,19 +11779,19 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="G45" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H45" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I45" t="n">
         <v>1000</v>
       </c>
       <c r="J45" t="n">
-        <v>3.3</v>
+        <v>2.22</v>
       </c>
       <c r="K45" t="n">
         <v>1000</v>
@@ -11800,10 +11800,10 @@
         <v>1.16</v>
       </c>
       <c r="M45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="O45" t="n">
         <v>1.3</v>
@@ -11830,7 +11830,7 @@
         <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="G46" t="n">
         <v>1000</v>
@@ -12045,7 +12045,7 @@
         <v>1000</v>
       </c>
       <c r="J46" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K46" t="n">
         <v>1000</v>
@@ -12141,52 +12141,52 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K47" t="n">
         <v>1000</v>
@@ -12395,52 +12395,52 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12547,7 @@
         <v>4.3</v>
       </c>
       <c r="H48" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I48" t="n">
         <v>2.62</v>
@@ -12556,25 +12556,25 @@
         <v>2.78</v>
       </c>
       <c r="K48" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M48" t="n">
         <v>1.11</v>
       </c>
       <c r="N48" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O48" t="n">
         <v>1.49</v>
       </c>
       <c r="P48" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R48" t="n">
         <v>1.18</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="G49" t="n">
         <v>1000</v>
       </c>
       <c r="H49" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="I49" t="n">
         <v>1000</v>
@@ -12903,52 +12903,52 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF49" t="n">
         <v>1.01</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -13049,22 +13049,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="G50" t="n">
         <v>2.88</v>
       </c>
       <c r="H50" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="K50" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L50" t="n">
         <v>1.5</v>
@@ -13085,10 +13085,10 @@
         <v>2.62</v>
       </c>
       <c r="R50" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="T50" t="n">
         <v>2.12</v>
@@ -13127,7 +13127,7 @@
         <v>70</v>
       </c>
       <c r="AF50" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG50" t="n">
         <v>970</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -13303,16 +13303,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G51" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H51" t="n">
         <v>4.4</v>
       </c>
       <c r="I51" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J51" t="n">
         <v>3</v>
@@ -13330,7 +13330,7 @@
         <v>2.74</v>
       </c>
       <c r="O51" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P51" t="n">
         <v>1.59</v>
@@ -13345,16 +13345,16 @@
         <v>4.4</v>
       </c>
       <c r="T51" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U51" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V51" t="n">
         <v>1.21</v>
       </c>
       <c r="W51" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X51" t="n">
         <v>11</v>
@@ -13393,7 +13393,7 @@
         <v>110</v>
       </c>
       <c r="AJ51" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK51" t="n">
         <v>28</v>
@@ -13408,7 +13408,7 @@
         <v>23</v>
       </c>
       <c r="AO51" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP51" t="n">
         <v>8.4</v>
@@ -13420,7 +13420,7 @@
         <v>23</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT51" t="n">
         <v>5.7</v>
@@ -13444,7 +13444,7 @@
         <v>17.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB51" t="n">
         <v>18</v>
@@ -13456,31 +13456,31 @@
         <v>34</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF51" t="n">
         <v>14.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BH51" t="n">
         <v>3.1</v>
       </c>
       <c r="BI51" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ51" t="n">
         <v>12.5</v>
       </c>
       <c r="BK51" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN51" t="n">
         <v>4.8</v>
@@ -13489,44 +13489,44 @@
         <v>3.55</v>
       </c>
       <c r="BP51" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ51" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR51" t="n">
         <v>40</v>
       </c>
       <c r="BS51" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BT51" t="n">
         <v>9</v>
       </c>
       <c r="BU51" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV51" t="n">
         <v>55</v>
       </c>
       <c r="BW51" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BX51" t="n">
         <v>75</v>
       </c>
       <c r="BY51" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BZ51" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA51" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
         <v>1000</v>
       </c>
       <c r="J52" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K52" t="n">
         <v>3</v>
@@ -13581,10 +13581,10 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O52" t="n">
         <v>1.02</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1.01</v>
       </c>
       <c r="P52" t="n">
         <v>1.25</v>
@@ -13599,10 +13599,10 @@
         <v>1.56</v>
       </c>
       <c r="T52" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U52" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V52" t="n">
         <v>1.01</v>
@@ -13665,52 +13665,52 @@
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -14068,10 +14068,10 @@
         <v>2.1</v>
       </c>
       <c r="G54" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I54" t="n">
         <v>4.4</v>
@@ -14080,7 +14080,7 @@
         <v>3.2</v>
       </c>
       <c r="K54" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L54" t="n">
         <v>1.44</v>
@@ -14089,7 +14089,7 @@
         <v>1.11</v>
       </c>
       <c r="N54" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O54" t="n">
         <v>1.47</v>
@@ -14107,7 +14107,7 @@
         <v>4.8</v>
       </c>
       <c r="T54" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U54" t="n">
         <v>1.83</v>
@@ -14116,10 +14116,10 @@
         <v>1.29</v>
       </c>
       <c r="W54" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X54" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y54" t="n">
         <v>970</v>
@@ -14143,7 +14143,7 @@
         <v>70</v>
       </c>
       <c r="AF54" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG54" t="n">
         <v>970</v>
@@ -14155,10 +14155,10 @@
         <v>110</v>
       </c>
       <c r="AJ54" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK54" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL54" t="n">
         <v>55</v>
@@ -14167,7 +14167,7 @@
         <v>200</v>
       </c>
       <c r="AN54" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO54" t="n">
         <v>120</v>
@@ -14182,7 +14182,7 @@
         <v>9.4</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AT54" t="n">
         <v>6.4</v>
@@ -14194,10 +14194,10 @@
         <v>7.6</v>
       </c>
       <c r="AW54" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AX54" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY54" t="n">
         <v>9.6</v>
@@ -14206,19 +14206,19 @@
         <v>19</v>
       </c>
       <c r="BA54" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="BB54" t="n">
         <v>23</v>
       </c>
       <c r="BC54" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="BD54" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="BE54" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BF54" t="n">
         <v>19</v>
@@ -14230,7 +14230,7 @@
         <v>2.84</v>
       </c>
       <c r="BI54" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ54" t="n">
         <v>11</v>
@@ -14245,13 +14245,13 @@
         <v>15.5</v>
       </c>
       <c r="BN54" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO54" t="n">
         <v>3.7</v>
       </c>
       <c r="BP54" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ54" t="n">
         <v>8.6</v>
@@ -14260,25 +14260,25 @@
         <v>1000</v>
       </c>
       <c r="BS54" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT54" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU54" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV54" t="n">
         <v>1000</v>
       </c>
       <c r="BW54" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -14319,22 +14319,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H55" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I55" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J55" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K55" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L55" t="n">
         <v>1.43</v>
@@ -14343,7 +14343,7 @@
         <v>1.1</v>
       </c>
       <c r="N55" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O55" t="n">
         <v>1.45</v>
@@ -14352,7 +14352,7 @@
         <v>1.67</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R55" t="n">
         <v>1.24</v>
@@ -14367,10 +14367,10 @@
         <v>1.86</v>
       </c>
       <c r="V55" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W55" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X55" t="n">
         <v>970</v>
@@ -14394,7 +14394,7 @@
         <v>970</v>
       </c>
       <c r="AE55" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF55" t="n">
         <v>970</v>
@@ -14406,7 +14406,7 @@
         <v>22</v>
       </c>
       <c r="AI55" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ55" t="n">
         <v>26</v>
@@ -14433,10 +14433,10 @@
         <v>6.6</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="AT55" t="n">
         <v>4.8</v>
@@ -14448,7 +14448,7 @@
         <v>7.8</v>
       </c>
       <c r="AW55" t="n">
-        <v>2.02</v>
+        <v>3.8</v>
       </c>
       <c r="AX55" t="n">
         <v>10</v>
@@ -14457,28 +14457,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="BA55" t="n">
-        <v>2.02</v>
+        <v>2.98</v>
       </c>
       <c r="BB55" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="BD55" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BE55" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="BF55" t="n">
         <v>16</v>
       </c>
       <c r="BG55" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="BH55" t="n">
         <v>2.96</v>
@@ -14526,13 +14526,13 @@
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BZ55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -14576,10 +14576,10 @@
         <v>1.49</v>
       </c>
       <c r="G56" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H56" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I56" t="n">
         <v>9</v>
@@ -14606,7 +14606,7 @@
         <v>1.92</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R56" t="n">
         <v>1.33</v>
@@ -14624,7 +14624,7 @@
         <v>1.12</v>
       </c>
       <c r="W56" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="X56" t="n">
         <v>16.5</v>
@@ -14642,7 +14642,7 @@
         <v>7</v>
       </c>
       <c r="AC56" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD56" t="n">
         <v>38</v>
@@ -14684,13 +14684,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ56" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR56" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS56" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT56" t="n">
         <v>6.2</v>
@@ -14699,10 +14699,10 @@
         <v>9</v>
       </c>
       <c r="AV56" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW56" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX56" t="n">
         <v>6.8</v>
@@ -14711,28 +14711,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ56" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BA56" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB56" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC56" t="n">
         <v>15.5</v>
       </c>
       <c r="BD56" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE56" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF56" t="n">
         <v>6.8</v>
       </c>
       <c r="BG56" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH56" t="n">
         <v>3.35</v>
@@ -14750,13 +14750,13 @@
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN56" t="n">
         <v>3.8</v>
       </c>
       <c r="BO56" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP56" t="n">
         <v>9.800000000000001</v>
@@ -14765,7 +14765,7 @@
         <v>6</v>
       </c>
       <c r="BR56" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS56" t="n">
         <v>10.5</v>
@@ -14774,19 +14774,19 @@
         <v>11.5</v>
       </c>
       <c r="BU56" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV56" t="n">
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ56" t="n">
         <v>21</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -14827,175 +14827,175 @@
         </is>
       </c>
       <c r="F57" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R57" t="n">
         <v>1.22</v>
       </c>
-      <c r="G57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N57" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S57" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="T57" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U57" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V57" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W57" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="X57" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z57" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA57" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB57" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC57" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD57" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE57" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF57" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG57" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH57" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI57" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK57" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL57" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM57" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN57" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO57" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT57" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV57" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG57" t="n">
         <v>1.01</v>
       </c>
       <c r="BH57" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="BI57" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="BJ57" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BK57" t="n">
         <v>5.7</v>
@@ -15004,53 +15004,53 @@
         <v>1000</v>
       </c>
       <c r="BM57" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="BN57" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO57" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BP57" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ57" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR57" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BS57" t="n">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="BT57" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BU57" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BV57" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW57" t="n">
-        <v>2.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX57" t="n">
         <v>1000</v>
       </c>
       <c r="BY57" t="n">
-        <v>2.16</v>
+        <v>9.4</v>
       </c>
       <c r="BZ57" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="CA57" t="n">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -15081,230 +15081,230 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.02</v>
+        <v>2.52</v>
       </c>
       <c r="G58" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="H58" t="n">
-        <v>1.02</v>
+        <v>2.76</v>
       </c>
       <c r="I58" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K58" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L58" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M58" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N58" t="n">
-        <v>1.25</v>
+        <v>2.64</v>
       </c>
       <c r="O58" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P58" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R58" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S58" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="T58" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U58" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V58" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="W58" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="X58" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y58" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z58" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA58" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB58" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC58" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD58" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF58" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG58" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI58" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK58" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL58" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM58" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN58" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO58" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG58" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH58" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI58" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BJ58" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK58" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL58" t="n">
         <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BN58" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO58" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP58" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR58" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS58" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BT58" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU58" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV58" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW58" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BX58" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY58" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BZ58" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA58" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -15335,230 +15335,230 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="G59" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="H59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J59" t="n">
         <v>3.05</v>
       </c>
-      <c r="I59" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J59" t="n">
-        <v>3</v>
-      </c>
       <c r="K59" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L59" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="M59" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="O59" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P59" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R59" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S59" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T59" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="U59" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="V59" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W59" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="X59" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y59" t="n">
         <v>13.5</v>
       </c>
       <c r="Z59" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA59" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB59" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC59" t="n">
         <v>8.6</v>
       </c>
       <c r="AD59" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE59" t="n">
         <v>60</v>
       </c>
       <c r="AF59" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG59" t="n">
         <v>13.5</v>
       </c>
       <c r="AH59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI59" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ59" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK59" t="n">
         <v>34</v>
       </c>
       <c r="AL59" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM59" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN59" t="n">
         <v>32</v>
       </c>
       <c r="AO59" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU59" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV59" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA59" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH59" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BJ59" t="n">
         <v>11</v>
       </c>
       <c r="BK59" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>2.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN59" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO59" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP59" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ59" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR59" t="n">
         <v>38</v>
       </c>
       <c r="BS59" t="n">
-        <v>2.22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT59" t="n">
         <v>7</v>
       </c>
       <c r="BU59" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV59" t="n">
         <v>34</v>
       </c>
       <c r="BW59" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="BX59" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY59" t="n">
-        <v>2.26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ59" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA59" t="n">
-        <v>2.22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G60" t="n">
         <v>2.42</v>
@@ -15604,7 +15604,7 @@
         <v>2.94</v>
       </c>
       <c r="K60" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L60" t="n">
         <v>1.48</v>
@@ -15613,13 +15613,13 @@
         <v>1.11</v>
       </c>
       <c r="N60" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="O60" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P60" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q60" t="n">
         <v>2.44</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -15843,22 +15843,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="G61" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H61" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I61" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J61" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K61" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L61" t="n">
         <v>1.43</v>
@@ -15867,13 +15867,13 @@
         <v>1.07</v>
       </c>
       <c r="N61" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O61" t="n">
         <v>1.36</v>
       </c>
       <c r="P61" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q61" t="n">
         <v>2.06</v>
@@ -15888,13 +15888,13 @@
         <v>1.89</v>
       </c>
       <c r="U61" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W61" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="X61" t="n">
         <v>14</v>
@@ -15903,7 +15903,7 @@
         <v>14</v>
       </c>
       <c r="Z61" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA61" t="n">
         <v>95</v>
@@ -15918,10 +15918,10 @@
         <v>17</v>
       </c>
       <c r="AE61" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF61" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG61" t="n">
         <v>11</v>
@@ -15939,13 +15939,13 @@
         <v>23</v>
       </c>
       <c r="AL61" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM61" t="n">
         <v>140</v>
       </c>
       <c r="AN61" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AO61" t="n">
         <v>75</v>
@@ -15960,7 +15960,7 @@
         <v>24</v>
       </c>
       <c r="AS61" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT61" t="n">
         <v>7.4</v>
@@ -15972,7 +15972,7 @@
         <v>14</v>
       </c>
       <c r="AW61" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AX61" t="n">
         <v>10.5</v>
@@ -15984,7 +15984,7 @@
         <v>17.5</v>
       </c>
       <c r="BA61" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB61" t="n">
         <v>21</v>
@@ -15996,13 +15996,13 @@
         <v>29</v>
       </c>
       <c r="BE61" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF61" t="n">
         <v>13</v>
       </c>
       <c r="BG61" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH61" t="n">
         <v>3.35</v>
@@ -16014,59 +16014,59 @@
         <v>10.5</v>
       </c>
       <c r="BK61" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL61" t="n">
         <v>1000</v>
       </c>
       <c r="BM61" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN61" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO61" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BP61" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ61" t="n">
         <v>6.2</v>
       </c>
       <c r="BR61" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS61" t="n">
         <v>8</v>
       </c>
       <c r="BT61" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU61" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BV61" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW61" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX61" t="n">
         <v>50</v>
       </c>
       <c r="BY61" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ61" t="n">
         <v>30</v>
       </c>
       <c r="CA61" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G62" t="n">
         <v>2.06</v>
@@ -16106,13 +16106,13 @@
         <v>4.4</v>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>3.35</v>
       </c>
       <c r="K62" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L62" t="n">
         <v>1.38</v>
@@ -16142,7 +16142,7 @@
         <v>1.95</v>
       </c>
       <c r="U62" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V62" t="n">
         <v>1.25</v>
@@ -16154,7 +16154,7 @@
         <v>14.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z62" t="n">
         <v>42</v>
@@ -16202,19 +16202,19 @@
         <v>22</v>
       </c>
       <c r="AO62" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP62" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ62" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AR62" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AS62" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT62" t="n">
         <v>6.8</v>
@@ -16226,43 +16226,43 @@
         <v>4.4</v>
       </c>
       <c r="AW62" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX62" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AY62" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AZ62" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA62" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB62" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC62" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD62" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE62" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF62" t="n">
         <v>12.5</v>
       </c>
       <c r="BG62" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH62" t="n">
         <v>3.15</v>
       </c>
       <c r="BI62" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ62" t="n">
         <v>15</v>
@@ -16274,16 +16274,16 @@
         <v>1000</v>
       </c>
       <c r="BM62" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="BN62" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO62" t="n">
         <v>4</v>
       </c>
       <c r="BP62" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ62" t="n">
         <v>9.199999999999999</v>
@@ -16292,35 +16292,35 @@
         <v>1000</v>
       </c>
       <c r="BS62" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BT62" t="n">
         <v>10.5</v>
       </c>
       <c r="BU62" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV62" t="n">
         <v>1000</v>
       </c>
       <c r="BW62" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BX62" t="n">
         <v>1000</v>
       </c>
       <c r="BY62" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ62" t="n">
         <v>1000</v>
       </c>
       <c r="CA62" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -16605,7 +16605,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G64" t="n">
         <v>1.88</v>
@@ -16617,10 +16617,10 @@
         <v>6.8</v>
       </c>
       <c r="J64" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K64" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L64" t="n">
         <v>1.44</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16886,7 @@
         <v>2.6</v>
       </c>
       <c r="O65" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P65" t="n">
         <v>1.54</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -860,13 +860,13 @@
         <v>2.72</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H2" t="n">
         <v>2.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
@@ -881,22 +881,22 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
         <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
         <v>1.6</v>
@@ -941,13 +941,13 @@
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI2" t="n">
         <v>38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AK2" t="n">
         <v>29</v>
@@ -956,7 +956,7 @@
         <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>550</v>
+        <v>190</v>
       </c>
       <c r="AN2" t="n">
         <v>21</v>
@@ -968,7 +968,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
         <v>17</v>
@@ -986,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
         <v>15.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -1126,10 +1126,10 @@
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1174,7 +1174,7 @@
         <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
         <v>13</v>
@@ -1198,19 +1198,19 @@
         <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
         <v>90</v>
       </c>
       <c r="AM3" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>85</v>
@@ -1234,7 +1234,7 @@
         <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
@@ -1258,16 +1258,16 @@
         <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
         <v>20</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.15</v>
+        <v>1.81</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.13</v>
+        <v>2.28</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.29</v>
+        <v>2.78</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
         <v>1.4</v>
@@ -1413,118 +1413,118 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="I5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
         <v>3.9</v>
@@ -1649,136 +1649,136 @@
         <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.02</v>
+        <v>3.95</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
         <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>24</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE5" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH5" t="n">
         <v>60</v>
       </c>
-      <c r="AG5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>34</v>
-      </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AL5" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="n">
         <v>2.98</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BT5" t="n">
         <v>4.3</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G6" t="n">
         <v>2.66</v>
@@ -1912,13 +1912,13 @@
         <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
         <v>1.59</v>
       </c>
       <c r="U6" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
         <v>1.54</v>
@@ -1927,19 +1927,19 @@
         <v>1.6</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="Y6" t="n">
         <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA6" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC6" t="n">
         <v>9.199999999999999</v>
@@ -1957,22 +1957,22 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
         <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>800</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
         <v>17</v>
@@ -1981,13 +1981,13 @@
         <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AQ6" t="n">
         <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
         <v>28</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
         <v>4.5</v>
@@ -2151,28 +2151,28 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
         <v>2.36</v>
       </c>
       <c r="T7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V7" t="n">
         <v>1.49</v>
@@ -2181,73 +2181,73 @@
         <v>1.59</v>
       </c>
       <c r="X7" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="Y7" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="Z7" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
         <v>7.4</v>
@@ -2256,31 +2256,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
         <v>9.800000000000001</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
         <v>3.95</v>
@@ -2396,7 +2396,7 @@
         <v>2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.54</v>
@@ -2435,28 +2435,28 @@
         <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
         <v>970</v>
@@ -2465,82 +2465,82 @@
         <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AQ8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT8" t="n">
         <v>3.95</v>
       </c>
-      <c r="AR8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="AU8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>3.15</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BA8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG8" t="n">
         <v>3.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.15</v>
       </c>
       <c r="BH8" t="n">
         <v>4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -2641,10 +2641,10 @@
         <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
         <v>2.96</v>
@@ -2680,121 +2680,121 @@
         <v>1.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Y9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
         <v>970</v>
       </c>
-      <c r="Z9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9</v>
-      </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AE9" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY9" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -2892,16 +2892,16 @@
         <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="H10" t="n">
         <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
@@ -2919,10 +2919,10 @@
         <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
@@ -2937,118 +2937,118 @@
         <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA10" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>470</v>
+      </c>
+      <c r="AF10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>12</v>
-      </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>370</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL10" t="n">
         <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="AR10" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.98</v>
+        <v>4.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="n">
         <v>3.25</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G11" t="n">
         <v>2.22</v>
@@ -3188,7 +3188,7 @@
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
         <v>1.23</v>
@@ -3200,13 +3200,13 @@
         <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Z11" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
         <v>8.199999999999999</v>
@@ -3215,94 +3215,94 @@
         <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AF11" t="n">
         <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="AH11" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AI11" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AO11" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU11" t="n">
         <v>3.2</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AR11" t="n">
+      <c r="AV11" t="n">
         <v>3.95</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AW11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB11" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW11" t="n">
+      <c r="BC11" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA11" t="n">
+      <c r="BD11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF11" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BG11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH11" t="n">
         <v>2.88</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="J12" t="n">
         <v>3.05</v>
@@ -3415,160 +3415,160 @@
         <v>3.45</v>
       </c>
       <c r="L12" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="O12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="X12" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AB12" t="n">
         <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AF12" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AM12" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO12" t="n">
         <v>42</v>
       </c>
-      <c r="AO12" t="n">
-        <v>65</v>
-      </c>
       <c r="AP12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AR12" t="n">
         <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AU12" t="n">
         <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>26</v>
+        <v>7.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.3</v>
+        <v>38</v>
       </c>
       <c r="BB12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,50 +3577,50 @@
         <v>10.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BQ12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW12" t="n">
         <v>7.6</v>
       </c>
-      <c r="BR12" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>29</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BX12" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>42</v>
       </c>
       <c r="CA12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
         <v>2.52</v>
@@ -3663,7 +3663,7 @@
         <v>3.95</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
         <v>3.8</v>
@@ -3705,28 +3705,28 @@
         <v>1.66</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y13" t="n">
         <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
         <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
         <v>970</v>
@@ -3735,82 +3735,82 @@
         <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV13" t="n">
         <v>5</v>
       </c>
-      <c r="AT13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="AX13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD13" t="n">
         <v>4</v>
       </c>
-      <c r="AY13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
         <v>1.23</v>
@@ -3962,10 +3962,10 @@
         <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="Z14" t="n">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="AA14" t="n">
         <v>190</v>
@@ -3980,19 +3980,19 @@
         <v>32</v>
       </c>
       <c r="AE14" t="n">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="AF14" t="n">
         <v>14.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="AJ14" t="n">
         <v>16.5</v>
@@ -4001,10 +4001,10 @@
         <v>16</v>
       </c>
       <c r="AL14" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="AN14" t="n">
         <v>5.4</v>
@@ -4013,16 +4013,16 @@
         <v>65</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -4034,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX14" t="n">
         <v>9.4</v>
@@ -4046,7 +4046,7 @@
         <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BB14" t="n">
         <v>12</v>
@@ -4058,13 +4058,13 @@
         <v>18</v>
       </c>
       <c r="BE14" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH14" t="n">
         <v>5.3</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -4165,10 +4165,10 @@
         <v>1.98</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
         <v>3.8</v>
@@ -4207,13 +4207,13 @@
         <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
         <v>2.02</v>
       </c>
       <c r="X15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
         <v>21</v>
@@ -4222,49 +4222,49 @@
         <v>36</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB15" t="n">
         <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
         <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP15" t="n">
         <v>17</v>
@@ -4273,13 +4273,13 @@
         <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
         <v>36</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
         <v>8</v>
@@ -4303,7 +4303,7 @@
         <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC15" t="n">
         <v>16.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H16" t="n">
         <v>6.8</v>
@@ -4425,10 +4425,10 @@
         <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.24</v>
@@ -4446,10 +4446,10 @@
         <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S16" t="n">
         <v>2.38</v>
@@ -4464,16 +4464,16 @@
         <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X16" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
         <v>36</v>
       </c>
       <c r="Z16" t="n">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AA16" t="n">
         <v>210</v>
@@ -4482,13 +4482,13 @@
         <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD16" t="n">
         <v>32</v>
       </c>
       <c r="AE16" t="n">
-        <v>100</v>
+        <v>480</v>
       </c>
       <c r="AF16" t="n">
         <v>11</v>
@@ -4497,40 +4497,40 @@
         <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AI16" t="n">
-        <v>85</v>
+        <v>390</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN16" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AP16" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
         <v>9.199999999999999</v>
@@ -4539,10 +4539,10 @@
         <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AX16" t="n">
         <v>8.199999999999999</v>
@@ -4554,7 +4554,7 @@
         <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BB16" t="n">
         <v>11</v>
@@ -4566,19 +4566,19 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF16" t="n">
         <v>5.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BH16" t="n">
         <v>4.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4596,13 +4596,13 @@
         <v>4.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BP16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G17" t="n">
         <v>5.5</v>
@@ -4676,13 +4676,13 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.25</v>
@@ -4709,19 +4709,19 @@
         <v>2.36</v>
       </c>
       <c r="T17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
         <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X17" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="Y17" t="n">
         <v>970</v>
@@ -4730,64 +4730,64 @@
         <v>970</v>
       </c>
       <c r="AA17" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE17" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AH17" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI17" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AK17" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AM17" t="n">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>48</v>
+        <v>700</v>
       </c>
       <c r="AO17" t="n">
         <v>8.6</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
@@ -4796,34 +4796,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB17" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC17" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG17" t="n">
         <v>5.9</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G18" t="n">
         <v>6.2</v>
@@ -4930,7 +4930,7 @@
         <v>1.72</v>
       </c>
       <c r="I18" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="J18" t="n">
         <v>3.55</v>
@@ -4969,61 +4969,61 @@
         <v>1.89</v>
       </c>
       <c r="V18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W18" t="n">
         <v>1.19</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>22</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AF18" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AH18" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AL18" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AM18" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO18" t="n">
         <v>15.5</v>
@@ -5038,7 +5038,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AT18" t="n">
         <v>13.5</v>
@@ -5053,7 +5053,7 @@
         <v>15</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AY18" t="n">
         <v>17</v>
@@ -5062,22 +5062,22 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BG18" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
         <v>3.35</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -5181,19 +5181,19 @@
         <v>1.74</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
         <v>7.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
         <v>4.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -5211,7 +5211,7 @@
         <v>1.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
         <v>3.15</v>
@@ -5232,115 +5232,115 @@
         <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="Z19" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF19" t="n">
         <v>970</v>
       </c>
-      <c r="AC19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ19" t="n">
         <v>970</v>
       </c>
       <c r="AK19" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AL19" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.5</v>
+        <v>2.18</v>
       </c>
       <c r="AT19" t="n">
         <v>6.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AV19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4.3</v>
       </c>
-      <c r="AW19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BG19" t="n">
-        <v>5</v>
+        <v>2.52</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -5441,10 +5441,10 @@
         <v>5.3</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K20" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.18</v>
@@ -5453,7 +5453,7 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.12</v>
@@ -5462,13 +5462,13 @@
         <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R20" t="n">
         <v>1.88</v>
       </c>
       <c r="S20" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="T20" t="n">
         <v>1.49</v>
@@ -5477,22 +5477,22 @@
         <v>2.72</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W20" t="n">
         <v>2.36</v>
       </c>
       <c r="X20" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="Y20" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="Z20" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AB20" t="n">
         <v>970</v>
@@ -5501,64 +5501,64 @@
         <v>970</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AE20" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AF20" t="n">
         <v>970</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH20" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI20" t="n">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AK20" t="n">
         <v>970</v>
       </c>
       <c r="AL20" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AO20" t="n">
-        <v>34</v>
+        <v>700</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.48</v>
+        <v>8.4</v>
       </c>
       <c r="AX20" t="n">
         <v>10.5</v>
@@ -5570,7 +5570,7 @@
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.98</v>
+        <v>8.4</v>
       </c>
       <c r="BB20" t="n">
         <v>12</v>
@@ -5579,16 +5579,16 @@
         <v>10.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF20" t="n">
         <v>4.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
         <v>1.59</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R21" t="n">
         <v>1.22</v>
@@ -5737,58 +5737,58 @@
         <v>1.39</v>
       </c>
       <c r="X21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
         <v>19</v>
       </c>
       <c r="AA21" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
         <v>10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AE21" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
         <v>25</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AI21" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AK21" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL21" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM21" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO21" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
         <v>7.6</v>
@@ -5800,7 +5800,7 @@
         <v>12.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
         <v>7.6</v>
@@ -5812,7 +5812,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="AX21" t="n">
         <v>16</v>
@@ -5824,25 +5824,25 @@
         <v>15.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH21" t="n">
         <v>3.05</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J22" t="n">
         <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -5964,151 +5964,151 @@
         <v>3.95</v>
       </c>
       <c r="O22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R22" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y22" t="n">
         <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA22" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
         <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="AO22" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF22" t="n">
         <v>5.5</v>
       </c>
-      <c r="AS22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU22" t="n">
+      <c r="BG22" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC22" t="n">
+      <c r="BH22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>5</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6117,40 +6117,40 @@
         <v>1.41</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT22" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
         <v>1.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q23" t="n">
         <v>2.08</v>
@@ -6245,7 +6245,7 @@
         <v>1.27</v>
       </c>
       <c r="X23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y23" t="n">
         <v>8.800000000000001</v>
@@ -6254,10 +6254,10 @@
         <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="AB23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC23" t="n">
         <v>8.199999999999999</v>
@@ -6269,7 +6269,7 @@
         <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AG23" t="n">
         <v>18.5</v>
@@ -6278,76 +6278,76 @@
         <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>44</v>
+        <v>290</v>
       </c>
       <c r="AJ23" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK23" t="n">
         <v>70</v>
       </c>
       <c r="AL23" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM23" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN23" t="n">
         <v>150</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>80</v>
       </c>
       <c r="AO23" t="n">
         <v>23</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ23" t="n">
         <v>7</v>
       </c>
       <c r="AR23" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AW23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>6</v>
       </c>
-      <c r="AX23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BA23" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC23" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC23" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD23" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG23" t="n">
         <v>13.5</v>
@@ -6356,7 +6356,7 @@
         <v>3.25</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.82</v>
+        <v>2.54</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -6466,7 +6466,7 @@
         <v>1.22</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
         <v>6.4</v>
@@ -6499,7 +6499,7 @@
         <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y24" t="n">
         <v>25</v>
@@ -6535,7 +6535,7 @@
         <v>38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK24" t="n">
         <v>18</v>
@@ -6553,52 +6553,52 @@
         <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ24" t="n">
         <v>20</v>
       </c>
       <c r="AR24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY24" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE24" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF24" t="n">
         <v>5.8</v>
@@ -6616,7 +6616,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
@@ -6628,13 +6628,13 @@
         <v>5.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP24" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BR24" t="n">
         <v>20</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -6759,10 +6759,10 @@
         <v>16</v>
       </c>
       <c r="Z25" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AA25" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
         <v>9.4</v>
@@ -6774,37 +6774,37 @@
         <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AF25" t="n">
         <v>14</v>
       </c>
       <c r="AG25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
         <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29</v>
+        <v>900</v>
       </c>
       <c r="AK25" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN25" t="n">
         <v>21</v>
       </c>
       <c r="AO25" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP25" t="n">
         <v>9.4</v>
@@ -6813,10 +6813,10 @@
         <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT25" t="n">
         <v>7</v>
@@ -6828,10 +6828,10 @@
         <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AY25" t="n">
         <v>8.199999999999999</v>
@@ -6840,7 +6840,7 @@
         <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB25" t="n">
         <v>19</v>
@@ -6849,16 +6849,16 @@
         <v>18</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF25" t="n">
         <v>14</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH25" t="n">
         <v>3.25</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
         <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
         <v>1.74</v>
@@ -7004,7 +7004,7 @@
         <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X26" t="n">
         <v>21</v>
@@ -7016,7 +7016,7 @@
         <v>32</v>
       </c>
       <c r="AA26" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
         <v>13</v>
@@ -7034,7 +7034,7 @@
         <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
         <v>19</v>
@@ -7043,16 +7043,16 @@
         <v>55</v>
       </c>
       <c r="AJ26" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
         <v>38</v>
       </c>
       <c r="AM26" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AN26" t="n">
         <v>16</v>
@@ -7070,7 +7070,7 @@
         <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT26" t="n">
         <v>8.4</v>
@@ -7082,7 +7082,7 @@
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX26" t="n">
         <v>11</v>
@@ -7094,7 +7094,7 @@
         <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB26" t="n">
         <v>20</v>
@@ -7103,16 +7103,16 @@
         <v>16</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF26" t="n">
         <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH26" t="n">
         <v>3.9</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
         <v>18</v>
       </c>
       <c r="AS27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT27" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -7360,7 +7360,7 @@
         <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF27" t="n">
         <v>9.4</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
         <v>22</v>
       </c>
       <c r="AA28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB28" t="n">
         <v>11.5</v>
@@ -7551,7 +7551,7 @@
         <v>70</v>
       </c>
       <c r="AJ28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK28" t="n">
         <v>48</v>
@@ -7569,7 +7569,7 @@
         <v>50</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>8</v>
@@ -7578,10 +7578,10 @@
         <v>15.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU28" t="n">
         <v>6.2</v>
@@ -7590,7 +7590,7 @@
         <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX28" t="n">
         <v>15.5</v>
@@ -7602,25 +7602,25 @@
         <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH28" t="n">
         <v>3.05</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
         <v>2.16</v>
       </c>
       <c r="I29" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J29" t="n">
         <v>3.45</v>
@@ -7739,28 +7739,28 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T29" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U29" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V29" t="n">
         <v>1.7</v>
@@ -7778,7 +7778,7 @@
         <v>970</v>
       </c>
       <c r="AA29" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
         <v>970</v>
@@ -7790,10 +7790,10 @@
         <v>970</v>
       </c>
       <c r="AE29" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AF29" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AG29" t="n">
         <v>970</v>
@@ -7802,79 +7802,79 @@
         <v>970</v>
       </c>
       <c r="AI29" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AJ29" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK29" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AL29" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM29" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AN29" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AO29" t="n">
         <v>970</v>
       </c>
       <c r="AP29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT29" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.95</v>
       </c>
       <c r="AU29" t="n">
         <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF29" t="n">
         <v>4.8</v>
       </c>
-      <c r="BF29" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH29" t="n">
         <v>3.75</v>
@@ -7916,7 +7916,7 @@
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>3.15</v>
       </c>
       <c r="G30" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H30" t="n">
         <v>2.7</v>
@@ -7981,7 +7981,7 @@
         <v>3.1</v>
       </c>
       <c r="J30" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="K30" t="n">
         <v>2.98</v>
@@ -8032,7 +8032,7 @@
         <v>970</v>
       </c>
       <c r="AA30" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AB30" t="n">
         <v>9.199999999999999</v>
@@ -8044,46 +8044,46 @@
         <v>970</v>
       </c>
       <c r="AE30" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF30" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AG30" t="n">
         <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AI30" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ30" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AK30" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AL30" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN30" t="n">
         <v>120</v>
       </c>
       <c r="AO30" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AP30" t="n">
         <v>5.1</v>
       </c>
       <c r="AQ30" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS30" t="n">
         <v>5.5</v>
@@ -8095,7 +8095,7 @@
         <v>5.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW30" t="n">
         <v>5.5</v>
@@ -8104,7 +8104,7 @@
         <v>4.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ30" t="n">
         <v>5</v>
@@ -8116,7 +8116,7 @@
         <v>5.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD30" t="n">
         <v>5.7</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
         <v>1.26</v>
       </c>
       <c r="M31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N31" t="n">
         <v>5.2</v>
@@ -8268,7 +8268,7 @@
         <v>1.67</v>
       </c>
       <c r="U31" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V31" t="n">
         <v>1.25</v>
@@ -8280,13 +8280,13 @@
         <v>27</v>
       </c>
       <c r="Y31" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="Z31" t="n">
         <v>50</v>
       </c>
       <c r="AA31" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB31" t="n">
         <v>11.5</v>
@@ -8298,7 +8298,7 @@
         <v>23</v>
       </c>
       <c r="AE31" t="n">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AF31" t="n">
         <v>12</v>
@@ -8307,10 +8307,10 @@
         <v>11.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AI31" t="n">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AJ31" t="n">
         <v>23</v>
@@ -8319,10 +8319,10 @@
         <v>16</v>
       </c>
       <c r="AL31" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AN31" t="n">
         <v>9.4</v>
@@ -8412,7 +8412,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G32" t="n">
         <v>2.72</v>
@@ -8489,7 +8489,7 @@
         <v>3.85</v>
       </c>
       <c r="J32" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K32" t="n">
         <v>3.35</v>
@@ -8507,7 +8507,7 @@
         <v>1.52</v>
       </c>
       <c r="P32" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q32" t="n">
         <v>2.54</v>
@@ -8540,7 +8540,7 @@
         <v>29</v>
       </c>
       <c r="AA32" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
         <v>8.199999999999999</v>
@@ -8576,7 +8576,7 @@
         <v>70</v>
       </c>
       <c r="AM32" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN32" t="n">
         <v>50</v>
@@ -8585,7 +8585,7 @@
         <v>95</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ32" t="n">
         <v>8.4</v>
@@ -8600,10 +8600,10 @@
         <v>6.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AV32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW32" t="n">
         <v>5.8</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -8731,40 +8731,40 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="G33" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="H33" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="I33" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="K33" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L33" t="n">
         <v>1.62</v>
       </c>
       <c r="M33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N33" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="O33" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P33" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="R33" t="n">
         <v>1.14</v>
@@ -8776,64 +8776,64 @@
         <v>2.42</v>
       </c>
       <c r="U33" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V33" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W33" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="X33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA33" t="n">
-        <v>260</v>
+        <v>900</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD33" t="n">
         <v>36</v>
       </c>
       <c r="AE33" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AF33" t="n">
         <v>10.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="AH33" t="n">
         <v>42</v>
       </c>
       <c r="AI33" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AJ33" t="n">
-        <v>30</v>
+        <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AL33" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN33" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
@@ -8845,34 +8845,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR33" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT33" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ33" t="n">
         <v>6.4</v>
       </c>
-      <c r="AW33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BA33" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB33" t="n">
         <v>6</v>
@@ -8881,37 +8881,37 @@
         <v>22</v>
       </c>
       <c r="BD33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF33" t="n">
         <v>20</v>
       </c>
       <c r="BG33" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH33" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BI33" t="n">
         <v>2.14</v>
       </c>
       <c r="BJ33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK33" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO33" t="n">
         <v>3.4</v>
@@ -8926,35 +8926,35 @@
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA33" t="n">
         <v>8.6</v>
       </c>
-      <c r="BT33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -8985,100 +8985,100 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G34" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="H34" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="I34" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="J34" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K34" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>2.96</v>
+        <v>6.6</v>
       </c>
       <c r="O34" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P34" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="R34" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="S34" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="T34" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="U34" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="V34" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y34" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Z34" t="n">
         <v>36</v>
       </c>
       <c r="AA34" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AB34" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AD34" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AE34" t="n">
         <v>36</v>
       </c>
       <c r="AF34" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AG34" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AH34" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AI34" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ34" t="n">
         <v>42</v>
       </c>
       <c r="AK34" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AL34" t="n">
         <v>34</v>
@@ -9087,43 +9087,43 @@
         <v>60</v>
       </c>
       <c r="AN34" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.68</v>
+        <v>7</v>
       </c>
       <c r="AQ34" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AR34" t="n">
         <v>17.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.56</v>
+        <v>30</v>
       </c>
       <c r="AT34" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AW34" t="n">
         <v>17.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AY34" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BA34" t="n">
         <v>19</v>
@@ -9132,19 +9132,19 @@
         <v>20</v>
       </c>
       <c r="BC34" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BD34" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.56</v>
+        <v>30</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>2.68</v>
+        <v>12.5</v>
       </c>
       <c r="BH34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -9496,10 +9496,10 @@
         <v>2.16</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H36" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="I36" t="n">
         <v>3.15</v>
@@ -9514,7 +9514,7 @@
         <v>1.17</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N36" t="n">
         <v>7.6</v>
@@ -9544,7 +9544,7 @@
         <v>1.46</v>
       </c>
       <c r="W36" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X36" t="n">
         <v>55</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
         <v>1.81</v>
       </c>
       <c r="J37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K37" t="n">
         <v>7</v>
@@ -9801,19 +9801,19 @@
         <v>1.27</v>
       </c>
       <c r="X37" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="Y37" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="Z37" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AA37" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AB37" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AC37" t="n">
         <v>970</v>
@@ -9825,28 +9825,28 @@
         <v>970</v>
       </c>
       <c r="AF37" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AG37" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AH37" t="n">
         <v>970</v>
       </c>
       <c r="AI37" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AJ37" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AK37" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL37" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AM37" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AN37" t="n">
         <v>970</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="G38" t="n">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="H38" t="n">
         <v>4</v>
@@ -10013,7 +10013,7 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10025,34 +10025,34 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="O38" t="n">
         <v>1.29</v>
       </c>
       <c r="P38" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="R38" t="n">
         <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="V38" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W38" t="n">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10091,7 +10091,7 @@
         <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.09</v>
+        <v>1.72</v>
       </c>
       <c r="G39" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="H39" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10279,142 +10279,142 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="O39" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="P39" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R39" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S39" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T39" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U39" t="n">
         <v>1.11</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -10509,166 +10509,166 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="G40" t="n">
         <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I40" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J40" t="n">
-        <v>1.09</v>
+        <v>2.4</v>
       </c>
       <c r="K40" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O40" t="n">
-        <v>1.51</v>
+        <v>1.13</v>
       </c>
       <c r="P40" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.44</v>
+        <v>1.55</v>
       </c>
       <c r="R40" t="n">
         <v>1.17</v>
       </c>
       <c r="S40" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="T40" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U40" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -10763,22 +10763,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="G41" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="H41" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>2.12</v>
       </c>
       <c r="J41" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L41" t="n">
         <v>1.22</v>
@@ -10787,46 +10787,46 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O41" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P41" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="R41" t="n">
         <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="T41" t="n">
         <v>1.11</v>
       </c>
       <c r="U41" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.11</v>
       </c>
-      <c r="V41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X41" t="n">
         <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB41" t="n">
         <v>1000</v>
@@ -10835,10 +10835,10 @@
         <v>1000</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF41" t="n">
         <v>1000</v>
@@ -10850,7 +10850,7 @@
         <v>1000</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ41" t="n">
         <v>1000</v>
@@ -10868,7 +10868,7 @@
         <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP41" t="n">
         <v>1.01</v>
@@ -10919,7 +10919,7 @@
         <v>1.01</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="BG41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -11017,13 +11017,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G42" t="n">
         <v>1000</v>
       </c>
       <c r="H42" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="I42" t="n">
         <v>1000</v>
@@ -11041,10 +11041,10 @@
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="O42" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="P42" t="n">
         <v>1.29</v>
@@ -11056,7 +11056,7 @@
         <v>1.18</v>
       </c>
       <c r="S42" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -11065,118 +11065,118 @@
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="W42" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="G43" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H43" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>1.14</v>
+        <v>2.54</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L43" t="n">
         <v>1.23</v>
@@ -11295,10 +11295,10 @@
         <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O43" t="n">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="P43" t="n">
         <v>1.47</v>
@@ -11316,13 +11316,13 @@
         <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W43" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11337,7 +11337,7 @@
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC43" t="n">
         <v>1000</v>
@@ -11349,10 +11349,10 @@
         <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG43" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH43" t="n">
         <v>1000</v>
@@ -11361,76 +11361,76 @@
         <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM43" t="n">
         <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO43" t="n">
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
         <v>1.5</v>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>6.2</v>
       </c>
       <c r="H44" t="n">
         <v>2.3</v>
@@ -11549,13 +11549,13 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O44" t="n">
         <v>1.31</v>
       </c>
       <c r="P44" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q44" t="n">
         <v>1.31</v>
@@ -11573,10 +11573,10 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11591,7 +11591,7 @@
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC44" t="n">
         <v>1000</v>
@@ -11603,10 +11603,10 @@
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG44" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH44" t="n">
         <v>1000</v>
@@ -11615,19 +11615,19 @@
         <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM44" t="n">
         <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -11779,22 +11779,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="G45" t="n">
         <v>1.87</v>
       </c>
       <c r="H45" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I45" t="n">
         <v>1000</v>
       </c>
       <c r="J45" t="n">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="K45" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L45" t="n">
         <v>1.16</v>
@@ -11827,7 +11827,7 @@
         <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W45" t="n">
         <v>2.14</v>
@@ -11869,7 +11869,7 @@
         <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -12033,22 +12033,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.19</v>
+        <v>1.7</v>
       </c>
       <c r="G46" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H46" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="I46" t="n">
         <v>1000</v>
       </c>
       <c r="J46" t="n">
-        <v>1.1</v>
+        <v>2.14</v>
       </c>
       <c r="K46" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -12075,70 +12075,70 @@
         <v>1.72</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W46" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -12287,19 +12287,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
         <v>1000</v>
       </c>
       <c r="H47" t="n">
-        <v>1.09</v>
+        <v>2.1</v>
       </c>
       <c r="I47" t="n">
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="K47" t="n">
         <v>1000</v>
@@ -12335,64 +12335,64 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA47" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G48" t="n">
         <v>4.3</v>
@@ -12553,7 +12553,7 @@
         <v>2.62</v>
       </c>
       <c r="J48" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K48" t="n">
         <v>3.35</v>
@@ -12583,10 +12583,10 @@
         <v>5</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U48" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V48" t="n">
         <v>1.62</v>
@@ -12631,7 +12631,7 @@
         <v>70</v>
       </c>
       <c r="AJ48" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AK48" t="n">
         <v>70</v>
@@ -12640,7 +12640,7 @@
         <v>95</v>
       </c>
       <c r="AM48" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN48" t="n">
         <v>100</v>
@@ -12649,10 +12649,10 @@
         <v>38</v>
       </c>
       <c r="AP48" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="AQ48" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR48" t="n">
         <v>4.1</v>
@@ -12661,10 +12661,10 @@
         <v>4.8</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="AV48" t="n">
         <v>3.95</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -12795,19 +12795,19 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.19</v>
+        <v>1.93</v>
       </c>
       <c r="G49" t="n">
         <v>1000</v>
       </c>
       <c r="H49" t="n">
-        <v>1.19</v>
+        <v>2.18</v>
       </c>
       <c r="I49" t="n">
         <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="K49" t="n">
         <v>1000</v>
@@ -12843,64 +12843,64 @@
         <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W49" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP49" t="n">
         <v>1.01</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -13058,10 +13058,10 @@
         <v>3.15</v>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J50" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="K50" t="n">
         <v>3.2</v>
@@ -13109,10 +13109,10 @@
         <v>970</v>
       </c>
       <c r="Z50" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AA50" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB50" t="n">
         <v>970</v>
@@ -13124,7 +13124,7 @@
         <v>970</v>
       </c>
       <c r="AE50" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AF50" t="n">
         <v>970</v>
@@ -13133,25 +13133,25 @@
         <v>970</v>
       </c>
       <c r="AH50" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AI50" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ50" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AK50" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AL50" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AM50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN50" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO50" t="n">
         <v>1000</v>
@@ -13160,7 +13160,7 @@
         <v>3</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AR50" t="n">
         <v>3.8</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -13345,7 +13345,7 @@
         <v>4.4</v>
       </c>
       <c r="T51" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U51" t="n">
         <v>1.73</v>
@@ -13366,7 +13366,7 @@
         <v>40</v>
       </c>
       <c r="AA51" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB51" t="n">
         <v>7.6</v>
@@ -13402,13 +13402,13 @@
         <v>55</v>
       </c>
       <c r="AM51" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN51" t="n">
         <v>23</v>
       </c>
       <c r="AO51" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AP51" t="n">
         <v>8.4</v>
@@ -13420,7 +13420,7 @@
         <v>23</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT51" t="n">
         <v>5.7</v>
@@ -13432,7 +13432,7 @@
         <v>15.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX51" t="n">
         <v>8.6</v>
@@ -13444,7 +13444,7 @@
         <v>17.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB51" t="n">
         <v>18</v>
@@ -13456,13 +13456,13 @@
         <v>34</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF51" t="n">
         <v>14.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH51" t="n">
         <v>3.1</v>
@@ -13474,13 +13474,13 @@
         <v>12.5</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN51" t="n">
         <v>4.8</v>
@@ -13492,41 +13492,41 @@
         <v>16.5</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR51" t="n">
         <v>40</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT51" t="n">
         <v>9</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV51" t="n">
         <v>55</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX51" t="n">
         <v>75</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ51" t="n">
         <v>40</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -13605,64 +13605,64 @@
         <v>1.11</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W52" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -14065,148 +14065,148 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G54" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H54" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J54" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K54" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L54" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M54" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N54" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="O54" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="P54" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="R54" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S54" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="T54" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U54" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="V54" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W54" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="X54" t="n">
         <v>10.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA54" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB54" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC54" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD54" t="n">
         <v>970</v>
       </c>
       <c r="AE54" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AF54" t="n">
         <v>12</v>
       </c>
       <c r="AG54" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AI54" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ54" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AK54" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL54" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM54" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN54" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AO54" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AP54" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AQ54" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR54" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT54" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU54" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV54" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW54" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AX54" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ54" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY54" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>19</v>
-      </c>
       <c r="BA54" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BB54" t="n">
         <v>23</v>
@@ -14215,19 +14215,19 @@
         <v>23</v>
       </c>
       <c r="BD54" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="BE54" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BF54" t="n">
         <v>19</v>
       </c>
       <c r="BG54" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BH54" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BI54" t="n">
         <v>2.44</v>
@@ -14236,31 +14236,31 @@
         <v>11</v>
       </c>
       <c r="BK54" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BN54" t="n">
         <v>4.7</v>
       </c>
       <c r="BO54" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP54" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ54" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR54" t="n">
         <v>1000</v>
       </c>
       <c r="BS54" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT54" t="n">
         <v>7.4</v>
@@ -14272,23 +14272,23 @@
         <v>1000</v>
       </c>
       <c r="BW54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ54" t="n">
         <v>1000</v>
       </c>
       <c r="CA54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
         <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H55" t="n">
         <v>4.3</v>
@@ -14334,37 +14334,37 @@
         <v>3.3</v>
       </c>
       <c r="K55" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L55" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M55" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N55" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="O55" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="P55" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="R55" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S55" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T55" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U55" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="V55" t="n">
         <v>1.26</v>
@@ -14379,112 +14379,112 @@
         <v>970</v>
       </c>
       <c r="Z55" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA55" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB55" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AC55" t="n">
         <v>970</v>
       </c>
       <c r="AD55" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AE55" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AF55" t="n">
         <v>970</v>
       </c>
       <c r="AG55" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI55" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ55" t="n">
-        <v>26</v>
+        <v>900</v>
       </c>
       <c r="AK55" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AL55" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM55" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN55" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AO55" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP55" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ55" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV55" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR55" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AW55" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX55" t="n">
         <v>10</v>
       </c>
       <c r="AY55" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="BA55" t="n">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="BB55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="BD55" t="n">
-        <v>2.3</v>
+        <v>3.95</v>
       </c>
       <c r="BE55" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="BF55" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BG55" t="n">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="BH55" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BJ55" t="n">
         <v>11</v>
@@ -14496,53 +14496,53 @@
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>2.48</v>
+        <v>1.6</v>
       </c>
       <c r="BN55" t="n">
         <v>4.6</v>
       </c>
       <c r="BO55" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP55" t="n">
         <v>1000</v>
       </c>
       <c r="BQ55" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR55" t="n">
         <v>1000</v>
       </c>
       <c r="BS55" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BT55" t="n">
         <v>7.6</v>
       </c>
       <c r="BU55" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV55" t="n">
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>2.42</v>
+        <v>1.57</v>
       </c>
       <c r="BZ55" t="n">
         <v>1000</v>
       </c>
       <c r="CA55" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -14573,31 +14573,31 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="G56" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="H56" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="J56" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K56" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L56" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M56" t="n">
         <v>1.07</v>
       </c>
       <c r="N56" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O56" t="n">
         <v>1.35</v>
@@ -14606,43 +14606,43 @@
         <v>1.92</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R56" t="n">
         <v>1.33</v>
       </c>
       <c r="S56" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T56" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U56" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="V56" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W56" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="X56" t="n">
         <v>16.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Z56" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AA56" t="n">
-        <v>380</v>
+        <v>470</v>
       </c>
       <c r="AB56" t="n">
         <v>7</v>
       </c>
       <c r="AC56" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD56" t="n">
         <v>38</v>
@@ -14651,7 +14651,7 @@
         <v>190</v>
       </c>
       <c r="AF56" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG56" t="n">
         <v>10.5</v>
@@ -14663,22 +14663,22 @@
         <v>170</v>
       </c>
       <c r="AJ56" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK56" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL56" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM56" t="n">
         <v>270</v>
       </c>
       <c r="AN56" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO56" t="n">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="AP56" t="n">
         <v>11.5</v>
@@ -14687,116 +14687,116 @@
         <v>7</v>
       </c>
       <c r="AR56" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS56" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT56" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU56" t="n">
         <v>9</v>
       </c>
       <c r="AV56" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="AW56" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX56" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY56" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ56" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BA56" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BB56" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC56" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD56" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BE56" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF56" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG56" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH56" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BJ56" t="n">
         <v>12.5</v>
       </c>
       <c r="BK56" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN56" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BO56" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP56" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BQ56" t="n">
         <v>6</v>
       </c>
       <c r="BR56" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS56" t="n">
         <v>10.5</v>
       </c>
       <c r="BT56" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU56" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BV56" t="n">
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ56" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
         <v>2.04</v>
       </c>
       <c r="H57" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I57" t="n">
         <v>5.3</v>
@@ -14878,7 +14878,7 @@
         <v>1.23</v>
       </c>
       <c r="W57" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X57" t="n">
         <v>12.5</v>
@@ -14890,7 +14890,7 @@
         <v>48</v>
       </c>
       <c r="AA57" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB57" t="n">
         <v>8.4</v>
@@ -14926,7 +14926,7 @@
         <v>65</v>
       </c>
       <c r="AM57" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN57" t="n">
         <v>24</v>
@@ -14941,10 +14941,10 @@
         <v>10</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT57" t="n">
         <v>5.3</v>
@@ -14956,7 +14956,7 @@
         <v>15</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX57" t="n">
         <v>7.8</v>
@@ -14968,7 +14968,7 @@
         <v>17</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB57" t="n">
         <v>16.5</v>
@@ -14977,16 +14977,16 @@
         <v>17.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF57" t="n">
         <v>14</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH57" t="n">
         <v>3</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -15084,13 +15084,13 @@
         <v>2.52</v>
       </c>
       <c r="G58" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H58" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J58" t="n">
         <v>3.05</v>
@@ -15099,13 +15099,13 @@
         <v>3.65</v>
       </c>
       <c r="L58" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M58" t="n">
         <v>1.1</v>
       </c>
       <c r="N58" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="O58" t="n">
         <v>1.44</v>
@@ -15114,22 +15114,22 @@
         <v>1.59</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R58" t="n">
         <v>1.21</v>
       </c>
       <c r="S58" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T58" t="n">
         <v>1.92</v>
       </c>
       <c r="U58" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V58" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W58" t="n">
         <v>1.51</v>
@@ -15144,7 +15144,7 @@
         <v>23</v>
       </c>
       <c r="AA58" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB58" t="n">
         <v>10.5</v>
@@ -15153,13 +15153,13 @@
         <v>8.4</v>
       </c>
       <c r="AD58" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE58" t="n">
         <v>48</v>
       </c>
       <c r="AF58" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG58" t="n">
         <v>14.5</v>
@@ -15171,7 +15171,7 @@
         <v>70</v>
       </c>
       <c r="AJ58" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK58" t="n">
         <v>42</v>
@@ -15180,7 +15180,7 @@
         <v>65</v>
       </c>
       <c r="AM58" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN58" t="n">
         <v>46</v>
@@ -15189,55 +15189,55 @@
         <v>55</v>
       </c>
       <c r="AP58" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ58" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR58" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AS58" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW58" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT58" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AX58" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AY58" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="AZ58" t="n">
-        <v>4.3</v>
+        <v>19</v>
       </c>
       <c r="BA58" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB58" t="n">
         <v>4.7</v>
       </c>
       <c r="BC58" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE58" t="n">
         <v>5</v>
       </c>
       <c r="BF58" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG58" t="n">
         <v>4.7</v>
@@ -15246,19 +15246,19 @@
         <v>3.05</v>
       </c>
       <c r="BI58" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ58" t="n">
         <v>11</v>
       </c>
       <c r="BK58" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL58" t="n">
         <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BN58" t="n">
         <v>5.9</v>
@@ -15276,7 +15276,7 @@
         <v>46</v>
       </c>
       <c r="BS58" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BT58" t="n">
         <v>6.4</v>
@@ -15285,7 +15285,7 @@
         <v>3.75</v>
       </c>
       <c r="BV58" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW58" t="n">
         <v>2.12</v>
@@ -15300,11 +15300,11 @@
         <v>44</v>
       </c>
       <c r="CA58" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
         <v>3.55</v>
       </c>
       <c r="L59" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M59" t="n">
         <v>1.1</v>
@@ -15374,7 +15374,7 @@
         <v>1.24</v>
       </c>
       <c r="S59" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="T59" t="n">
         <v>1.91</v>
@@ -15383,7 +15383,7 @@
         <v>1.89</v>
       </c>
       <c r="V59" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W59" t="n">
         <v>1.65</v>
@@ -15398,7 +15398,7 @@
         <v>29</v>
       </c>
       <c r="AA59" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB59" t="n">
         <v>9.6</v>
@@ -15425,7 +15425,7 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK59" t="n">
         <v>34</v>
@@ -15434,7 +15434,7 @@
         <v>60</v>
       </c>
       <c r="AM59" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN59" t="n">
         <v>32</v>
@@ -15482,25 +15482,25 @@
         <v>4.5</v>
       </c>
       <c r="BC59" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD59" t="n">
         <v>4.7</v>
       </c>
       <c r="BE59" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF59" t="n">
         <v>20</v>
       </c>
       <c r="BG59" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH59" t="n">
         <v>3.1</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="BJ59" t="n">
         <v>11</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -15592,16 +15592,16 @@
         <v>2.16</v>
       </c>
       <c r="G60" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H60" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I60" t="n">
         <v>4.4</v>
       </c>
       <c r="J60" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K60" t="n">
         <v>3.35</v>
@@ -15616,19 +15616,19 @@
         <v>2.62</v>
       </c>
       <c r="O60" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P60" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R60" t="n">
         <v>1.2</v>
       </c>
       <c r="S60" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T60" t="n">
         <v>2.02</v>
@@ -15652,7 +15652,7 @@
         <v>32</v>
       </c>
       <c r="AA60" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB60" t="n">
         <v>8.6</v>
@@ -15664,10 +15664,10 @@
         <v>20</v>
       </c>
       <c r="AE60" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF60" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG60" t="n">
         <v>13.5</v>
@@ -15676,7 +15676,7 @@
         <v>26</v>
       </c>
       <c r="AI60" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ60" t="n">
         <v>38</v>
@@ -15688,16 +15688,16 @@
         <v>70</v>
       </c>
       <c r="AM60" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN60" t="n">
         <v>36</v>
       </c>
       <c r="AO60" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP60" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ60" t="n">
         <v>8.6</v>
@@ -15706,7 +15706,7 @@
         <v>20</v>
       </c>
       <c r="AS60" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT60" t="n">
         <v>5.8</v>
@@ -15718,7 +15718,7 @@
         <v>13</v>
       </c>
       <c r="AW60" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX60" t="n">
         <v>10</v>
@@ -15730,55 +15730,55 @@
         <v>17</v>
       </c>
       <c r="BA60" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD60" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE60" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG60" t="n">
         <v>5</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG60" t="n">
-        <v>4.9</v>
       </c>
       <c r="BH60" t="n">
         <v>2.88</v>
       </c>
       <c r="BI60" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ60" t="n">
         <v>11.5</v>
       </c>
       <c r="BK60" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL60" t="n">
         <v>1000</v>
       </c>
       <c r="BM60" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN60" t="n">
         <v>5.1</v>
       </c>
       <c r="BO60" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP60" t="n">
         <v>20</v>
       </c>
       <c r="BQ60" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR60" t="n">
         <v>1000</v>
@@ -15796,7 +15796,7 @@
         <v>1000</v>
       </c>
       <c r="BW60" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G61" t="n">
         <v>2.08</v>
@@ -15906,7 +15906,7 @@
         <v>34</v>
       </c>
       <c r="AA61" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB61" t="n">
         <v>8.6</v>
@@ -15942,7 +15942,7 @@
         <v>42</v>
       </c>
       <c r="AM61" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AN61" t="n">
         <v>17</v>
@@ -16026,7 +16026,7 @@
         <v>4.9</v>
       </c>
       <c r="BO61" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP61" t="n">
         <v>15.5</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -16109,13 +16109,13 @@
         <v>5</v>
       </c>
       <c r="J62" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K62" t="n">
         <v>3.7</v>
       </c>
       <c r="L62" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M62" t="n">
         <v>1.08</v>
@@ -16124,7 +16124,7 @@
         <v>3.15</v>
       </c>
       <c r="O62" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P62" t="n">
         <v>1.76</v>
@@ -16139,28 +16139,28 @@
         <v>4</v>
       </c>
       <c r="T62" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U62" t="n">
         <v>1.92</v>
       </c>
       <c r="V62" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W62" t="n">
         <v>1.95</v>
       </c>
       <c r="X62" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y62" t="n">
         <v>17</v>
       </c>
       <c r="Z62" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AA62" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB62" t="n">
         <v>7.8</v>
@@ -16169,52 +16169,52 @@
         <v>7.8</v>
       </c>
       <c r="AD62" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AE62" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF62" t="n">
         <v>14</v>
       </c>
       <c r="AG62" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AH62" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI62" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ62" t="n">
-        <v>28</v>
+        <v>900</v>
       </c>
       <c r="AK62" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AL62" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM62" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN62" t="n">
         <v>22</v>
       </c>
       <c r="AO62" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP62" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AQ62" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AR62" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AS62" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT62" t="n">
         <v>6.8</v>
@@ -16223,43 +16223,43 @@
         <v>7</v>
       </c>
       <c r="AV62" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AW62" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ62" t="n">
         <v>5.4</v>
       </c>
-      <c r="AX62" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BA62" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB62" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC62" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD62" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE62" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF62" t="n">
         <v>12.5</v>
       </c>
       <c r="BG62" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH62" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI62" t="n">
         <v>2.6</v>
@@ -16292,35 +16292,35 @@
         <v>1000</v>
       </c>
       <c r="BS62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BT62" t="n">
         <v>10.5</v>
       </c>
       <c r="BU62" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV62" t="n">
         <v>1000</v>
       </c>
       <c r="BW62" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX62" t="n">
         <v>1000</v>
       </c>
       <c r="BY62" t="n">
-        <v>8.199999999999999</v>
+        <v>2.12</v>
       </c>
       <c r="BZ62" t="n">
         <v>1000</v>
       </c>
       <c r="CA62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -16459,7 +16459,7 @@
         <v>230</v>
       </c>
       <c r="AP63" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ63" t="n">
         <v>21</v>
@@ -16486,10 +16486,10 @@
         <v>7.2</v>
       </c>
       <c r="AY63" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ63" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BA63" t="n">
         <v>4.8</v>
@@ -16498,7 +16498,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BC63" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD63" t="n">
         <v>4.8</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -16859,31 +16859,31 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="G65" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H65" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I65" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J65" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K65" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L65" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M65" t="n">
         <v>1.11</v>
       </c>
       <c r="N65" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O65" t="n">
         <v>1.49</v>
@@ -16892,49 +16892,49 @@
         <v>1.54</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R65" t="n">
         <v>1.19</v>
       </c>
       <c r="S65" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T65" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U65" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V65" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W65" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="X65" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y65" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z65" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA65" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AB65" t="n">
         <v>7.8</v>
       </c>
       <c r="AC65" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD65" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE65" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF65" t="n">
         <v>12.5</v>
@@ -16943,10 +16943,10 @@
         <v>13.5</v>
       </c>
       <c r="AH65" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI65" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ65" t="n">
         <v>28</v>
@@ -16958,13 +16958,13 @@
         <v>70</v>
       </c>
       <c r="AM65" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN65" t="n">
         <v>27</v>
       </c>
       <c r="AO65" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP65" t="n">
         <v>6.8</v>
@@ -16973,13 +16973,13 @@
         <v>11</v>
       </c>
       <c r="AR65" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS65" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT65" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AU65" t="n">
         <v>5.8</v>
@@ -16988,10 +16988,10 @@
         <v>16</v>
       </c>
       <c r="AW65" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX65" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY65" t="n">
         <v>8.199999999999999</v>
@@ -17000,7 +17000,7 @@
         <v>21</v>
       </c>
       <c r="BA65" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB65" t="n">
         <v>19</v>
@@ -17009,19 +17009,19 @@
         <v>19</v>
       </c>
       <c r="BD65" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE65" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF65" t="n">
         <v>18.5</v>
       </c>
       <c r="BG65" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH65" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI65" t="n">
         <v>2.28</v>
@@ -17030,49 +17030,49 @@
         <v>12.5</v>
       </c>
       <c r="BK65" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL65" t="n">
         <v>1000</v>
       </c>
       <c r="BM65" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN65" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO65" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BQ65" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR65" t="n">
         <v>42</v>
       </c>
       <c r="BS65" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT65" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BU65" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BV65" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW65" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX65" t="n">
         <v>1000</v>
       </c>
       <c r="BY65" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ65" t="n">
         <v>0</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -857,28 +857,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="G2" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.31</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4.9</v>
@@ -887,16 +887,16 @@
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
         <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T2" t="n">
         <v>1.6</v>
@@ -905,10 +905,10 @@
         <v>2.58</v>
       </c>
       <c r="V2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -923,7 +923,7 @@
         <v>46</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
         <v>8.800000000000001</v>
@@ -935,10 +935,10 @@
         <v>30</v>
       </c>
       <c r="AF2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
         <v>16</v>
@@ -950,7 +950,7 @@
         <v>90</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
         <v>40</v>
@@ -959,7 +959,7 @@
         <v>190</v>
       </c>
       <c r="AN2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
         <v>19.5</v>
@@ -968,16 +968,16 @@
         <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
         <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
         <v>7.8</v>
@@ -989,7 +989,7 @@
         <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
@@ -998,16 +998,16 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
         <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE2" t="n">
         <v>42</v>
@@ -1016,7 +1016,7 @@
         <v>15.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH2" t="n">
         <v>4.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -1117,19 +1117,19 @@
         <v>3.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="I3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1141,7 +1141,7 @@
         <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
         <v>2.44</v>
@@ -1156,10 +1156,10 @@
         <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W3" t="n">
         <v>1.39</v>
@@ -1171,7 +1171,7 @@
         <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA3" t="n">
         <v>500</v>
@@ -1183,7 +1183,7 @@
         <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
         <v>40</v>
@@ -1192,10 +1192,10 @@
         <v>36</v>
       </c>
       <c r="AG3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
         <v>380</v>
@@ -1213,16 +1213,16 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
         <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>10.5</v>
@@ -1231,13 +1231,13 @@
         <v>23</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
         <v>20</v>
@@ -1249,22 +1249,22 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
         <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
         <v>9.800000000000001</v>
@@ -1276,7 +1276,7 @@
         <v>2.86</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
@@ -1312,7 +1312,7 @@
         <v>5.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BV3" t="n">
         <v>21</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="J4" t="n">
         <v>2.78</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1392,19 +1392,19 @@
         <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1416,7 +1416,7 @@
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1434,7 +1434,7 @@
         <v>500</v>
       </c>
       <c r="AC4" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
         <v>500</v>
@@ -1464,61 +1464,61 @@
         <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
         <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AU4" t="n">
         <v>4.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BF4" t="n">
         <v>5.7</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>3.9</v>
@@ -1643,7 +1643,7 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
         <v>1.46</v>
@@ -1652,19 +1652,19 @@
         <v>1.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R5" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
         <v>2.1</v>
@@ -1673,7 +1673,7 @@
         <v>1.16</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Y5" t="n">
         <v>6.8</v>
@@ -1685,7 +1685,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
         <v>14</v>
@@ -1703,7 +1703,7 @@
         <v>500</v>
       </c>
       <c r="AH5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1727,64 +1727,64 @@
         <v>85</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY5" t="n">
         <v>6</v>
       </c>
-      <c r="AY5" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.34</v>
+        <v>2.44</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
@@ -1808,19 +1808,19 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.32</v>
+        <v>2.38</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="BT5" t="n">
         <v>4.3</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.3</v>
+        <v>2.32</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
         <v>2.74</v>
@@ -1885,13 +1885,13 @@
         <v>2.82</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
@@ -1912,7 +1912,7 @@
         <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T6" t="n">
         <v>1.59</v>
@@ -1927,7 +1927,7 @@
         <v>1.6</v>
       </c>
       <c r="X6" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
         <v>15.5</v>
@@ -1942,7 +1942,7 @@
         <v>18.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
         <v>13</v>
@@ -1957,25 +1957,25 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="n">
         <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO6" t="n">
         <v>18</v>
@@ -1987,7 +1987,7 @@
         <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
         <v>28</v>
@@ -2002,7 +2002,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
         <v>17.5</v>
@@ -2014,7 +2014,7 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB6" t="n">
         <v>26</v>
@@ -2023,10 +2023,10 @@
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BF6" t="n">
         <v>14.5</v>
@@ -2035,7 +2035,7 @@
         <v>15.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI6" t="n">
         <v>3.15</v>
@@ -2044,13 +2044,13 @@
         <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
         <v>6</v>
@@ -2062,41 +2062,41 @@
         <v>18.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
         <v>6.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV6" t="n">
         <v>19.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
         <v>28</v>
       </c>
       <c r="BY6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>19.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
         <v>2.68</v>
@@ -2151,7 +2151,7 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
@@ -2160,7 +2160,7 @@
         <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
         <v>1.6</v>
@@ -2175,7 +2175,7 @@
         <v>2.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.59</v>
@@ -2205,13 +2205,13 @@
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -2238,13 +2238,13 @@
         <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR7" t="n">
         <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AT7" t="n">
         <v>9</v>
@@ -2268,10 +2268,10 @@
         <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BC7" t="n">
         <v>11.5</v>
@@ -2280,7 +2280,7 @@
         <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
         <v>9.800000000000001</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="H8" t="n">
         <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
         <v>2.94</v>
@@ -2405,28 +2405,28 @@
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="O8" t="n">
         <v>1.49</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
         <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
         <v>1.36</v>
@@ -2435,7 +2435,7 @@
         <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
@@ -2471,7 +2471,7 @@
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
         <v>500</v>
@@ -2483,67 +2483,67 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="AZ8" t="n">
         <v>3.15</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.35</v>
+        <v>2.76</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI8" t="n">
         <v>2.34</v>
@@ -2594,7 +2594,7 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K9" t="n">
         <v>3.45</v>
@@ -2659,13 +2659,13 @@
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O9" t="n">
         <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
         <v>2.38</v>
@@ -2677,7 +2677,7 @@
         <v>1.01</v>
       </c>
       <c r="T9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
         <v>1.82</v>
@@ -2707,13 +2707,13 @@
         <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
         <v>500</v>
@@ -2722,7 +2722,7 @@
         <v>500</v>
       </c>
       <c r="AI9" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AJ9" t="n">
         <v>900</v>
@@ -2734,67 +2734,67 @@
         <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ9" t="n">
         <v>5.6</v>
       </c>
       <c r="AR9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS9" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.6</v>
       </c>
       <c r="AT9" t="n">
         <v>4.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AX9" t="n">
         <v>7</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AZ9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD9" t="n">
         <v>5.9</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BE9" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD9" t="n">
+      <c r="BF9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG9" t="n">
         <v>6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6.6</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
@@ -2919,16 +2919,16 @@
         <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.98</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -3155,13 +3155,13 @@
         <v>5.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
         <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
@@ -3170,13 +3170,13 @@
         <v>2.74</v>
       </c>
       <c r="O11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
         <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R11" t="n">
         <v>1.2</v>
@@ -3188,7 +3188,7 @@
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
         <v>1.23</v>
@@ -3242,13 +3242,13 @@
         <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>160</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
         <v>3.45</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H12" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.49</v>
@@ -3439,16 +3439,16 @@
         <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
         <v>11</v>
@@ -3460,7 +3460,7 @@
         <v>18.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
         <v>10.5</v>
@@ -3478,10 +3478,10 @@
         <v>19.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>60</v>
@@ -3502,19 +3502,19 @@
         <v>46</v>
       </c>
       <c r="AO12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AT12" t="n">
         <v>8.4</v>
@@ -3526,7 +3526,7 @@
         <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
@@ -3535,25 +3535,25 @@
         <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BB12" t="n">
         <v>36</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BD12" t="n">
         <v>40</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BG12" t="n">
         <v>32</v>
@@ -3562,19 +3562,19 @@
         <v>3.05</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN12" t="n">
         <v>6</v>
@@ -3586,16 +3586,16 @@
         <v>26</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR12" t="n">
         <v>44</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU12" t="n">
         <v>4.3</v>
@@ -3610,17 +3610,17 @@
         <v>44</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>42</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>2.16</v>
       </c>
       <c r="G13" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="H13" t="n">
         <v>3.2</v>
@@ -3666,7 +3666,7 @@
         <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.41</v>
@@ -3702,7 +3702,7 @@
         <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="X13" t="n">
         <v>500</v>
@@ -3753,10 +3753,10 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
         <v>5.8</v>
@@ -3768,19 +3768,19 @@
         <v>5.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AT13" t="n">
         <v>5.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
         <v>5</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AX13" t="n">
         <v>7.6</v>
@@ -3792,19 +3792,19 @@
         <v>5.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BC13" t="n">
         <v>5.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BF13" t="n">
         <v>6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.23</v>
@@ -3932,22 +3932,22 @@
         <v>6.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U14" t="n">
         <v>2.34</v>
@@ -3962,7 +3962,7 @@
         <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Z14" t="n">
         <v>270</v>
@@ -3977,13 +3977,13 @@
         <v>15</v>
       </c>
       <c r="AD14" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AE14" t="n">
         <v>240</v>
       </c>
       <c r="AF14" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
         <v>12</v>
@@ -3995,10 +3995,10 @@
         <v>180</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AL14" t="n">
         <v>500</v>
@@ -4007,22 +4007,22 @@
         <v>260</v>
       </c>
       <c r="AN14" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AO14" t="n">
         <v>65</v>
       </c>
       <c r="AP14" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -4031,22 +4031,22 @@
         <v>10.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX14" t="n">
         <v>9.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB14" t="n">
         <v>12</v>
@@ -4058,77 +4058,77 @@
         <v>18</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
         <v>4.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN14" t="n">
         <v>4.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT14" t="n">
         <v>11</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>8</v>
-      </c>
       <c r="BZ14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.92</v>
       </c>
       <c r="G15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H15" t="n">
         <v>4.3</v>
@@ -4207,7 +4207,7 @@
         <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
         <v>2.02</v>
@@ -4231,7 +4231,7 @@
         <v>9</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE15" t="n">
         <v>110</v>
@@ -4258,7 +4258,7 @@
         <v>50</v>
       </c>
       <c r="AM15" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
         <v>10.5</v>
@@ -4273,10 +4273,10 @@
         <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AS15" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AT15" t="n">
         <v>10</v>
@@ -4303,22 +4303,22 @@
         <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE15" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BF15" t="n">
         <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BH15" t="n">
         <v>3.95</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -4413,31 +4413,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
@@ -4446,31 +4446,31 @@
         <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
         <v>1.71</v>
       </c>
       <c r="U16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V16" t="n">
         <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X16" t="n">
         <v>50</v>
       </c>
       <c r="Y16" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="Z16" t="n">
         <v>420</v>
@@ -4479,13 +4479,13 @@
         <v>210</v>
       </c>
       <c r="AB16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AE16" t="n">
         <v>480</v>
@@ -4494,7 +4494,7 @@
         <v>11</v>
       </c>
       <c r="AG16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
         <v>36</v>
@@ -4521,16 +4521,16 @@
         <v>200</v>
       </c>
       <c r="AP16" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
         <v>9.199999999999999</v>
@@ -4539,46 +4539,46 @@
         <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BH16" t="n">
         <v>4.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -4670,40 +4670,40 @@
         <v>4.6</v>
       </c>
       <c r="G17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H17" t="n">
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K17" t="n">
         <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M17" t="n">
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S17" t="n">
         <v>2.36</v>
@@ -4712,13 +4712,13 @@
         <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
         <v>500</v>
@@ -4751,7 +4751,7 @@
         <v>500</v>
       </c>
       <c r="AH17" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI17" t="n">
         <v>500</v>
@@ -4772,10 +4772,10 @@
         <v>700</v>
       </c>
       <c r="AO17" t="n">
-        <v>8.6</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ17" t="n">
         <v>7</v>
@@ -4784,10 +4784,10 @@
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
@@ -4799,7 +4799,7 @@
         <v>9</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AY17" t="n">
         <v>10.5</v>
@@ -4808,19 +4808,19 @@
         <v>9</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="BF17" t="n">
         <v>5.8</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -4927,13 +4927,13 @@
         <v>6.2</v>
       </c>
       <c r="H18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="I18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
@@ -4951,25 +4951,25 @@
         <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
         <v>2.04</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="W18" t="n">
         <v>1.19</v>
@@ -4978,7 +4978,7 @@
         <v>25</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
         <v>20</v>
@@ -4993,7 +4993,7 @@
         <v>14</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>500</v>
@@ -5026,7 +5026,7 @@
         <v>130</v>
       </c>
       <c r="AO18" t="n">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
         <v>10</v>
@@ -5038,7 +5038,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT18" t="n">
         <v>13.5</v>
@@ -5050,34 +5050,34 @@
         <v>8.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>17</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE18" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG18" t="n">
         <v>10</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -5175,58 +5175,58 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G19" t="n">
         <v>1.74</v>
       </c>
       <c r="H19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I19" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="J19" t="n">
         <v>3.75</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5241,10 +5241,10 @@
         <v>700</v>
       </c>
       <c r="AB19" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AC19" t="n">
-        <v>42</v>
+        <v>16.5</v>
       </c>
       <c r="AD19" t="n">
         <v>500</v>
@@ -5283,64 +5283,64 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU19" t="n">
         <v>4.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AX19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG19" t="n">
-        <v>2.52</v>
+        <v>1.79</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
@@ -5358,7 +5358,7 @@
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -5438,13 +5438,13 @@
         <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.18</v>
@@ -5453,7 +5453,7 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.12</v>
@@ -5462,7 +5462,7 @@
         <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R20" t="n">
         <v>1.88</v>
@@ -5561,10 +5561,10 @@
         <v>8.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>12.5</v>
@@ -5573,13 +5573,13 @@
         <v>8.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BC20" t="n">
         <v>10.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BE20" t="n">
         <v>8.4</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -5683,28 +5683,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="I21" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J21" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.49</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N21" t="n">
         <v>2.72</v>
@@ -5713,7 +5713,7 @@
         <v>1.47</v>
       </c>
       <c r="P21" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q21" t="n">
         <v>2.38</v>
@@ -5722,7 +5722,7 @@
         <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
         <v>1.94</v>
@@ -5731,13 +5731,13 @@
         <v>1.83</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y21" t="n">
         <v>9</v>
@@ -5761,7 +5761,7 @@
         <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AG21" t="n">
         <v>26</v>
@@ -5773,7 +5773,7 @@
         <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK21" t="n">
         <v>500</v>
@@ -5791,7 +5791,7 @@
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ21" t="n">
         <v>6.6</v>
@@ -5800,7 +5800,7 @@
         <v>12.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
         <v>7.6</v>
@@ -5824,25 +5824,25 @@
         <v>15.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF21" t="n">
         <v>8</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH21" t="n">
         <v>3.05</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H22" t="n">
         <v>3.35</v>
       </c>
       <c r="I22" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J22" t="n">
         <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -5964,7 +5964,7 @@
         <v>3.95</v>
       </c>
       <c r="O22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
@@ -5985,13 +5985,13 @@
         <v>2.26</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X22" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="Y22" t="n">
         <v>970</v>
@@ -6015,7 +6015,7 @@
         <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
@@ -6039,22 +6039,22 @@
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AO22" t="n">
         <v>500</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="AQ22" t="n">
         <v>10.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT22" t="n">
         <v>8.800000000000001</v>
@@ -6066,7 +6066,7 @@
         <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
@@ -6078,25 +6078,25 @@
         <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH22" t="n">
         <v>3.6</v>
@@ -6114,13 +6114,13 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.41</v>
+        <v>10</v>
       </c>
       <c r="BN22" t="n">
         <v>5.3</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G23" t="n">
         <v>4.6</v>
       </c>
       <c r="H23" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="J23" t="n">
         <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L23" t="n">
         <v>1.38</v>
@@ -6239,10 +6239,10 @@
         <v>1.96</v>
       </c>
       <c r="V23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X23" t="n">
         <v>13</v>
@@ -6314,7 +6314,7 @@
         <v>11.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
         <v>7.6</v>
@@ -6356,7 +6356,7 @@
         <v>3.25</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6368,7 +6368,7 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="BN23" t="n">
         <v>7.6</v>
@@ -6380,7 +6380,7 @@
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
@@ -6410,11 +6410,11 @@
         <v>32</v>
       </c>
       <c r="CA23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -6454,13 +6454,13 @@
         <v>3.6</v>
       </c>
       <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
         <v>4.1</v>
       </c>
-      <c r="J24" t="n">
-        <v>4.2</v>
-      </c>
       <c r="K24" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.22</v>
@@ -6475,19 +6475,19 @@
         <v>1.15</v>
       </c>
       <c r="P24" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R24" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="S24" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T24" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U24" t="n">
         <v>2.68</v>
@@ -6502,16 +6502,16 @@
         <v>32</v>
       </c>
       <c r="Y24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z24" t="n">
         <v>36</v>
       </c>
       <c r="AA24" t="n">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="AB24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC24" t="n">
         <v>11.5</v>
@@ -6547,61 +6547,61 @@
         <v>55</v>
       </c>
       <c r="AN24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AP24" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
         <v>20</v>
       </c>
       <c r="AR24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY24" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BB24" t="n">
         <v>19.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG24" t="n">
         <v>19.5</v>
@@ -6640,7 +6640,7 @@
         <v>20</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT24" t="n">
         <v>8</v>
@@ -6658,7 +6658,7 @@
         <v>29</v>
       </c>
       <c r="BY24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ24" t="n">
         <v>13</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G25" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H25" t="n">
         <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
         <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L25" t="n">
         <v>1.44</v>
@@ -6744,22 +6744,22 @@
         <v>1.87</v>
       </c>
       <c r="U25" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>1.26</v>
       </c>
       <c r="W25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X25" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="n">
         <v>16</v>
       </c>
       <c r="Z25" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
@@ -6768,7 +6768,7 @@
         <v>9.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
         <v>21</v>
@@ -6780,10 +6780,10 @@
         <v>14</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AI25" t="n">
         <v>500</v>
@@ -6792,16 +6792,16 @@
         <v>900</v>
       </c>
       <c r="AK25" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL25" t="n">
         <v>500</v>
       </c>
       <c r="AM25" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AO25" t="n">
         <v>500</v>
@@ -6813,10 +6813,10 @@
         <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AT25" t="n">
         <v>7</v>
@@ -6828,10 +6828,10 @@
         <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY25" t="n">
         <v>8.199999999999999</v>
@@ -6840,7 +6840,7 @@
         <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BB25" t="n">
         <v>19</v>
@@ -6849,16 +6849,16 @@
         <v>18</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BF25" t="n">
         <v>14</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BH25" t="n">
         <v>3.25</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G26" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H26" t="n">
         <v>3.35</v>
       </c>
       <c r="I26" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J26" t="n">
         <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.31</v>
@@ -7001,34 +7001,34 @@
         <v>2.24</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W26" t="n">
         <v>1.79</v>
       </c>
       <c r="X26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y26" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AA26" t="n">
-        <v>900</v>
+        <v>280</v>
       </c>
       <c r="AB26" t="n">
         <v>13</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AF26" t="n">
         <v>17</v>
@@ -7037,10 +7037,10 @@
         <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ26" t="n">
         <v>29</v>
@@ -7052,7 +7052,7 @@
         <v>38</v>
       </c>
       <c r="AM26" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
         <v>16</v>
@@ -7070,7 +7070,7 @@
         <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AT26" t="n">
         <v>8.4</v>
@@ -7082,7 +7082,7 @@
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AX26" t="n">
         <v>11</v>
@@ -7094,7 +7094,7 @@
         <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB26" t="n">
         <v>20</v>
@@ -7103,16 +7103,16 @@
         <v>16</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BF26" t="n">
         <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH26" t="n">
         <v>3.9</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -7210,19 +7210,19 @@
         <v>2.2</v>
       </c>
       <c r="G27" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H27" t="n">
         <v>3.1</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.26</v>
@@ -7240,7 +7240,7 @@
         <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R27" t="n">
         <v>1.54</v>
@@ -7255,7 +7255,7 @@
         <v>2.58</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
         <v>1.74</v>
@@ -7306,7 +7306,7 @@
         <v>36</v>
       </c>
       <c r="AM27" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN27" t="n">
         <v>15</v>
@@ -7324,7 +7324,7 @@
         <v>18</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT27" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -7348,19 +7348,19 @@
         <v>11</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="BC27" t="n">
         <v>19</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF27" t="n">
         <v>9.4</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G28" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H28" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I28" t="n">
         <v>3.1</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K28" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.49</v>
@@ -7509,13 +7509,13 @@
         <v>1.9</v>
       </c>
       <c r="V28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y28" t="n">
         <v>11.5</v>
@@ -7533,7 +7533,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
         <v>48</v>
@@ -7554,7 +7554,7 @@
         <v>55</v>
       </c>
       <c r="AK28" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL28" t="n">
         <v>70</v>
@@ -7566,10 +7566,10 @@
         <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>8</v>
@@ -7578,7 +7578,7 @@
         <v>15.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT28" t="n">
         <v>8.199999999999999</v>
@@ -7590,7 +7590,7 @@
         <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX28" t="n">
         <v>15.5</v>
@@ -7602,25 +7602,25 @@
         <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH28" t="n">
         <v>3.05</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -7721,46 +7721,46 @@
         <v>3.75</v>
       </c>
       <c r="H29" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I29" t="n">
         <v>2.42</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L29" t="n">
         <v>1.32</v>
       </c>
       <c r="M29" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
         <v>1.26</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U29" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V29" t="n">
         <v>1.7</v>
@@ -7814,67 +7814,67 @@
         <v>500</v>
       </c>
       <c r="AM29" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
         <v>500</v>
       </c>
       <c r="AO29" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU29" t="n">
         <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="BC29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG29" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>4.2</v>
       </c>
       <c r="BH29" t="n">
         <v>3.75</v>
@@ -7916,7 +7916,7 @@
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
@@ -7928,7 +7928,7 @@
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>2.06</v>
+        <v>8</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -7972,10 +7972,10 @@
         <v>3.15</v>
       </c>
       <c r="G30" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H30" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I30" t="n">
         <v>3.1</v>
@@ -7996,10 +7996,10 @@
         <v>2.12</v>
       </c>
       <c r="O30" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="P30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q30" t="n">
         <v>3.3</v>
@@ -8014,7 +8014,7 @@
         <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V30" t="n">
         <v>1.48</v>
@@ -8023,7 +8023,7 @@
         <v>1.38</v>
       </c>
       <c r="X30" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
         <v>7.4</v>
@@ -8035,13 +8035,13 @@
         <v>500</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC30" t="n">
         <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE30" t="n">
         <v>500</v>
@@ -8056,7 +8056,7 @@
         <v>500</v>
       </c>
       <c r="AI30" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ30" t="n">
         <v>500</v>
@@ -8065,7 +8065,7 @@
         <v>500</v>
       </c>
       <c r="AL30" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM30" t="n">
         <v>500</v>
@@ -8080,13 +8080,13 @@
         <v>5.1</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT30" t="n">
         <v>6.2</v>
@@ -8095,40 +8095,40 @@
         <v>5.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AY30" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BB30" t="n">
         <v>5.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.7</v>
+        <v>3.05</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH30" t="n">
         <v>2.38</v>
@@ -8152,7 +8152,7 @@
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -8223,49 +8223,49 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G31" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="H31" t="n">
         <v>4.6</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K31" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L31" t="n">
         <v>1.26</v>
       </c>
       <c r="M31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
         <v>1.21</v>
       </c>
       <c r="P31" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R31" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S31" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="T31" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U31" t="n">
         <v>2.32</v>
@@ -8274,40 +8274,40 @@
         <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="X31" t="n">
         <v>27</v>
       </c>
       <c r="Y31" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Z31" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA31" t="n">
         <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AC31" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AE31" t="n">
         <v>700</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AG31" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH31" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AI31" t="n">
         <v>700</v>
@@ -8316,13 +8316,13 @@
         <v>23</v>
       </c>
       <c r="AK31" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
         <v>9.4</v>
@@ -8334,34 +8334,34 @@
         <v>18</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR31" t="n">
         <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV31" t="n">
         <v>13.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA31" t="n">
         <v>26</v>
@@ -8376,77 +8376,77 @@
         <v>17.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF31" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI31" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ31" t="n">
         <v>9.6</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP31" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT31" t="n">
         <v>9</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA31" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8540,7 @@
         <v>29</v>
       </c>
       <c r="AA32" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB32" t="n">
         <v>8.199999999999999</v>
@@ -8558,7 +8558,7 @@
         <v>16</v>
       </c>
       <c r="AG32" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH32" t="n">
         <v>28</v>
@@ -8582,7 +8582,7 @@
         <v>50</v>
       </c>
       <c r="AO32" t="n">
-        <v>95</v>
+        <v>390</v>
       </c>
       <c r="AP32" t="n">
         <v>7.4</v>
@@ -8594,7 +8594,7 @@
         <v>19</v>
       </c>
       <c r="AS32" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT32" t="n">
         <v>6.6</v>
@@ -8606,7 +8606,7 @@
         <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX32" t="n">
         <v>12.5</v>
@@ -8618,25 +8618,25 @@
         <v>19</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB32" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC32" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH32" t="n">
         <v>2.8</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -8734,19 +8734,19 @@
         <v>1.95</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H33" t="n">
         <v>4.9</v>
       </c>
       <c r="I33" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K33" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L33" t="n">
         <v>1.62</v>
@@ -8779,16 +8779,16 @@
         <v>1.57</v>
       </c>
       <c r="V33" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W33" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="X33" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
         <v>500</v>
@@ -8809,13 +8809,13 @@
         <v>700</v>
       </c>
       <c r="AF33" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG33" t="n">
         <v>36</v>
       </c>
       <c r="AH33" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AI33" t="n">
         <v>700</v>
@@ -8824,7 +8824,7 @@
         <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AL33" t="n">
         <v>500</v>
@@ -8842,13 +8842,13 @@
         <v>6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT33" t="n">
         <v>5.1</v>
@@ -8860,40 +8860,40 @@
         <v>18</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX33" t="n">
         <v>8.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB33" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>6</v>
       </c>
       <c r="BC33" t="n">
         <v>22</v>
       </c>
       <c r="BD33" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE33" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF33" t="n">
         <v>20</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH33" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BI33" t="n">
         <v>2.14</v>
@@ -8902,19 +8902,19 @@
         <v>14</v>
       </c>
       <c r="BK33" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN33" t="n">
         <v>4.5</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP33" t="n">
         <v>970</v>
@@ -8926,7 +8926,7 @@
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT33" t="n">
         <v>9.4</v>
@@ -8938,23 +8938,23 @@
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G34" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H34" t="n">
         <v>2.88</v>
@@ -9003,7 +9003,7 @@
         <v>4.6</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M34" t="n">
         <v>1.02</v>
@@ -9036,7 +9036,7 @@
         <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X34" t="n">
         <v>38</v>
@@ -9048,7 +9048,7 @@
         <v>36</v>
       </c>
       <c r="AA34" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AB34" t="n">
         <v>19.5</v>
@@ -9147,13 +9147,13 @@
         <v>12.5</v>
       </c>
       <c r="BH34" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK34" t="n">
         <v>1.01</v>
@@ -9165,50 +9165,50 @@
         <v>1.01</v>
       </c>
       <c r="BN34" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ34" t="n">
         <v>1.01</v>
       </c>
       <c r="BR34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS34" t="n">
         <v>1.01</v>
       </c>
       <c r="BT34" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW34" t="n">
         <v>1.01</v>
       </c>
       <c r="BX34" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY34" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA34" t="n">
         <v>1.01</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
         <v>3.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R35" t="n">
         <v>1.97</v>
@@ -9344,7 +9344,7 @@
         <v>24</v>
       </c>
       <c r="AO35" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AP35" t="n">
         <v>30</v>
@@ -9359,7 +9359,7 @@
         <v>17</v>
       </c>
       <c r="AT35" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU35" t="n">
         <v>9.800000000000001</v>
@@ -9371,7 +9371,7 @@
         <v>12.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY35" t="n">
         <v>14.5</v>
@@ -9386,13 +9386,13 @@
         <v>5.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF35" t="n">
         <v>16</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -9493,22 +9493,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G36" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H36" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="I36" t="n">
         <v>3.15</v>
       </c>
       <c r="J36" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K36" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L36" t="n">
         <v>1.17</v>
@@ -9517,10 +9517,10 @@
         <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P36" t="n">
         <v>3.45</v>
@@ -9541,16 +9541,16 @@
         <v>3.25</v>
       </c>
       <c r="V36" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W36" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X36" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Y36" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z36" t="n">
         <v>34</v>
@@ -9559,10 +9559,10 @@
         <v>55</v>
       </c>
       <c r="AB36" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AC36" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AD36" t="n">
         <v>18</v>
@@ -9580,7 +9580,7 @@
         <v>14.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AJ36" t="n">
         <v>34</v>
@@ -9592,22 +9592,22 @@
         <v>24</v>
       </c>
       <c r="AM36" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AN36" t="n">
         <v>7.8</v>
       </c>
       <c r="AO36" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ36" t="n">
         <v>21</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="AS36" t="n">
         <v>36</v>
@@ -9622,7 +9622,7 @@
         <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX36" t="n">
         <v>18</v>
@@ -9637,7 +9637,7 @@
         <v>21</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC36" t="n">
         <v>15</v>
@@ -9646,7 +9646,7 @@
         <v>17</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="BF36" t="n">
         <v>6.4</v>
@@ -9658,7 +9658,7 @@
         <v>6.2</v>
       </c>
       <c r="BI36" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BJ36" t="n">
         <v>8.4</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         <v>500</v>
       </c>
       <c r="AH37" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI37" t="n">
         <v>500</v>
@@ -9846,61 +9846,61 @@
         <v>500</v>
       </c>
       <c r="AM37" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN37" t="n">
-        <v>970</v>
+        <v>250</v>
       </c>
       <c r="AO37" t="n">
         <v>4.7</v>
       </c>
       <c r="AP37" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ37" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR37" t="n">
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT37" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU37" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AV37" t="n">
         <v>10</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD37" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY37" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE37" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF37" t="n">
         <v>11.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -10004,10 +10004,10 @@
         <v>1.21</v>
       </c>
       <c r="G38" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I38" t="n">
         <v>1000</v>
@@ -10025,25 +10025,25 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="O38" t="n">
         <v>1.29</v>
       </c>
       <c r="P38" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="R38" t="n">
         <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U38" t="n">
         <v>1.23</v>
@@ -10052,7 +10052,7 @@
         <v>1.06</v>
       </c>
       <c r="W38" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10103,64 +10103,64 @@
         <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO38" t="n">
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF38" t="n">
         <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -10246,175 +10246,175 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="G39" t="n">
-        <v>3.75</v>
+        <v>1.87</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>500</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M39" t="n">
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.24</v>
+        <v>1.58</v>
       </c>
       <c r="O39" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="P39" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="R39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T39" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U39" t="n">
         <v>1.11</v>
       </c>
       <c r="V39" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>970</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
         <v>970</v>
       </c>
-      <c r="Z39" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>500</v>
-      </c>
       <c r="AO39" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BB39" t="n">
         <v>1.03</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -10509,22 +10509,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G40" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="I40" t="n">
-        <v>870</v>
+        <v>5.3</v>
       </c>
       <c r="J40" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="K40" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -10533,13 +10533,13 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="P40" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Q40" t="n">
         <v>1.55</v>
@@ -10551,7 +10551,7 @@
         <v>1.55</v>
       </c>
       <c r="T40" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="U40" t="n">
         <v>1.11</v>
@@ -10617,58 +10617,58 @@
         <v>500</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -10769,7 +10769,7 @@
         <v>32</v>
       </c>
       <c r="H41" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I41" t="n">
         <v>2.12</v>
@@ -10787,13 +10787,13 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="O41" t="n">
         <v>1.43</v>
       </c>
       <c r="P41" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Q41" t="n">
         <v>1.46</v>
@@ -10832,7 +10832,7 @@
         <v>1000</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD41" t="n">
         <v>970</v>
@@ -10871,58 +10871,58 @@
         <v>500</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -11017,16 +11017,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G42" t="n">
         <v>1000</v>
       </c>
       <c r="H42" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J42" t="n">
         <v>2.4</v>
@@ -11041,13 +11041,13 @@
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O42" t="n">
         <v>1.07</v>
       </c>
       <c r="P42" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q42" t="n">
         <v>2.06</v>
@@ -11059,10 +11059,10 @@
         <v>2.06</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
         <v>1.47</v>
@@ -11125,58 +11125,58 @@
         <v>500</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -11262,46 +11262,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G43" t="n">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="I43" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="K43" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L43" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="O43" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="P43" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="Q43" t="n">
         <v>1.44</v>
@@ -11310,19 +11310,19 @@
         <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11340,7 +11340,7 @@
         <v>970</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD43" t="n">
         <v>1000</v>
@@ -11361,7 +11361,7 @@
         <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK43" t="n">
         <v>500</v>
@@ -11373,64 +11373,64 @@
         <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AO43" t="n">
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -11516,67 +11516,67 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G44" t="n">
-        <v>6.2</v>
+        <v>2.28</v>
       </c>
       <c r="H44" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="K44" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M44" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N44" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="O44" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P44" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="R44" t="n">
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="V44" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="W44" t="n">
-        <v>1.2</v>
+        <v>1.84</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11594,7 +11594,7 @@
         <v>970</v>
       </c>
       <c r="AC44" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD44" t="n">
         <v>1000</v>
@@ -11615,7 +11615,7 @@
         <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK44" t="n">
         <v>500</v>
@@ -11627,64 +11627,64 @@
         <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AO44" t="n">
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -11770,175 +11770,175 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="G45" t="n">
-        <v>1.87</v>
+        <v>3.9</v>
       </c>
       <c r="H45" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="I45" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="K45" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L45" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="n">
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X45" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>540</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR45" t="n">
         <v>1.58</v>
       </c>
-      <c r="O45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W45" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AS45" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -12036,10 +12036,10 @@
         <v>1.7</v>
       </c>
       <c r="G46" t="n">
-        <v>100</v>
+        <v>7.8</v>
       </c>
       <c r="H46" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="I46" t="n">
         <v>1000</v>
@@ -12084,7 +12084,7 @@
         <v>1.19</v>
       </c>
       <c r="W46" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="X46" t="n">
         <v>500</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="K47" t="n">
         <v>1000</v>
@@ -12311,16 +12311,16 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P47" t="n">
         <v>1.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="R47" t="n">
         <v>1.12</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
         <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="K49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -13058,13 +13058,13 @@
         <v>3.15</v>
       </c>
       <c r="I50" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J50" t="n">
         <v>2.58</v>
       </c>
       <c r="K50" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L50" t="n">
         <v>1.5</v>
@@ -13082,13 +13082,13 @@
         <v>1.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R50" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S50" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="T50" t="n">
         <v>2.12</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -13605,10 +13605,10 @@
         <v>1.11</v>
       </c>
       <c r="V52" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W52" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X52" t="n">
         <v>500</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -14110,7 +14110,7 @@
         <v>2.2</v>
       </c>
       <c r="U54" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V54" t="n">
         <v>1.28</v>
@@ -14248,7 +14248,7 @@
         <v>4.7</v>
       </c>
       <c r="BO54" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP54" t="n">
         <v>17.5</v>
@@ -14266,7 +14266,7 @@
         <v>7.4</v>
       </c>
       <c r="BU54" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G55" t="n">
         <v>2.12</v>
@@ -14328,13 +14328,13 @@
         <v>4.3</v>
       </c>
       <c r="I55" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J55" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K55" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L55" t="n">
         <v>1.45</v>
@@ -14364,7 +14364,7 @@
         <v>2.08</v>
       </c>
       <c r="U55" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V55" t="n">
         <v>1.26</v>
@@ -14421,70 +14421,70 @@
         <v>500</v>
       </c>
       <c r="AN55" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AO55" t="n">
         <v>500</v>
       </c>
       <c r="AP55" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AQ55" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR55" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AS55" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT55" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AU55" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV55" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW55" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX55" t="n">
         <v>10</v>
       </c>
       <c r="AY55" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AZ55" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="BB55" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC55" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BD55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE55" t="n">
         <v>3.95</v>
       </c>
-      <c r="BE55" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF55" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG55" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="BH55" t="n">
         <v>2.9</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ55" t="n">
         <v>11</v>
@@ -14496,7 +14496,7 @@
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="BN55" t="n">
         <v>4.6</v>
@@ -14508,7 +14508,7 @@
         <v>1000</v>
       </c>
       <c r="BQ55" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR55" t="n">
         <v>1000</v>
@@ -14517,7 +14517,7 @@
         <v>2.32</v>
       </c>
       <c r="BT55" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU55" t="n">
         <v>6</v>
@@ -14526,13 +14526,13 @@
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="BZ55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -14588,10 +14588,10 @@
         <v>4.5</v>
       </c>
       <c r="K56" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L56" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M56" t="n">
         <v>1.07</v>
@@ -14738,22 +14738,22 @@
         <v>3.4</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BJ56" t="n">
         <v>12.5</v>
       </c>
       <c r="BK56" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN56" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BO56" t="n">
         <v>3</v>
@@ -14762,41 +14762,41 @@
         <v>9.4</v>
       </c>
       <c r="BQ56" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT56" t="n">
         <v>12.5</v>
       </c>
       <c r="BU56" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV56" t="n">
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ56" t="n">
         <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -15108,7 +15108,7 @@
         <v>2.72</v>
       </c>
       <c r="O58" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P58" t="n">
         <v>1.59</v>
@@ -15123,7 +15123,7 @@
         <v>4.5</v>
       </c>
       <c r="T58" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U58" t="n">
         <v>1.84</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -15344,7 +15344,7 @@
         <v>3.4</v>
       </c>
       <c r="I59" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
         <v>3.05</v>
@@ -15353,7 +15353,7 @@
         <v>3.55</v>
       </c>
       <c r="L59" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M59" t="n">
         <v>1.1</v>
@@ -15368,7 +15368,7 @@
         <v>1.65</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R59" t="n">
         <v>1.24</v>
@@ -15500,7 +15500,7 @@
         <v>3.1</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="BJ59" t="n">
         <v>11</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -15843,19 +15843,19 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G61" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H61" t="n">
         <v>4.1</v>
       </c>
       <c r="I61" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K61" t="n">
         <v>3.8</v>
@@ -15891,10 +15891,10 @@
         <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W61" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="X61" t="n">
         <v>14</v>
@@ -15903,7 +15903,7 @@
         <v>14</v>
       </c>
       <c r="Z61" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA61" t="n">
         <v>900</v>
@@ -15984,7 +15984,7 @@
         <v>17.5</v>
       </c>
       <c r="BA61" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB61" t="n">
         <v>21</v>
@@ -16014,7 +16014,7 @@
         <v>10.5</v>
       </c>
       <c r="BK61" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BL61" t="n">
         <v>1000</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G62" t="n">
         <v>2.06</v>
@@ -16115,13 +16115,13 @@
         <v>3.7</v>
       </c>
       <c r="L62" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M62" t="n">
         <v>1.08</v>
       </c>
       <c r="N62" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O62" t="n">
         <v>1.4</v>
@@ -16133,7 +16133,7 @@
         <v>2.16</v>
       </c>
       <c r="R62" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -16145,10 +16145,10 @@
         <v>1.92</v>
       </c>
       <c r="V62" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W62" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X62" t="n">
         <v>14</v>
@@ -16175,7 +16175,7 @@
         <v>500</v>
       </c>
       <c r="AF62" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG62" t="n">
         <v>36</v>
@@ -16205,16 +16205,16 @@
         <v>500</v>
       </c>
       <c r="AP62" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ62" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AR62" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS62" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT62" t="n">
         <v>6.8</v>
@@ -16223,46 +16223,46 @@
         <v>7</v>
       </c>
       <c r="AV62" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AW62" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX62" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY62" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY62" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AZ62" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BA62" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB62" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC62" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BD62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE62" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF62" t="n">
         <v>12.5</v>
       </c>
       <c r="BG62" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BH62" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI62" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="BJ62" t="n">
         <v>15</v>
@@ -16274,10 +16274,10 @@
         <v>1000</v>
       </c>
       <c r="BM62" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="BN62" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO62" t="n">
         <v>4</v>
@@ -16295,10 +16295,10 @@
         <v>8</v>
       </c>
       <c r="BT62" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BU62" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV62" t="n">
         <v>1000</v>
@@ -16310,17 +16310,17 @@
         <v>1000</v>
       </c>
       <c r="BY62" t="n">
-        <v>2.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ62" t="n">
         <v>1000</v>
       </c>
       <c r="CA62" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -16366,40 +16366,40 @@
         <v>4.7</v>
       </c>
       <c r="K63" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L63" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M63" t="n">
         <v>1.04</v>
       </c>
       <c r="N63" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O63" t="n">
         <v>1.23</v>
       </c>
       <c r="P63" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R63" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S63" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T63" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U63" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V63" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W63" t="n">
         <v>3</v>
@@ -16417,7 +16417,7 @@
         <v>390</v>
       </c>
       <c r="AB63" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC63" t="n">
         <v>14</v>
@@ -16453,67 +16453,67 @@
         <v>180</v>
       </c>
       <c r="AN63" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO63" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AP63" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AQ63" t="n">
         <v>21</v>
       </c>
       <c r="AR63" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS63" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT63" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU63" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV63" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW63" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX63" t="n">
         <v>7.2</v>
       </c>
       <c r="AY63" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ63" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA63" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB63" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC63" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BD63" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE63" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF63" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG63" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH63" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI63" t="n">
         <v>3.05</v>
@@ -16531,16 +16531,16 @@
         <v>1.01</v>
       </c>
       <c r="BN63" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO63" t="n">
         <v>3.05</v>
       </c>
       <c r="BP63" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ63" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR63" t="n">
         <v>26</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -16605,46 +16605,46 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="G64" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="H64" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="I64" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J64" t="n">
         <v>3.4</v>
       </c>
       <c r="K64" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L64" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M64" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N64" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="O64" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="P64" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R64" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S64" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T64" t="n">
         <v>2</v>
@@ -16653,10 +16653,10 @@
         <v>1.65</v>
       </c>
       <c r="V64" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="W64" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="X64" t="n">
         <v>970</v>
@@ -16665,19 +16665,19 @@
         <v>970</v>
       </c>
       <c r="Z64" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA64" t="n">
         <v>1000</v>
       </c>
       <c r="AB64" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AC64" t="n">
         <v>970</v>
       </c>
       <c r="AD64" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AE64" t="n">
         <v>1000</v>
@@ -16689,16 +16689,16 @@
         <v>970</v>
       </c>
       <c r="AH64" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI64" t="n">
         <v>1000</v>
       </c>
       <c r="AJ64" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AK64" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AL64" t="n">
         <v>60</v>
@@ -16707,118 +16707,118 @@
         <v>1000</v>
       </c>
       <c r="AN64" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AO64" t="n">
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU64" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY64" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BF64" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG64" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BH64" t="n">
         <v>3.35</v>
       </c>
       <c r="BI64" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ64" t="n">
         <v>1000</v>
       </c>
       <c r="BK64" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BL64" t="n">
         <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="BN64" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO64" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BP64" t="n">
         <v>1000</v>
       </c>
       <c r="BQ64" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="BR64" t="n">
         <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="BT64" t="n">
         <v>1000</v>
       </c>
       <c r="BU64" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV64" t="n">
         <v>1000</v>
       </c>
       <c r="BW64" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY64" t="n">
         <v>1.46</v>
-      </c>
-      <c r="BX64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY64" t="n">
-        <v>1.47</v>
       </c>
       <c r="BZ64" t="n">
         <v>0</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -16871,7 +16871,7 @@
         <v>5.5</v>
       </c>
       <c r="J65" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K65" t="n">
         <v>3.6</v>
@@ -16925,22 +16925,22 @@
         <v>180</v>
       </c>
       <c r="AB65" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC65" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD65" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE65" t="n">
         <v>110</v>
       </c>
       <c r="AF65" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG65" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH65" t="n">
         <v>30</v>
@@ -16949,7 +16949,7 @@
         <v>130</v>
       </c>
       <c r="AJ65" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK65" t="n">
         <v>32</v>
@@ -16961,7 +16961,7 @@
         <v>250</v>
       </c>
       <c r="AN65" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO65" t="n">
         <v>180</v>
@@ -16973,22 +16973,22 @@
         <v>11</v>
       </c>
       <c r="AR65" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS65" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AT65" t="n">
         <v>5.1</v>
       </c>
       <c r="AU65" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV65" t="n">
         <v>16</v>
       </c>
       <c r="AW65" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX65" t="n">
         <v>8</v>
@@ -17000,7 +17000,7 @@
         <v>21</v>
       </c>
       <c r="BA65" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB65" t="n">
         <v>19</v>
@@ -17009,16 +17009,16 @@
         <v>19</v>
       </c>
       <c r="BD65" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BE65" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF65" t="n">
         <v>18.5</v>
       </c>
       <c r="BG65" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH65" t="n">
         <v>2.88</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G2" t="n">
         <v>2.9</v>
@@ -866,7 +866,7 @@
         <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
@@ -881,28 +881,28 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
         <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
         <v>1.61</v>
@@ -917,10 +917,10 @@
         <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB2" t="n">
         <v>16</v>
@@ -929,10 +929,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AF2" t="n">
         <v>22</v>
@@ -944,31 +944,31 @@
         <v>16</v>
       </c>
       <c r="AI2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
         <v>90</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
         <v>19</v>
       </c>
       <c r="AO2" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
         <v>17</v>
@@ -989,7 +989,7 @@
         <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
@@ -1007,7 +1007,7 @@
         <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
         <v>42</v>
@@ -1022,7 +1022,7 @@
         <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ2" t="n">
         <v>9</v>
@@ -1052,7 +1052,7 @@
         <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1064,23 +1064,23 @@
         <v>18</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX2" t="n">
         <v>26</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA2" t="n">
         <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
@@ -1135,13 +1135,13 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
         <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
         <v>2.44</v>
@@ -1156,16 +1156,16 @@
         <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
         <v>8</v>
@@ -1174,7 +1174,7 @@
         <v>16.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AB3" t="n">
         <v>13</v>
@@ -1198,16 +1198,16 @@
         <v>25</v>
       </c>
       <c r="AI3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AL3" t="n">
         <v>380</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>90</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
@@ -1219,16 +1219,16 @@
         <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
         <v>9.199999999999999</v>
@@ -1240,37 +1240,37 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX3" t="n">
         <v>20</v>
       </c>
-      <c r="AX3" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BG3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BH3" t="n">
         <v>2.86</v>
@@ -1324,17 +1324,17 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -1386,19 +1386,19 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
         <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
         <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1416,13 +1416,13 @@
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>500</v>
@@ -1431,25 +1431,25 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>42</v>
       </c>
       <c r="AD4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>500</v>
+        <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1467,7 +1467,7 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1476,55 +1476,55 @@
         <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.29</v>
+        <v>1.78</v>
       </c>
       <c r="AU4" t="n">
         <v>4.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.29</v>
+        <v>1.78</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.32</v>
+        <v>1.81</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="BF4" t="n">
         <v>5.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -1619,67 +1619,67 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="O5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="W5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
         <v>6.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1688,13 +1688,13 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AF5" t="n">
         <v>500</v>
@@ -1703,7 +1703,7 @@
         <v>500</v>
       </c>
       <c r="AH5" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1727,7 +1727,7 @@
         <v>85</v>
       </c>
       <c r="AP5" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.4</v>
@@ -1736,103 +1736,103 @@
         <v>7.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
         <v>5.3</v>
       </c>
-      <c r="AU5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.38</v>
+        <v>2.82</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="BT5" t="n">
         <v>4.3</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>2.74</v>
       </c>
       <c r="I6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
         <v>3.85</v>
@@ -1912,7 +1912,7 @@
         <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
         <v>1.59</v>
@@ -1921,7 +1921,7 @@
         <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
         <v>1.6</v>
@@ -1930,16 +1930,16 @@
         <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
         <v>80</v>
       </c>
       <c r="AB6" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AC6" t="n">
         <v>9</v>
@@ -1948,49 +1948,49 @@
         <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
         <v>80</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
         <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
         <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
@@ -2002,19 +2002,19 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AX6" t="n">
         <v>17.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BB6" t="n">
         <v>26</v>
@@ -2023,10 +2023,10 @@
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BF6" t="n">
         <v>14.5</v>
@@ -2038,10 +2038,10 @@
         <v>4.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BK6" t="n">
         <v>5.1</v>
@@ -2050,53 +2050,53 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
         <v>6</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP6" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT6" t="n">
         <v>6.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV6" t="n">
         <v>19.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY6" t="n">
         <v>28</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>8.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>19.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -2145,34 +2145,34 @@
         <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T7" t="n">
         <v>1.5</v>
       </c>
       <c r="U7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V7" t="n">
         <v>1.5</v>
@@ -2181,7 +2181,7 @@
         <v>1.59</v>
       </c>
       <c r="X7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="Y7" t="n">
         <v>500</v>
@@ -2193,7 +2193,7 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
@@ -2238,13 +2238,13 @@
         <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AR7" t="n">
         <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
         <v>9</v>
@@ -2268,10 +2268,10 @@
         <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
         <v>11.5</v>
@@ -2280,34 +2280,34 @@
         <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG7" t="n">
         <v>11.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.87</v>
+        <v>8.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO7" t="n">
         <v>4.5</v>
@@ -2316,16 +2316,16 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.78</v>
+        <v>6.8</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU7" t="n">
         <v>4.8</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.29</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
         <v>1.01</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U9" t="n">
         <v>1.82</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -2892,49 +2892,49 @@
         <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
         <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
         <v>1.18</v>
@@ -2943,10 +2943,10 @@
         <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="Z10" t="n">
         <v>120</v>
@@ -2976,7 +2976,7 @@
         <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>370</v>
+        <v>700</v>
       </c>
       <c r="AJ10" t="n">
         <v>19.5</v>
@@ -3000,13 +3000,13 @@
         <v>5.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
         <v>4.4</v>
@@ -3015,10 +3015,10 @@
         <v>4.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX10" t="n">
         <v>5.1</v>
@@ -3027,34 +3027,34 @@
         <v>7</v>
       </c>
       <c r="AZ10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB10" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ10" t="n">
         <v>11.5</v>
@@ -3066,7 +3066,7 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.3</v>
@@ -3081,10 +3081,10 @@
         <v>6.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BT10" t="n">
         <v>9.199999999999999</v>
@@ -3096,13 +3096,13 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>2.44</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>2.48</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
         <v>1.23</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -3403,67 +3403,67 @@
         <v>3.15</v>
       </c>
       <c r="H12" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P12" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U12" t="n">
         <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
         <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z12" t="n">
         <v>18.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC12" t="n">
         <v>7.6</v>
@@ -3472,16 +3472,16 @@
         <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
         <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>60</v>
@@ -3502,22 +3502,22 @@
         <v>46</v>
       </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ12" t="n">
         <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS12" t="n">
         <v>30</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU12" t="n">
         <v>6.2</v>
@@ -3526,7 +3526,7 @@
         <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
@@ -3538,46 +3538,46 @@
         <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
         <v>36</v>
       </c>
       <c r="BC12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BD12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BE12" t="n">
-        <v>44</v>
+        <v>9.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BG12" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO12" t="n">
         <v>4.4</v>
@@ -3586,41 +3586,41 @@
         <v>26</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT12" t="n">
         <v>5.9</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>44</v>
       </c>
-      <c r="BY12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>42</v>
-      </c>
       <c r="CA12" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -3651,58 +3651,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
         <v>2.44</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J13" t="n">
         <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
         <v>2.04</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
         <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X13" t="n">
         <v>500</v>
@@ -3717,7 +3717,7 @@
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
         <v>14</v>
@@ -3765,10 +3765,10 @@
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AT13" t="n">
         <v>5.6</v>
@@ -3777,10 +3777,10 @@
         <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="AX13" t="n">
         <v>7.6</v>
@@ -3789,34 +3789,34 @@
         <v>7.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB13" t="n">
         <v>3.1</v>
       </c>
-      <c r="BB13" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BC13" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="BF13" t="n">
         <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -3905,52 +3905,52 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M14" t="n">
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="R14" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
         <v>1.16</v>
@@ -3959,7 +3959,7 @@
         <v>2.76</v>
       </c>
       <c r="X14" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Y14" t="n">
         <v>95</v>
@@ -3968,25 +3968,25 @@
         <v>270</v>
       </c>
       <c r="AA14" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AB14" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AE14" t="n">
         <v>240</v>
       </c>
       <c r="AF14" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
         <v>36</v>
@@ -3995,10 +3995,10 @@
         <v>180</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AL14" t="n">
         <v>500</v>
@@ -4007,22 +4007,22 @@
         <v>260</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -4031,46 +4031,46 @@
         <v>10.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX14" t="n">
         <v>9.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC14" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BJ14" t="n">
         <v>10</v>
@@ -4082,22 +4082,22 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO14" t="n">
         <v>3.55</v>
       </c>
       <c r="BP14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ14" t="n">
         <v>4.8</v>
       </c>
       <c r="BR14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BS14" t="n">
         <v>6.6</v>
@@ -4121,14 +4121,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -4243,19 +4243,19 @@
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI15" t="n">
         <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AM15" t="n">
         <v>90</v>
@@ -4273,10 +4273,10 @@
         <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AS15" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AT15" t="n">
         <v>10</v>
@@ -4288,7 +4288,7 @@
         <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AX15" t="n">
         <v>11.5</v>
@@ -4300,19 +4300,19 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BB15" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
         <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF15" t="n">
         <v>9.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>1.48</v>
       </c>
       <c r="G16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.28</v>
@@ -4437,7 +4437,7 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
@@ -4446,37 +4446,37 @@
         <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U16" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V16" t="n">
         <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="X16" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="Z16" t="n">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="AA16" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
         <v>11</v>
@@ -4485,94 +4485,94 @@
         <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AE16" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH16" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>390</v>
+        <v>160</v>
       </c>
       <c r="AJ16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AM16" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO16" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU16" t="n">
         <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.4</v>
+        <v>60</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BB16" t="n">
         <v>12.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.4</v>
+        <v>60</v>
       </c>
       <c r="BH16" t="n">
         <v>4.7</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="J17" t="n">
         <v>4.3</v>
@@ -4715,7 +4715,7 @@
         <v>2.44</v>
       </c>
       <c r="V17" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.25</v>
@@ -4811,10 +4811,10 @@
         <v>7.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BC17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD17" t="n">
         <v>8.199999999999999</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="G18" t="n">
         <v>6.2</v>
@@ -4930,13 +4930,13 @@
         <v>1.71</v>
       </c>
       <c r="I18" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.43</v>
@@ -4945,31 +4945,31 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
         <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V18" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="W18" t="n">
         <v>1.19</v>
@@ -4984,10 +4984,10 @@
         <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AC18" t="n">
         <v>14</v>
@@ -5026,7 +5026,7 @@
         <v>130</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>13.5</v>
       </c>
       <c r="AP18" t="n">
         <v>10</v>
@@ -5038,55 +5038,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV18" t="n">
         <v>8.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY18" t="n">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="AZ18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF18" t="n">
         <v>7</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>7.6</v>
       </c>
       <c r="BG18" t="n">
         <v>10</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
@@ -5110,13 +5110,13 @@
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.65</v>
+        <v>3.25</v>
       </c>
       <c r="BT18" t="n">
         <v>4.4</v>
@@ -5125,26 +5125,26 @@
         <v>3.05</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.59</v>
+        <v>3.05</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G19" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="H19" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I19" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
         <v>4.8</v>
@@ -5199,34 +5199,34 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
         <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5244,7 +5244,7 @@
         <v>500</v>
       </c>
       <c r="AC19" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="AD19" t="n">
         <v>500</v>
@@ -5256,7 +5256,7 @@
         <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
         <v>500</v>
@@ -5265,7 +5265,7 @@
         <v>700</v>
       </c>
       <c r="AJ19" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
         <v>970</v>
@@ -5283,79 +5283,79 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.7</v>
+        <v>2.76</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AT19" t="n">
         <v>6.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.3</v>
+        <v>1.89</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.75</v>
+        <v>2.32</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.28</v>
+        <v>1.79</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.6</v>
+        <v>2.58</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.54</v>
+        <v>1.83</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BO19" t="n">
         <v>3.35</v>
@@ -5364,41 +5364,41 @@
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -5438,13 +5438,13 @@
         <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
         <v>4.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L20" t="n">
         <v>1.18</v>
@@ -5462,7 +5462,7 @@
         <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.88</v>
@@ -5495,7 +5495,7 @@
         <v>700</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC20" t="n">
         <v>970</v>
@@ -5531,22 +5531,22 @@
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>15</v>
+        <v>5.6</v>
       </c>
       <c r="AO20" t="n">
         <v>700</v>
       </c>
       <c r="AP20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
@@ -5558,7 +5558,7 @@
         <v>9</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX20" t="n">
         <v>9</v>
@@ -5579,22 +5579,22 @@
         <v>10.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
         <v>4.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
@@ -5609,10 +5609,10 @@
         <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
@@ -5627,7 +5627,7 @@
         <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H21" t="n">
         <v>2.54</v>
@@ -5695,10 +5695,10 @@
         <v>2.84</v>
       </c>
       <c r="J21" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
         <v>1.49</v>
@@ -5710,7 +5710,7 @@
         <v>2.72</v>
       </c>
       <c r="O21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P21" t="n">
         <v>1.58</v>
@@ -5728,22 +5728,22 @@
         <v>1.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V21" t="n">
         <v>1.54</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y21" t="n">
         <v>9</v>
       </c>
       <c r="Z21" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
         <v>900</v>
@@ -5761,7 +5761,7 @@
         <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG21" t="n">
         <v>26</v>
@@ -5782,67 +5782,67 @@
         <v>500</v>
       </c>
       <c r="AM21" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR21" t="n">
         <v>12.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE21" t="n">
         <v>8</v>
       </c>
       <c r="BF21" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BH21" t="n">
         <v>3.05</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G22" t="n">
         <v>2.34</v>
@@ -5961,10 +5961,10 @@
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
@@ -5979,10 +5979,10 @@
         <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U22" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V22" t="n">
         <v>1.37</v>
@@ -5991,46 +5991,46 @@
         <v>1.74</v>
       </c>
       <c r="X22" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE22" t="n">
         <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
         <v>500</v>
       </c>
       <c r="AJ22" t="n">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL22" t="n">
         <v>500</v>
@@ -6039,70 +6039,70 @@
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP22" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AQ22" t="n">
         <v>10.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AT22" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BH22" t="n">
         <v>3.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
@@ -6120,7 +6120,7 @@
         <v>5.3</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -6203,25 +6203,25 @@
         <v>2.16</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
         <v>3.55</v>
       </c>
       <c r="L23" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q23" t="n">
         <v>2.08</v>
@@ -6230,10 +6230,10 @@
         <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U23" t="n">
         <v>1.96</v>
@@ -6245,10 +6245,10 @@
         <v>1.28</v>
       </c>
       <c r="X23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z23" t="n">
         <v>13</v>
@@ -6284,7 +6284,7 @@
         <v>900</v>
       </c>
       <c r="AK23" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AL23" t="n">
         <v>500</v>
@@ -6299,70 +6299,70 @@
         <v>23</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT23" t="n">
         <v>11.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD23" t="n">
         <v>8</v>
       </c>
-      <c r="BC23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF23" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>7.8</v>
       </c>
       <c r="BG23" t="n">
         <v>13.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6374,47 +6374,47 @@
         <v>7.6</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT23" t="n">
         <v>4.9</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV23" t="n">
         <v>16.5</v>
       </c>
       <c r="BW23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX23" t="n">
         <v>34</v>
       </c>
       <c r="BY23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ23" t="n">
         <v>32</v>
       </c>
       <c r="CA23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H24" t="n">
         <v>3.6</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
         <v>4.7</v>
@@ -6469,13 +6469,13 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.15</v>
       </c>
       <c r="P24" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q24" t="n">
         <v>1.47</v>
@@ -6484,7 +6484,7 @@
         <v>1.72</v>
       </c>
       <c r="S24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T24" t="n">
         <v>1.5</v>
@@ -6496,7 +6496,7 @@
         <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="X24" t="n">
         <v>32</v>
@@ -6517,13 +6517,13 @@
         <v>11.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE24" t="n">
         <v>38</v>
       </c>
       <c r="AF24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG24" t="n">
         <v>11.5</v>
@@ -6559,40 +6559,40 @@
         <v>20</v>
       </c>
       <c r="AR24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS24" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="AU24" t="n">
         <v>9.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX24" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB24" t="n">
         <v>19.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BD24" t="n">
         <v>7.4</v>
@@ -6604,7 +6604,7 @@
         <v>6.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH24" t="n">
         <v>5</v>
@@ -6628,7 +6628,7 @@
         <v>5.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP24" t="n">
         <v>12.5</v>
@@ -6646,10 +6646,10 @@
         <v>8</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW24" t="n">
         <v>8.199999999999999</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -6699,25 +6699,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H25" t="n">
         <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L25" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
@@ -6747,52 +6747,52 @@
         <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X25" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC25" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="n">
         <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>900</v>
+        <v>30</v>
       </c>
       <c r="AK25" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AL25" t="n">
         <v>500</v>
@@ -6801,46 +6801,46 @@
         <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="AO25" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
         <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="AT25" t="n">
         <v>7</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV25" t="n">
         <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AX25" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BB25" t="n">
         <v>19</v>
@@ -6849,16 +6849,16 @@
         <v>18</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BF25" t="n">
         <v>14</v>
       </c>
       <c r="BG25" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BH25" t="n">
         <v>3.25</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G26" t="n">
         <v>2.26</v>
@@ -7043,7 +7043,7 @@
         <v>150</v>
       </c>
       <c r="AJ26" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AK26" t="n">
         <v>23</v>
@@ -7061,7 +7061,7 @@
         <v>40</v>
       </c>
       <c r="AP26" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
         <v>12</v>
@@ -7073,7 +7073,7 @@
         <v>6.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU26" t="n">
         <v>7</v>
@@ -7088,25 +7088,25 @@
         <v>11</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
         <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB26" t="n">
         <v>20</v>
       </c>
       <c r="BC26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>18</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF26" t="n">
         <v>10.5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G27" t="n">
         <v>2.34</v>
       </c>
       <c r="H27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I27" t="n">
         <v>3.35</v>
@@ -7225,7 +7225,7 @@
         <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="M27" t="n">
         <v>1.04</v>
@@ -7234,7 +7234,7 @@
         <v>4.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P27" t="n">
         <v>2.34</v>
@@ -7258,7 +7258,7 @@
         <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X27" t="n">
         <v>27</v>
@@ -7276,7 +7276,7 @@
         <v>16.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD27" t="n">
         <v>17.5</v>
@@ -7324,7 +7324,7 @@
         <v>18</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT27" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -7348,7 +7348,7 @@
         <v>11</v>
       </c>
       <c r="BA27" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="BB27" t="n">
         <v>14.5</v>
@@ -7360,7 +7360,7 @@
         <v>14.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.3</v>
+        <v>44</v>
       </c>
       <c r="BF27" t="n">
         <v>9.4</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -7464,13 +7464,13 @@
         <v>2.76</v>
       </c>
       <c r="G28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I28" t="n">
         <v>3.05</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>3.1</v>
@@ -7491,7 +7491,7 @@
         <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q28" t="n">
         <v>2.28</v>
@@ -7506,7 +7506,7 @@
         <v>1.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V28" t="n">
         <v>1.48</v>
@@ -7518,19 +7518,19 @@
         <v>11</v>
       </c>
       <c r="Y28" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="n">
         <v>55</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
         <v>14</v>
@@ -7539,13 +7539,13 @@
         <v>48</v>
       </c>
       <c r="AF28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG28" t="n">
         <v>16</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
         <v>70</v>
@@ -7578,7 +7578,7 @@
         <v>15.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT28" t="n">
         <v>8.199999999999999</v>
@@ -7590,7 +7590,7 @@
         <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX28" t="n">
         <v>15.5</v>
@@ -7602,25 +7602,25 @@
         <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH28" t="n">
         <v>3.05</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
         <v>3.2</v>
       </c>
       <c r="G29" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H29" t="n">
         <v>2.18</v>
@@ -7727,10 +7727,10 @@
         <v>2.42</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L29" t="n">
         <v>1.32</v>
@@ -7916,7 +7916,7 @@
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
@@ -7928,7 +7928,7 @@
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>8</v>
+        <v>2.06</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G30" t="n">
         <v>3.6</v>
@@ -7981,7 +7981,7 @@
         <v>3.1</v>
       </c>
       <c r="J30" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="K30" t="n">
         <v>2.98</v>
@@ -7993,7 +7993,7 @@
         <v>1.17</v>
       </c>
       <c r="N30" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O30" t="n">
         <v>1.75</v>
@@ -8020,13 +8020,13 @@
         <v>1.48</v>
       </c>
       <c r="W30" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X30" t="n">
         <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="Z30" t="n">
         <v>970</v>
@@ -8080,13 +8080,13 @@
         <v>5.1</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT30" t="n">
         <v>6.2</v>
@@ -8098,7 +8098,7 @@
         <v>8.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX30" t="n">
         <v>9</v>
@@ -8107,28 +8107,28 @@
         <v>9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA30" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BD30" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH30" t="n">
         <v>2.38</v>
@@ -8152,7 +8152,7 @@
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -8226,10 +8226,10 @@
         <v>1.72</v>
       </c>
       <c r="G31" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
         <v>5.3</v>
@@ -8238,7 +8238,7 @@
         <v>4.3</v>
       </c>
       <c r="K31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.26</v>
@@ -8247,34 +8247,34 @@
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P31" t="n">
         <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R31" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S31" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T31" t="n">
         <v>1.68</v>
       </c>
       <c r="U31" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="V31" t="n">
         <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X31" t="n">
         <v>27</v>
@@ -8289,10 +8289,10 @@
         <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD31" t="n">
         <v>970</v>
@@ -8304,10 +8304,10 @@
         <v>19</v>
       </c>
       <c r="AG31" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH31" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AI31" t="n">
         <v>700</v>
@@ -8316,7 +8316,7 @@
         <v>23</v>
       </c>
       <c r="AK31" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
@@ -8328,22 +8328,22 @@
         <v>9.4</v>
       </c>
       <c r="AO31" t="n">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="AP31" t="n">
         <v>18</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR31" t="n">
         <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU31" t="n">
         <v>8.4</v>
@@ -8352,7 +8352,7 @@
         <v>13.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX31" t="n">
         <v>9</v>
@@ -8361,7 +8361,7 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BA31" t="n">
         <v>26</v>
@@ -8376,34 +8376,34 @@
         <v>17.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF31" t="n">
         <v>8</v>
       </c>
       <c r="BG31" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ31" t="n">
         <v>9.6</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO31" t="n">
         <v>3.55</v>
@@ -8412,41 +8412,41 @@
         <v>11.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT31" t="n">
         <v>9</v>
       </c>
       <c r="BU31" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ31" t="n">
         <v>16.5</v>
       </c>
       <c r="CA31" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -8477,52 +8477,52 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H32" t="n">
         <v>3.25</v>
       </c>
       <c r="I32" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K32" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M32" t="n">
         <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P32" t="n">
         <v>1.52</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V32" t="n">
         <v>1.35</v>
@@ -8531,19 +8531,19 @@
         <v>1.58</v>
       </c>
       <c r="X32" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA32" t="n">
         <v>170</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
@@ -8561,7 +8561,7 @@
         <v>13.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI32" t="n">
         <v>85</v>
@@ -8570,7 +8570,7 @@
         <v>50</v>
       </c>
       <c r="AK32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL32" t="n">
         <v>70</v>
@@ -8594,7 +8594,7 @@
         <v>19</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT32" t="n">
         <v>6.6</v>
@@ -8606,7 +8606,7 @@
         <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX32" t="n">
         <v>12.5</v>
@@ -8618,7 +8618,7 @@
         <v>19</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB32" t="n">
         <v>9.199999999999999</v>
@@ -8627,25 +8627,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF32" t="n">
         <v>7.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BJ32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK32" t="n">
         <v>8.4</v>
@@ -8654,7 +8654,7 @@
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN32" t="n">
         <v>5.4</v>
@@ -8663,44 +8663,44 @@
         <v>4.5</v>
       </c>
       <c r="BP32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ32" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR32" t="n">
         <v>48</v>
       </c>
       <c r="BS32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU32" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV32" t="n">
         <v>36</v>
       </c>
       <c r="BW32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX32" t="n">
         <v>60</v>
       </c>
       <c r="BY32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ32" t="n">
         <v>55</v>
       </c>
       <c r="CA32" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -8737,10 +8737,10 @@
         <v>2.18</v>
       </c>
       <c r="H33" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J33" t="n">
         <v>2.86</v>
@@ -8749,43 +8749,43 @@
         <v>3.25</v>
       </c>
       <c r="L33" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M33" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N33" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O33" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="P33" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U33" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V33" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W33" t="n">
         <v>1.85</v>
       </c>
       <c r="X33" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="Y33" t="n">
         <v>13</v>
@@ -8797,13 +8797,13 @@
         <v>900</v>
       </c>
       <c r="AB33" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC33" t="n">
         <v>7.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AE33" t="n">
         <v>700</v>
@@ -8824,7 +8824,7 @@
         <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AL33" t="n">
         <v>500</v>
@@ -8839,16 +8839,16 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ33" t="n">
         <v>9.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT33" t="n">
         <v>5.1</v>
@@ -8860,7 +8860,7 @@
         <v>18</v>
       </c>
       <c r="AW33" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX33" t="n">
         <v>8.6</v>
@@ -8869,92 +8869,92 @@
         <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB33" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>6.4</v>
       </c>
       <c r="BC33" t="n">
         <v>22</v>
       </c>
       <c r="BD33" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE33" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF33" t="n">
         <v>20</v>
       </c>
       <c r="BG33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH33" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="BJ33" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN33" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW33" t="n">
         <v>9.4</v>
       </c>
-      <c r="BU33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW33" t="n">
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA33" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BX33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -8985,13 +8985,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G34" t="n">
         <v>2.34</v>
       </c>
       <c r="H34" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="I34" t="n">
         <v>3.25</v>
@@ -9003,7 +9003,7 @@
         <v>4.6</v>
       </c>
       <c r="L34" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M34" t="n">
         <v>1.02</v>
@@ -9015,22 +9015,22 @@
         <v>1.14</v>
       </c>
       <c r="P34" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q34" t="n">
         <v>1.44</v>
       </c>
       <c r="R34" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="S34" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="T34" t="n">
         <v>1.44</v>
       </c>
       <c r="U34" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="V34" t="n">
         <v>1.44</v>
@@ -9039,19 +9039,19 @@
         <v>1.74</v>
       </c>
       <c r="X34" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y34" t="n">
         <v>23</v>
       </c>
       <c r="Z34" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AA34" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AB34" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC34" t="n">
         <v>12</v>
@@ -9063,7 +9063,7 @@
         <v>36</v>
       </c>
       <c r="AF34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG34" t="n">
         <v>13</v>
@@ -9078,7 +9078,7 @@
         <v>42</v>
       </c>
       <c r="AK34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="n">
         <v>34</v>
@@ -9087,13 +9087,13 @@
         <v>60</v>
       </c>
       <c r="AN34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO34" t="n">
         <v>15.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ34" t="n">
         <v>18</v>
@@ -9102,7 +9102,7 @@
         <v>17.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT34" t="n">
         <v>15.5</v>
@@ -9114,7 +9114,7 @@
         <v>12</v>
       </c>
       <c r="AW34" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AX34" t="n">
         <v>17</v>
@@ -9126,10 +9126,10 @@
         <v>12</v>
       </c>
       <c r="BA34" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BB34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BC34" t="n">
         <v>17</v>
@@ -9138,7 +9138,7 @@
         <v>21</v>
       </c>
       <c r="BE34" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BF34" t="n">
         <v>7.8</v>
@@ -9156,59 +9156,59 @@
         <v>8.6</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN34" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO34" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP34" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR34" t="n">
         <v>21</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT34" t="n">
         <v>7.4</v>
       </c>
       <c r="BU34" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX34" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ34" t="n">
         <v>13</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>3.95</v>
       </c>
       <c r="G35" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H35" t="n">
         <v>1.76</v>
@@ -9275,7 +9275,7 @@
         <v>1.36</v>
       </c>
       <c r="R35" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S35" t="n">
         <v>1.89</v>
@@ -9329,10 +9329,10 @@
         <v>25</v>
       </c>
       <c r="AJ35" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AK35" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL35" t="n">
         <v>42</v>
@@ -9359,7 +9359,7 @@
         <v>17</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.1</v>
+        <v>24</v>
       </c>
       <c r="AU35" t="n">
         <v>9.800000000000001</v>
@@ -9371,7 +9371,7 @@
         <v>12.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="AY35" t="n">
         <v>14.5</v>
@@ -9383,16 +9383,16 @@
         <v>16</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.5</v>
+        <v>55</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.2</v>
+        <v>29</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.2</v>
+        <v>26</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="BF35" t="n">
         <v>16</v>
@@ -9410,16 +9410,16 @@
         <v>8.6</v>
       </c>
       <c r="BK35" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN35" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO35" t="n">
         <v>5.3</v>
@@ -9428,13 +9428,13 @@
         <v>26</v>
       </c>
       <c r="BQ35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR35" t="n">
         <v>26</v>
       </c>
       <c r="BS35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT35" t="n">
         <v>5.5</v>
@@ -9446,7 +9446,7 @@
         <v>11.5</v>
       </c>
       <c r="BW35" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX35" t="n">
         <v>17</v>
@@ -9458,11 +9458,11 @@
         <v>10</v>
       </c>
       <c r="CA35" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -9496,16 +9496,16 @@
         <v>2.18</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H36" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I36" t="n">
         <v>3.15</v>
       </c>
       <c r="J36" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K36" t="n">
         <v>4.9</v>
@@ -9517,19 +9517,19 @@
         <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O36" t="n">
         <v>1.11</v>
       </c>
       <c r="P36" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q36" t="n">
         <v>1.33</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S36" t="n">
         <v>1.81</v>
@@ -9544,7 +9544,7 @@
         <v>1.47</v>
       </c>
       <c r="W36" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X36" t="n">
         <v>48</v>
@@ -9565,7 +9565,7 @@
         <v>13.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE36" t="n">
         <v>28</v>
@@ -9601,13 +9601,13 @@
         <v>12.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="AQ36" t="n">
         <v>21</v>
       </c>
       <c r="AR36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AS36" t="n">
         <v>36</v>
@@ -9622,7 +9622,7 @@
         <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AX36" t="n">
         <v>18</v>
@@ -9637,7 +9637,7 @@
         <v>21</v>
       </c>
       <c r="BB36" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BC36" t="n">
         <v>15</v>
@@ -9646,7 +9646,7 @@
         <v>17</v>
       </c>
       <c r="BE36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BF36" t="n">
         <v>6.4</v>
@@ -9658,7 +9658,7 @@
         <v>6.2</v>
       </c>
       <c r="BI36" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BJ36" t="n">
         <v>8.4</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
         <v>4.4</v>
       </c>
       <c r="H37" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I37" t="n">
         <v>1.81</v>
@@ -9762,7 +9762,7 @@
         <v>5.2</v>
       </c>
       <c r="K37" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.14</v>
@@ -9819,7 +9819,7 @@
         <v>970</v>
       </c>
       <c r="AD37" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE37" t="n">
         <v>970</v>
@@ -9831,10 +9831,10 @@
         <v>500</v>
       </c>
       <c r="AH37" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AI37" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AJ37" t="n">
         <v>500</v>
@@ -9849,61 +9849,61 @@
         <v>580</v>
       </c>
       <c r="AN37" t="n">
-        <v>250</v>
+        <v>970</v>
       </c>
       <c r="AO37" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AP37" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ37" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AR37" t="n">
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="AU37" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV37" t="n">
         <v>10</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="AX37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ37" t="n">
         <v>6</v>
       </c>
-      <c r="AY37" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BA37" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD37" t="n">
         <v>7</v>
       </c>
-      <c r="BD37" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE37" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF37" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG37" t="n">
         <v>3.55</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
         <v>1.21</v>
       </c>
       <c r="G38" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H38" t="n">
         <v>4.3</v>
@@ -10052,7 +10052,7 @@
         <v>1.06</v>
       </c>
       <c r="W38" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
         <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="T39" t="n">
         <v>1.11</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="O40" t="n">
         <v>1.2</v>
@@ -10542,7 +10542,7 @@
         <v>1.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="R40" t="n">
         <v>1.17</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
         <v>1.43</v>
       </c>
       <c r="P41" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q41" t="n">
         <v>1.46</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -11041,13 +11041,13 @@
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="O42" t="n">
         <v>1.07</v>
       </c>
       <c r="P42" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Q42" t="n">
         <v>2.06</v>
@@ -11086,7 +11086,7 @@
         <v>970</v>
       </c>
       <c r="AC42" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD42" t="n">
         <v>970</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -11271,10 +11271,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G43" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="H43" t="n">
         <v>2.3</v>
@@ -11304,13 +11304,13 @@
         <v>1.32</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -11325,16 +11325,16 @@
         <v>1.2</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB43" t="n">
         <v>970</v>
@@ -11343,10 +11343,10 @@
         <v>970</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF43" t="n">
         <v>970</v>
@@ -11355,10 +11355,10 @@
         <v>970</v>
       </c>
       <c r="AH43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ43" t="n">
         <v>500</v>
@@ -11370,64 +11370,64 @@
         <v>500</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN43" t="n">
         <v>500</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BG43" t="n">
         <v>1.55</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -11806,19 +11806,19 @@
         <v>1.52</v>
       </c>
       <c r="O45" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="P45" t="n">
         <v>1.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="R45" t="n">
         <v>1.2</v>
       </c>
       <c r="S45" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="T45" t="n">
         <v>1.14</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>7.8</v>
       </c>
       <c r="H46" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="I46" t="n">
         <v>1000</v>
@@ -12087,7 +12087,7 @@
         <v>1.52</v>
       </c>
       <c r="X46" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y46" t="n">
         <v>500</v>
@@ -12099,10 +12099,10 @@
         <v>500</v>
       </c>
       <c r="AB46" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC46" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD46" t="n">
         <v>500</v>
@@ -12129,7 +12129,7 @@
         <v>500</v>
       </c>
       <c r="AL46" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM46" t="n">
         <v>500</v>
@@ -12141,10 +12141,10 @@
         <v>500</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR46" t="n">
         <v>1.01</v>
@@ -12153,10 +12153,10 @@
         <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV46" t="n">
         <v>1.01</v>
@@ -12165,10 +12165,10 @@
         <v>1.01</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ46" t="n">
         <v>1.01</v>
@@ -12192,7 +12192,7 @@
         <v>1.01</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -12320,13 +12320,13 @@
         <v>1.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R47" t="n">
         <v>1.12</v>
       </c>
       <c r="S47" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12341,10 +12341,10 @@
         <v>1.33</v>
       </c>
       <c r="X47" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y47" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z47" t="n">
         <v>500</v>
@@ -12353,10 +12353,10 @@
         <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC47" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AD47" t="n">
         <v>500</v>
@@ -12374,7 +12374,7 @@
         <v>500</v>
       </c>
       <c r="AI47" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ47" t="n">
         <v>900</v>
@@ -12395,10 +12395,10 @@
         <v>500</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR47" t="n">
         <v>1.01</v>
@@ -12407,10 +12407,10 @@
         <v>1.01</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV47" t="n">
         <v>1.01</v>
@@ -12419,7 +12419,7 @@
         <v>1.01</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY47" t="n">
         <v>1.01</v>
@@ -12443,10 +12443,10 @@
         <v>1.01</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -12595,19 +12595,19 @@
         <v>1.31</v>
       </c>
       <c r="X48" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y48" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z48" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA48" t="n">
         <v>40</v>
       </c>
       <c r="AB48" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC48" t="n">
         <v>8.199999999999999</v>
@@ -12619,10 +12619,10 @@
         <v>38</v>
       </c>
       <c r="AF48" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG48" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH48" t="n">
         <v>26</v>
@@ -12643,7 +12643,7 @@
         <v>500</v>
       </c>
       <c r="AN48" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="AO48" t="n">
         <v>38</v>
@@ -12655,10 +12655,10 @@
         <v>6.2</v>
       </c>
       <c r="AR48" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT48" t="n">
         <v>8.199999999999999</v>
@@ -12667,40 +12667,40 @@
         <v>5.9</v>
       </c>
       <c r="AV48" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AW48" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX48" t="n">
         <v>19.5</v>
       </c>
       <c r="AY48" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AZ48" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA48" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB48" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC48" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE48" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF48" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG48" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH48" t="n">
         <v>2.9</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12828,7 @@
         <v>1.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R49" t="n">
         <v>1.12</v>
@@ -12849,10 +12849,10 @@
         <v>1.36</v>
       </c>
       <c r="X49" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y49" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z49" t="n">
         <v>500</v>
@@ -12861,10 +12861,10 @@
         <v>500</v>
       </c>
       <c r="AB49" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC49" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AD49" t="n">
         <v>500</v>
@@ -12882,7 +12882,7 @@
         <v>500</v>
       </c>
       <c r="AI49" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ49" t="n">
         <v>500</v>
@@ -12903,10 +12903,10 @@
         <v>500</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR49" t="n">
         <v>1.01</v>
@@ -12915,10 +12915,10 @@
         <v>1.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV49" t="n">
         <v>1.01</v>
@@ -12927,7 +12927,7 @@
         <v>1.01</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY49" t="n">
         <v>1.01</v>
@@ -12951,10 +12951,10 @@
         <v>1.01</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
         <v>2.88</v>
       </c>
       <c r="H50" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I50" t="n">
         <v>4.1</v>
@@ -13064,10 +13064,10 @@
         <v>2.58</v>
       </c>
       <c r="K50" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L50" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M50" t="n">
         <v>1.11</v>
@@ -13103,10 +13103,10 @@
         <v>1.53</v>
       </c>
       <c r="X50" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y50" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z50" t="n">
         <v>500</v>
@@ -13115,7 +13115,7 @@
         <v>900</v>
       </c>
       <c r="AB50" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC50" t="n">
         <v>8.4</v>
@@ -13157,61 +13157,61 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AR50" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AT50" t="n">
         <v>5.8</v>
       </c>
       <c r="AU50" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE50" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX50" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA50" t="n">
+      <c r="BF50" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC50" t="n">
+      <c r="BG50" t="n">
         <v>4</v>
       </c>
-      <c r="BD50" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH50" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI50" t="n">
         <v>2.18</v>
@@ -13220,31 +13220,31 @@
         <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ50" t="n">
         <v>1.09</v>
       </c>
-      <c r="BN50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ50" t="n">
-        <v>1.31</v>
-      </c>
       <c r="BR50" t="n">
         <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BT50" t="n">
         <v>1000</v>
@@ -13256,23 +13256,23 @@
         <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BZ50" t="n">
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
         <v>22</v>
       </c>
       <c r="AE51" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF51" t="n">
         <v>12</v>
@@ -13408,7 +13408,7 @@
         <v>23</v>
       </c>
       <c r="AO51" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AP51" t="n">
         <v>8.4</v>
@@ -13432,7 +13432,7 @@
         <v>15.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AX51" t="n">
         <v>8.6</v>
@@ -13462,7 +13462,7 @@
         <v>14.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BH51" t="n">
         <v>3.1</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -13713,10 +13713,10 @@
         <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -14065,22 +14065,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G54" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H54" t="n">
         <v>4.2</v>
       </c>
       <c r="I54" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J54" t="n">
         <v>3.1</v>
       </c>
       <c r="K54" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L54" t="n">
         <v>1.45</v>
@@ -14113,10 +14113,10 @@
         <v>1.78</v>
       </c>
       <c r="V54" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W54" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X54" t="n">
         <v>10.5</v>
@@ -14140,7 +14140,7 @@
         <v>970</v>
       </c>
       <c r="AE54" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AF54" t="n">
         <v>12</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -14373,10 +14373,10 @@
         <v>1.89</v>
       </c>
       <c r="X55" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y55" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Z55" t="n">
         <v>500</v>
@@ -14388,7 +14388,7 @@
         <v>7</v>
       </c>
       <c r="AC55" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD55" t="n">
         <v>23</v>
@@ -14397,7 +14397,7 @@
         <v>500</v>
       </c>
       <c r="AF55" t="n">
-        <v>970</v>
+        <v>140</v>
       </c>
       <c r="AG55" t="n">
         <v>13.5</v>
@@ -14418,7 +14418,7 @@
         <v>500</v>
       </c>
       <c r="AM55" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN55" t="n">
         <v>500</v>
@@ -14430,55 +14430,55 @@
         <v>5.3</v>
       </c>
       <c r="AQ55" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AR55" t="n">
-        <v>3.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS55" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AT55" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU55" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AV55" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX55" t="n">
         <v>10</v>
       </c>
       <c r="AY55" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ55" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE55" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA55" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BF55" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG55" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="BH55" t="n">
         <v>2.9</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -14576,10 +14576,10 @@
         <v>1.45</v>
       </c>
       <c r="G56" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H56" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I56" t="n">
         <v>10.5</v>
@@ -14591,7 +14591,7 @@
         <v>5</v>
       </c>
       <c r="L56" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="M56" t="n">
         <v>1.07</v>
@@ -14633,10 +14633,10 @@
         <v>32</v>
       </c>
       <c r="Z56" t="n">
-        <v>100</v>
+        <v>420</v>
       </c>
       <c r="AA56" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="AB56" t="n">
         <v>7</v>
@@ -14645,7 +14645,7 @@
         <v>10.5</v>
       </c>
       <c r="AD56" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AE56" t="n">
         <v>190</v>
@@ -14657,16 +14657,16 @@
         <v>10.5</v>
       </c>
       <c r="AH56" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="n">
-        <v>170</v>
+        <v>470</v>
       </c>
       <c r="AJ56" t="n">
         <v>12</v>
       </c>
       <c r="AK56" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AL56" t="n">
         <v>500</v>
@@ -14678,16 +14678,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO56" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AP56" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ56" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AR56" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS56" t="n">
         <v>8.800000000000001</v>
@@ -14702,7 +14702,7 @@
         <v>27</v>
       </c>
       <c r="AW56" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX56" t="n">
         <v>6.6</v>
@@ -14711,10 +14711,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ56" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB56" t="n">
         <v>10.5</v>
@@ -14726,40 +14726,40 @@
         <v>42</v>
       </c>
       <c r="BE56" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF56" t="n">
         <v>7.6</v>
       </c>
       <c r="BG56" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BH56" t="n">
         <v>3.4</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ56" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK56" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN56" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO56" t="n">
         <v>3</v>
       </c>
       <c r="BP56" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ56" t="n">
         <v>5.9</v>
@@ -14768,7 +14768,7 @@
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT56" t="n">
         <v>12.5</v>
@@ -14780,23 +14780,23 @@
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ56" t="n">
         <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -14827,13 +14827,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="G57" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H57" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I57" t="n">
         <v>5.3</v>
@@ -14842,7 +14842,7 @@
         <v>3.3</v>
       </c>
       <c r="K57" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L57" t="n">
         <v>1.5</v>
@@ -14878,31 +14878,31 @@
         <v>1.23</v>
       </c>
       <c r="W57" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="X57" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y57" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AA57" t="n">
         <v>900</v>
       </c>
       <c r="AB57" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC57" t="n">
         <v>9.4</v>
       </c>
       <c r="AD57" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE57" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF57" t="n">
         <v>13</v>
@@ -14911,19 +14911,19 @@
         <v>13</v>
       </c>
       <c r="AH57" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI57" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ57" t="n">
         <v>28</v>
       </c>
       <c r="AK57" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL57" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM57" t="n">
         <v>500</v>
@@ -14932,7 +14932,7 @@
         <v>24</v>
       </c>
       <c r="AO57" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP57" t="n">
         <v>7.6</v>
@@ -14941,22 +14941,22 @@
         <v>10</v>
       </c>
       <c r="AR57" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AS57" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT57" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AU57" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV57" t="n">
         <v>15</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX57" t="n">
         <v>7.8</v>
@@ -14965,10 +14965,10 @@
         <v>7.8</v>
       </c>
       <c r="AZ57" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB57" t="n">
         <v>16.5</v>
@@ -14977,16 +14977,16 @@
         <v>17.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BE57" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF57" t="n">
         <v>14</v>
       </c>
       <c r="BG57" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH57" t="n">
         <v>3</v>
@@ -14998,59 +14998,59 @@
         <v>12</v>
       </c>
       <c r="BK57" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL57" t="n">
         <v>1000</v>
       </c>
       <c r="BM57" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN57" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO57" t="n">
         <v>3.4</v>
       </c>
       <c r="BP57" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ57" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR57" t="n">
         <v>38</v>
       </c>
       <c r="BS57" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT57" t="n">
         <v>8.4</v>
       </c>
-      <c r="BT57" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BU57" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BV57" t="n">
         <v>55</v>
       </c>
       <c r="BW57" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY57" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BX57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY57" t="n">
-        <v>9.4</v>
       </c>
       <c r="BZ57" t="n">
         <v>38</v>
       </c>
       <c r="CA57" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -15084,13 +15084,13 @@
         <v>2.52</v>
       </c>
       <c r="G58" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H58" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I58" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
         <v>3.05</v>
@@ -15108,13 +15108,13 @@
         <v>2.72</v>
       </c>
       <c r="O58" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P58" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R58" t="n">
         <v>1.21</v>
@@ -15123,70 +15123,70 @@
         <v>4.5</v>
       </c>
       <c r="T58" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U58" t="n">
         <v>1.84</v>
       </c>
       <c r="V58" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W58" t="n">
         <v>1.51</v>
       </c>
       <c r="X58" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y58" t="n">
         <v>11</v>
       </c>
       <c r="Z58" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA58" t="n">
         <v>60</v>
       </c>
       <c r="AB58" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC58" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD58" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF58" t="n">
         <v>19.5</v>
       </c>
       <c r="AG58" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI58" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ58" t="n">
         <v>48</v>
       </c>
       <c r="AK58" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN58" t="n">
         <v>42</v>
       </c>
-      <c r="AL58" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>46</v>
-      </c>
       <c r="AO58" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP58" t="n">
         <v>7.8</v>
@@ -15198,19 +15198,19 @@
         <v>16</v>
       </c>
       <c r="AS58" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT58" t="n">
         <v>6.8</v>
       </c>
       <c r="AU58" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AV58" t="n">
         <v>11</v>
       </c>
       <c r="AW58" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX58" t="n">
         <v>14</v>
@@ -15222,25 +15222,25 @@
         <v>19</v>
       </c>
       <c r="BA58" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB58" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC58" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BF58" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="BG58" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH58" t="n">
         <v>3.05</v>
@@ -15249,7 +15249,7 @@
         <v>2.42</v>
       </c>
       <c r="BJ58" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK58" t="n">
         <v>4.9</v>
@@ -15258,19 +15258,19 @@
         <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BN58" t="n">
         <v>5.9</v>
       </c>
       <c r="BO58" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP58" t="n">
         <v>25</v>
       </c>
       <c r="BQ58" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR58" t="n">
         <v>46</v>
@@ -15282,29 +15282,29 @@
         <v>6.4</v>
       </c>
       <c r="BU58" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BV58" t="n">
         <v>29</v>
       </c>
       <c r="BW58" t="n">
-        <v>2.12</v>
+        <v>6.6</v>
       </c>
       <c r="BX58" t="n">
         <v>48</v>
       </c>
       <c r="BY58" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BZ58" t="n">
         <v>44</v>
       </c>
       <c r="CA58" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -15353,28 +15353,28 @@
         <v>3.55</v>
       </c>
       <c r="L59" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M59" t="n">
         <v>1.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O59" t="n">
         <v>1.42</v>
       </c>
       <c r="P59" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R59" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S59" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T59" t="n">
         <v>1.91</v>
@@ -15389,28 +15389,28 @@
         <v>1.65</v>
       </c>
       <c r="X59" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y59" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z59" t="n">
         <v>29</v>
       </c>
       <c r="AA59" t="n">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AB59" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC59" t="n">
         <v>8.6</v>
       </c>
       <c r="AD59" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE59" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF59" t="n">
         <v>16.5</v>
@@ -15419,7 +15419,7 @@
         <v>13.5</v>
       </c>
       <c r="AH59" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI59" t="n">
         <v>80</v>
@@ -15428,115 +15428,115 @@
         <v>36</v>
       </c>
       <c r="AK59" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL59" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM59" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN59" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO59" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP59" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ59" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR59" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS59" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT59" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE59" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU59" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD59" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE59" t="n">
-        <v>5</v>
-      </c>
       <c r="BF59" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BG59" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BH59" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ59" t="n">
         <v>11</v>
       </c>
       <c r="BK59" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN59" t="n">
         <v>5.2</v>
       </c>
       <c r="BO59" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP59" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ59" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR59" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS59" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT59" t="n">
         <v>7</v>
       </c>
       <c r="BU59" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV59" t="n">
         <v>34</v>
@@ -15548,17 +15548,17 @@
         <v>55</v>
       </c>
       <c r="BY59" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ59" t="n">
         <v>40</v>
       </c>
       <c r="CA59" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G60" t="n">
         <v>2.48</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -15843,19 +15843,19 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G61" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H61" t="n">
         <v>4.1</v>
       </c>
       <c r="I61" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J61" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K61" t="n">
         <v>3.8</v>
@@ -15891,10 +15891,10 @@
         <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W61" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X61" t="n">
         <v>14</v>
@@ -16026,7 +16026,7 @@
         <v>4.9</v>
       </c>
       <c r="BO61" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP61" t="n">
         <v>15.5</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -16178,7 +16178,7 @@
         <v>970</v>
       </c>
       <c r="AG62" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH62" t="n">
         <v>500</v>
@@ -16205,13 +16205,13 @@
         <v>500</v>
       </c>
       <c r="AP62" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ62" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR62" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS62" t="n">
         <v>7.4</v>
@@ -16223,22 +16223,22 @@
         <v>7</v>
       </c>
       <c r="AV62" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AW62" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX62" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AY62" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AZ62" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA62" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB62" t="n">
         <v>6</v>
@@ -16247,16 +16247,16 @@
         <v>6</v>
       </c>
       <c r="BD62" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE62" t="n">
         <v>7.4</v>
       </c>
       <c r="BF62" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG62" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="BH62" t="n">
         <v>3.15</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -16465,7 +16465,7 @@
         <v>21</v>
       </c>
       <c r="AR63" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS63" t="n">
         <v>5</v>
@@ -16492,7 +16492,7 @@
         <v>21</v>
       </c>
       <c r="BA63" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB63" t="n">
         <v>10</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -16611,19 +16611,19 @@
         <v>1.67</v>
       </c>
       <c r="H64" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="I64" t="n">
         <v>1000</v>
       </c>
       <c r="J64" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K64" t="n">
         <v>950</v>
       </c>
       <c r="L64" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M64" t="n">
         <v>1.09</v>
@@ -16635,16 +16635,16 @@
         <v>1.41</v>
       </c>
       <c r="P64" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R64" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S64" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T64" t="n">
         <v>2</v>
@@ -16713,7 +16713,7 @@
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ64" t="n">
         <v>3.6</v>
@@ -16722,19 +16722,19 @@
         <v>4</v>
       </c>
       <c r="AS64" t="n">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="AT64" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AU64" t="n">
         <v>4</v>
       </c>
       <c r="AV64" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW64" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AX64" t="n">
         <v>5.9</v>
@@ -16743,13 +16743,13 @@
         <v>3.2</v>
       </c>
       <c r="AZ64" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA64" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="BB64" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC64" t="n">
         <v>14</v>
@@ -16758,34 +16758,34 @@
         <v>3.95</v>
       </c>
       <c r="BE64" t="n">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="BF64" t="n">
         <v>9.6</v>
       </c>
       <c r="BG64" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="BH64" t="n">
         <v>3.35</v>
       </c>
       <c r="BI64" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ64" t="n">
         <v>1000</v>
       </c>
       <c r="BK64" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BL64" t="n">
         <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BN64" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BO64" t="n">
         <v>3.2</v>
@@ -16800,13 +16800,13 @@
         <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BT64" t="n">
         <v>1000</v>
       </c>
       <c r="BU64" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV64" t="n">
         <v>1000</v>
@@ -16818,7 +16818,7 @@
         <v>1000</v>
       </c>
       <c r="BY64" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BZ64" t="n">
         <v>0</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -16859,22 +16859,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G65" t="n">
         <v>2.14</v>
       </c>
       <c r="H65" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I65" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J65" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L65" t="n">
         <v>1.53</v>
@@ -16883,7 +16883,7 @@
         <v>1.11</v>
       </c>
       <c r="N65" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O65" t="n">
         <v>1.49</v>
@@ -16904,34 +16904,34 @@
         <v>2.1</v>
       </c>
       <c r="U65" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V65" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W65" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X65" t="n">
         <v>11</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z65" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA65" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB65" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD65" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE65" t="n">
         <v>110</v>
@@ -16952,31 +16952,31 @@
         <v>27</v>
       </c>
       <c r="AK65" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL65" t="n">
         <v>70</v>
       </c>
       <c r="AM65" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN65" t="n">
         <v>26</v>
       </c>
       <c r="AO65" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP65" t="n">
         <v>6.8</v>
       </c>
       <c r="AQ65" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR65" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS65" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AT65" t="n">
         <v>5.1</v>
@@ -16988,10 +16988,10 @@
         <v>16</v>
       </c>
       <c r="AW65" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX65" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY65" t="n">
         <v>8.199999999999999</v>
@@ -17000,7 +17000,7 @@
         <v>21</v>
       </c>
       <c r="BA65" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BB65" t="n">
         <v>19</v>
@@ -17009,28 +17009,28 @@
         <v>19</v>
       </c>
       <c r="BD65" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BE65" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF65" t="n">
         <v>18.5</v>
       </c>
       <c r="BG65" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BH65" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI65" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ65" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK65" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL65" t="n">
         <v>1000</v>
@@ -17039,10 +17039,10 @@
         <v>10</v>
       </c>
       <c r="BN65" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO65" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP65" t="n">
         <v>17</v>
@@ -17060,7 +17060,7 @@
         <v>8.4</v>
       </c>
       <c r="BU65" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BV65" t="n">
         <v>1000</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,234 +843,234 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>FC Supra du Quebec</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="G2" t="n">
-        <v>9.6</v>
+        <v>1.39</v>
       </c>
       <c r="H2" t="n">
-        <v>1.63</v>
+        <v>11.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.65</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>980</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.5</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.94</v>
-      </c>
       <c r="V2" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.9</v>
+        <v>960</v>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AC2" t="n">
-        <v>4</v>
+        <v>960</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>38</v>
+        <v>960</v>
       </c>
       <c r="AI2" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AK2" t="n">
-        <v>80</v>
+        <v>970</v>
       </c>
       <c r="AL2" t="n">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>490</v>
+        <v>990</v>
       </c>
       <c r="AO2" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.4</v>
+        <v>1.05</v>
       </c>
       <c r="AS2" t="n">
-        <v>40</v>
+        <v>1.05</v>
       </c>
       <c r="AT2" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.85</v>
+        <v>1.05</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="AW2" t="n">
-        <v>55</v>
+        <v>1.05</v>
       </c>
       <c r="AX2" t="n">
-        <v>1000</v>
+        <v>1.06</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.5</v>
+        <v>1.05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>32</v>
+        <v>1.05</v>
       </c>
       <c r="BA2" t="n">
-        <v>160</v>
+        <v>1.05</v>
       </c>
       <c r="BB2" t="n">
-        <v>1000</v>
+        <v>1.05</v>
       </c>
       <c r="BC2" t="n">
-        <v>60</v>
+        <v>1.05</v>
       </c>
       <c r="BD2" t="n">
-        <v>120</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>340</v>
+        <v>1.05</v>
       </c>
       <c r="BF2" t="n">
-        <v>200</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
-        <v>160</v>
+        <v>1.05</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,78 +1097,78 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.29</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31</v>
+        <v>3.45</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>1.67</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>1.69</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.72</v>
+        <v>10.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>60</v>
       </c>
       <c r="R3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>330</v>
       </c>
       <c r="T3" t="n">
-        <v>2.86</v>
+        <v>17</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>4.2</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>1.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1177,100 +1177,100 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.66</v>
+        <v>4.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.4</v>
+        <v>29</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>5.7</v>
+        <v>29</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1000</v>
+        <v>1.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AS3" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.4</v>
+        <v>3.95</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.7</v>
+        <v>22</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="AW3" t="n">
-        <v>120</v>
+        <v>340</v>
       </c>
       <c r="AX3" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.800000000000001</v>
+        <v>100</v>
       </c>
       <c r="AZ3" t="n">
-        <v>32</v>
+        <v>260</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="BB3" t="n">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="BC3" t="n">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="BD3" t="n">
-        <v>150</v>
+        <v>330</v>
       </c>
       <c r="BE3" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="BF3" t="n">
-        <v>42</v>
+        <v>300</v>
       </c>
       <c r="BG3" t="n">
-        <v>18</v>
+        <v>290</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,234 +1351,234 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Confianca</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.34</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I4" t="n">
-        <v>14</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.75</v>
-      </c>
       <c r="X4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>410</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>300</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
         <v>50</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AQ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>85</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>300</v>
+      </c>
+      <c r="BF4" t="n">
         <v>120</v>
       </c>
-      <c r="AA4" t="n">
-        <v>520</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>100</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>160</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,515 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ituano</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Maranhao</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>320</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>300</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>85</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>160</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-28 20:00:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ypiranga RS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Confianca</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="X6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>860</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>95</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
